--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1982">
   <si>
     <t>en</t>
   </si>
@@ -5575,379 +5575,382 @@
     <t>Twisted Wonderland</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>Umineko - Ko jočejo</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Undertale rumena</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>Univerzalni simbol</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Do</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>Divje živali v mestih</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>V kot Vendeta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>Valentinovo</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>Vanilija (odstranjeno)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>Vanilijev blok</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>Hrana iz vanilije</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>Čelada Vanilla</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>Vanilija Element</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>Lovci na trezorje</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Zelenjava</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Vozilo</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Vikingi</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Vasilec</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>vaščan (puščava)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>vaščan (džungla)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>vaščan (ravnina)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>vaščan (Savanna)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>vaščan (Snežna tundra)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>vaščan (močvirje)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>vaščan (Tajga)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>Virtualni Youtuber</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>Hoja po mrtvih (Walking Dead)</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>Wallace in Gromit</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>Vojna svetov</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>Bojevniške mačke</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>Mi nosimo medvede</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>Mi smo srečni maloštevilni</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Vreme</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>Dobrodošli doma</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>Kdo je to?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Posodobitev divjine</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>Krila ognja</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>Medvedek Pujsek</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Zima</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>Čudoviti svet čudes</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Les</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Volna</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>Delovna varnostna čelada</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>Razbij ga, Ralph</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>Možje X</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>Simulator Yandere</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>Rumena podmornica</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Mladi</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>Ničelno krilo</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Zodiakalni znak</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>Zombie (vanilija)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
+    <t>Zootopija</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>Umineko - Ko jočejo</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Undertale rumena</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>Univerzalni simbol</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Do</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>Divje živali v mestih</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>V kot Vendeta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>Valentinovo</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>Vanilija (odstranjeno)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>Vanilijev blok</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>Hrana iz vanilije</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>Čelada Vanilla</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>Vanilija Element</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>Lovci na trezorje</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>Zelenjava</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Vozilo</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Vikingi</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>Vasilec</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>vaščan (puščava)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>vaščan (džungla)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>vaščan (ravnina)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>vaščan (Savanna)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>vaščan (Snežna tundra)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>vaščan (močvirje)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>vaščan (Tajga)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>Virtualni Youtuber</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>Hoja po mrtvih (Walking Dead)</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>Wallace in Gromit</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>Vojna svetov</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>Bojevniške mačke</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>Mi nosimo medvede</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>Mi smo srečni maloštevilni</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Vreme</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>Dobrodošli doma</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>Kdo je to?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>Posodobitev divjine</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>Krila ognja</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>Medvedek Pujsek</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Zima</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>Čudoviti svet čudes</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Les</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Volna</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>Delovna varnostna čelada</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>Razbij ga, Ralph</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>Možje X</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>Simulator Yandere</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>Rumena podmornica</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Mladi</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>Ničelno krilo</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>Zodiakalni znak</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>Zombie (vanilija)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
-  </si>
-  <si>
-    <t>Zootopija</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -6306,7 +6309,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15718,19 +15721,27 @@
         <v>1977</v>
       </c>
       <c r="B1176" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1177" t="s">
         <v>1979</v>
       </c>
-      <c r="B1177" t="s">
+    </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
         <v>1980</v>
       </c>
+      <c r="B1178" t="s">
+        <v>1981</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1983">
   <si>
     <t>en</t>
   </si>
@@ -4076,6 +4076,9 @@
   </si>
   <si>
     <t>Odprtokodni predmeti</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -6309,7 +6312,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12705,60 +12708,60 @@
         <v>1354</v>
       </c>
       <c r="B799" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B800" t="s">
         <v>1356</v>
-      </c>
-      <c r="B800" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B801" t="s">
         <v>1358</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B802" t="s">
         <v>1360</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B803" t="s">
         <v>1362</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B804" t="s">
         <v>1364</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B805" t="s">
         <v>1366</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B806" t="s">
         <v>1368</v>
@@ -12785,60 +12788,60 @@
         <v>1371</v>
       </c>
       <c r="B809" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B810" t="s">
         <v>1373</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B811" t="s">
         <v>1375</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B812" t="s">
         <v>1377</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B813" t="s">
         <v>1379</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B814" t="s">
         <v>1381</v>
-      </c>
-      <c r="B814" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B815" t="s">
         <v>1383</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B816" t="s">
         <v>1385</v>
@@ -12849,20 +12852,20 @@
         <v>1386</v>
       </c>
       <c r="B817" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B818" t="s">
         <v>1388</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B819" t="s">
         <v>1390</v>
@@ -12873,28 +12876,28 @@
         <v>1391</v>
       </c>
       <c r="B820" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B821" t="s">
         <v>1393</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B822" t="s">
         <v>1395</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="B823" t="s">
         <v>1397</v>
@@ -12905,12 +12908,12 @@
         <v>1398</v>
       </c>
       <c r="B824" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B825" t="s">
         <v>1400</v>
@@ -12921,12 +12924,12 @@
         <v>1401</v>
       </c>
       <c r="B826" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B827" t="s">
         <v>1403</v>
@@ -12937,12 +12940,12 @@
         <v>1404</v>
       </c>
       <c r="B828" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B829" t="s">
         <v>1406</v>
@@ -12953,12 +12956,12 @@
         <v>1407</v>
       </c>
       <c r="B830" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="B831" t="s">
         <v>1409</v>
@@ -12993,20 +12996,20 @@
         <v>1413</v>
       </c>
       <c r="B835" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B836" t="s">
         <v>1415</v>
-      </c>
-      <c r="B836" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B837" t="s">
         <v>1417</v>
@@ -13017,20 +13020,20 @@
         <v>1418</v>
       </c>
       <c r="B838" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B839" t="s">
         <v>1420</v>
-      </c>
-      <c r="B839" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B840" t="s">
         <v>1422</v>
@@ -13041,12 +13044,12 @@
         <v>1423</v>
       </c>
       <c r="B841" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B842" t="s">
         <v>1425</v>
@@ -13081,108 +13084,108 @@
         <v>1429</v>
       </c>
       <c r="B846" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B847" t="s">
         <v>1431</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B848" t="s">
         <v>1433</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B849" t="s">
         <v>1435</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B850" t="s">
         <v>1437</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B851" t="s">
         <v>1439</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B852" t="s">
         <v>1441</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B853" t="s">
         <v>1443</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B854" t="s">
         <v>1445</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B855" t="s">
         <v>1447</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B856" t="s">
         <v>1449</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B857" t="s">
         <v>1451</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B858" t="s">
         <v>1453</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="B859" t="s">
         <v>1455</v>
@@ -13241,12 +13244,12 @@
         <v>1462</v>
       </c>
       <c r="B866" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B867" t="s">
         <v>1464</v>
@@ -13273,12 +13276,12 @@
         <v>1467</v>
       </c>
       <c r="B870" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B871" t="s">
         <v>1469</v>
@@ -13289,52 +13292,52 @@
         <v>1470</v>
       </c>
       <c r="B872" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B873" t="s">
         <v>1472</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1473</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B874" t="s">
         <v>1474</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B875" t="s">
         <v>1476</v>
-      </c>
-      <c r="B875" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B876" t="s">
         <v>1478</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B877" t="s">
         <v>1480</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B878" t="s">
         <v>1482</v>
@@ -13353,28 +13356,28 @@
         <v>1484</v>
       </c>
       <c r="B880" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B881" t="s">
         <v>1486</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B882" t="s">
         <v>1488</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="B883" t="s">
         <v>1490</v>
@@ -13393,12 +13396,12 @@
         <v>1492</v>
       </c>
       <c r="B885" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B886" t="s">
         <v>1494</v>
@@ -13409,12 +13412,12 @@
         <v>1495</v>
       </c>
       <c r="B887" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B888" t="s">
         <v>1497</v>
@@ -13425,12 +13428,12 @@
         <v>1498</v>
       </c>
       <c r="B889" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B890" t="s">
         <v>1500</v>
@@ -13441,12 +13444,12 @@
         <v>1501</v>
       </c>
       <c r="B891" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B892" t="s">
         <v>1503</v>
@@ -13457,36 +13460,36 @@
         <v>1504</v>
       </c>
       <c r="B893" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B894" t="s">
         <v>1506</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B895" t="s">
         <v>1508</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B896" t="s">
         <v>1510</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B897" t="s">
         <v>1512</v>
@@ -13497,52 +13500,52 @@
         <v>1513</v>
       </c>
       <c r="B898" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B899" t="s">
         <v>1515</v>
-      </c>
-      <c r="B899" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B900" t="s">
         <v>1517</v>
-      </c>
-      <c r="B900" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B901" t="s">
         <v>1519</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B902" t="s">
         <v>1521</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B903" t="s">
         <v>1523</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B904" t="s">
         <v>1525</v>
@@ -13601,28 +13604,28 @@
         <v>1532</v>
       </c>
       <c r="B911" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B912" t="s">
         <v>1534</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1535</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B913" t="s">
         <v>1536</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B914" t="s">
         <v>1538</v>
@@ -13649,44 +13652,44 @@
         <v>1541</v>
       </c>
       <c r="B917" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B918" t="s">
         <v>1543</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B919" t="s">
         <v>1545</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B920" t="s">
         <v>1547</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B921" t="s">
         <v>1549</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B922" t="s">
         <v>1551</v>
@@ -13705,36 +13708,36 @@
         <v>1553</v>
       </c>
       <c r="B924" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B925" t="s">
         <v>1555</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1556</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B926" t="s">
         <v>1557</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B927" t="s">
         <v>1559</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B928" t="s">
         <v>1561</v>
@@ -13745,20 +13748,20 @@
         <v>1562</v>
       </c>
       <c r="B929" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B930" t="s">
         <v>1564</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B931" t="s">
         <v>1566</v>
@@ -13769,12 +13772,12 @@
         <v>1567</v>
       </c>
       <c r="B932" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B933" t="s">
         <v>1569</v>
@@ -13785,60 +13788,60 @@
         <v>1570</v>
       </c>
       <c r="B934" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B935" t="s">
         <v>1572</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B936" t="s">
         <v>1574</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B937" t="s">
         <v>1576</v>
-      </c>
-      <c r="B937" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B938" t="s">
         <v>1578</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B939" t="s">
         <v>1580</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B940" t="s">
         <v>1582</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1583</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B941" t="s">
         <v>1584</v>
@@ -13865,20 +13868,20 @@
         <v>1587</v>
       </c>
       <c r="B944" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B945" t="s">
         <v>1589</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B946" t="s">
         <v>1591</v>
@@ -13921,44 +13924,44 @@
         <v>1596</v>
       </c>
       <c r="B951" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B952" t="s">
         <v>1598</v>
-      </c>
-      <c r="B952" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B953" t="s">
         <v>1600</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B954" t="s">
         <v>1602</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B955" t="s">
         <v>1604</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B956" t="s">
         <v>1606</v>
@@ -13977,36 +13980,36 @@
         <v>1608</v>
       </c>
       <c r="B958" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B959" t="s">
         <v>1610</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B960" t="s">
         <v>1612</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B961" t="s">
         <v>1614</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B962" t="s">
         <v>1616</v>
@@ -14017,20 +14020,20 @@
         <v>1617</v>
       </c>
       <c r="B963" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B964" t="s">
         <v>1619</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1620</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B965" t="s">
         <v>1621</v>
@@ -14049,100 +14052,100 @@
         <v>1623</v>
       </c>
       <c r="B967" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B968" t="s">
         <v>1625</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B969" t="s">
         <v>1627</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B970" t="s">
         <v>1629</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B971" t="s">
         <v>1631</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1632</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B972" t="s">
         <v>1633</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B973" t="s">
         <v>1635</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B974" t="s">
         <v>1637</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B975" t="s">
         <v>1639</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B976" t="s">
         <v>1641</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B977" t="s">
         <v>1643</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B978" t="s">
         <v>1645</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1646</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="B979" t="s">
         <v>1647</v>
@@ -14169,12 +14172,12 @@
         <v>1650</v>
       </c>
       <c r="B982" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B983" t="s">
         <v>1652</v>
@@ -14209,12 +14212,12 @@
         <v>1656</v>
       </c>
       <c r="B987" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B988" t="s">
         <v>1658</v>
@@ -14225,36 +14228,36 @@
         <v>1659</v>
       </c>
       <c r="B989" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B990" t="s">
         <v>1661</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B991" t="s">
         <v>1663</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B992" t="s">
         <v>1665</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1666</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B993" t="s">
         <v>1667</v>
@@ -14265,20 +14268,20 @@
         <v>1668</v>
       </c>
       <c r="B994" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B995" t="s">
         <v>1670</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1671</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B996" t="s">
         <v>1672</v>
@@ -14289,52 +14292,52 @@
         <v>1673</v>
       </c>
       <c r="B997" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B998" t="s">
         <v>1675</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1676</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B999" t="s">
         <v>1677</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1679</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1681</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1683</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1684</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B1003" t="s">
         <v>1685</v>
@@ -14353,28 +14356,28 @@
         <v>1687</v>
       </c>
       <c r="B1005" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1689</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1691</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B1008" t="s">
         <v>1693</v>
@@ -14409,20 +14412,20 @@
         <v>1697</v>
       </c>
       <c r="B1012" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1699</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1700</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1014" t="s">
         <v>1701</v>
@@ -14433,12 +14436,12 @@
         <v>1702</v>
       </c>
       <c r="B1015" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B1016" t="s">
         <v>1704</v>
@@ -14457,20 +14460,20 @@
         <v>1706</v>
       </c>
       <c r="B1018" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1708</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B1020" t="s">
         <v>1710</v>
@@ -14481,28 +14484,28 @@
         <v>1711</v>
       </c>
       <c r="B1021" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1022" t="s">
         <v>1713</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1715</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1716</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="B1024" t="s">
         <v>1717</v>
@@ -14513,12 +14516,12 @@
         <v>1718</v>
       </c>
       <c r="B1025" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B1026" t="s">
         <v>1720</v>
@@ -14537,12 +14540,12 @@
         <v>1722</v>
       </c>
       <c r="B1028" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1029" t="s">
         <v>1724</v>
@@ -14593,20 +14596,20 @@
         <v>1730</v>
       </c>
       <c r="B1035" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B1036" t="s">
         <v>1732</v>
-      </c>
-      <c r="B1036" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B1037" t="s">
         <v>1734</v>
@@ -14617,28 +14620,28 @@
         <v>1735</v>
       </c>
       <c r="B1038" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1039" t="s">
         <v>1737</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1739</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1740</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B1041" t="s">
         <v>1741</v>
@@ -14649,20 +14652,20 @@
         <v>1742</v>
       </c>
       <c r="B1042" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1043" t="s">
         <v>1744</v>
-      </c>
-      <c r="B1043" t="s">
-        <v>1745</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B1044" t="s">
         <v>1746</v>
@@ -14673,124 +14676,124 @@
         <v>1747</v>
       </c>
       <c r="B1045" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1046" t="s">
         <v>1749</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1751</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1753</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1755</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B1050" t="s">
         <v>1757</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>1758</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1051" t="s">
         <v>1759</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>1760</v>
+      </c>
+      <c r="B1052" t="s">
         <v>1761</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1762</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1053" t="s">
         <v>1763</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1765</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1767</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1769</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1771</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1775</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B1060" t="s">
         <v>1777</v>
@@ -14801,100 +14804,100 @@
         <v>1778</v>
       </c>
       <c r="B1061" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1782</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1784</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1786</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1788</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1790</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1792</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1794</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1796</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1798</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1800</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B1073" t="s">
         <v>1802</v>
@@ -14905,20 +14908,20 @@
         <v>1803</v>
       </c>
       <c r="B1074" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1805</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B1076" t="s">
         <v>1807</v>
@@ -14937,12 +14940,12 @@
         <v>1809</v>
       </c>
       <c r="B1078" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B1079" t="s">
         <v>1811</v>
@@ -14953,20 +14956,20 @@
         <v>1812</v>
       </c>
       <c r="B1080" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1081" t="s">
         <v>1814</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B1082" t="s">
         <v>1816</v>
@@ -14977,76 +14980,76 @@
         <v>1817</v>
       </c>
       <c r="B1083" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1084" t="s">
         <v>1819</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1085" t="s">
         <v>1821</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1086" t="s">
         <v>1823</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1087" t="s">
         <v>1825</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1088" t="s">
         <v>1827</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1829</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1831</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1091" t="s">
         <v>1833</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B1092" t="s">
         <v>1835</v>
@@ -15057,44 +15060,44 @@
         <v>1836</v>
       </c>
       <c r="B1093" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1838</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1842</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1844</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="B1098" t="s">
         <v>1846</v>
@@ -15105,20 +15108,20 @@
         <v>1847</v>
       </c>
       <c r="B1099" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B1101" t="s">
         <v>1851</v>
@@ -15137,12 +15140,12 @@
         <v>1853</v>
       </c>
       <c r="B1103" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B1104" t="s">
         <v>1855</v>
@@ -15161,52 +15164,52 @@
         <v>1857</v>
       </c>
       <c r="B1106" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1107" t="s">
         <v>1859</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1108" t="s">
         <v>1861</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1863</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1110" t="s">
         <v>1865</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B1111" t="s">
         <v>1867</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B1112" t="s">
         <v>1869</v>
@@ -15217,44 +15220,44 @@
         <v>1870</v>
       </c>
       <c r="B1113" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1114" t="s">
         <v>1872</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1115" t="s">
         <v>1874</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1876</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1878</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="B1118" t="s">
         <v>1880</v>
@@ -15265,108 +15268,108 @@
         <v>1881</v>
       </c>
       <c r="B1119" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1883</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1885</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1887</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1889</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1890</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1891</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1892</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1893</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1894</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1895</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1896</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1897</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1898</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1899</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1901</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1903</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1905</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1906</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B1132" t="s">
         <v>1907</v>
@@ -15393,12 +15396,12 @@
         <v>1910</v>
       </c>
       <c r="B1135" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B1136" t="s">
         <v>1912</v>
@@ -15409,20 +15412,20 @@
         <v>1913</v>
       </c>
       <c r="B1137" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1915</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B1139" t="s">
         <v>1917</v>
@@ -15449,84 +15452,84 @@
         <v>1920</v>
       </c>
       <c r="B1142" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1922</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1923</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1924</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1925</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1925</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1926</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1927</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1928</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1929</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1930</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1931</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1148" t="s">
         <v>1932</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>1933</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1934</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1935</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1150" t="s">
         <v>1936</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>1937</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1151" t="s">
         <v>1938</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B1152" t="s">
         <v>1940</v>
@@ -15537,44 +15540,44 @@
         <v>1941</v>
       </c>
       <c r="B1153" t="s">
-        <v>1942</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1948</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1949</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1950</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1951</v>
+        <v>1950</v>
       </c>
       <c r="B1158" t="s">
         <v>1951</v>
@@ -15593,12 +15596,12 @@
         <v>1953</v>
       </c>
       <c r="B1160" t="s">
-        <v>1954</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B1161" t="s">
         <v>1955</v>
@@ -15609,20 +15612,20 @@
         <v>1956</v>
       </c>
       <c r="B1162" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1958</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1959</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B1164" t="s">
         <v>1960</v>
@@ -15641,12 +15644,12 @@
         <v>1962</v>
       </c>
       <c r="B1166" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B1167" t="s">
         <v>1964</v>
@@ -15681,20 +15684,20 @@
         <v>1968</v>
       </c>
       <c r="B1171" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B1172" t="s">
         <v>1970</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>1971</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B1173" t="s">
         <v>1972</v>
@@ -15705,20 +15708,20 @@
         <v>1973</v>
       </c>
       <c r="B1174" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1175" t="s">
         <v>1975</v>
-      </c>
-      <c r="B1175" t="s">
-        <v>1976</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B1176" t="s">
         <v>1977</v>
@@ -15729,19 +15732,27 @@
         <v>1978</v>
       </c>
       <c r="B1177" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1178" t="s">
         <v>1980</v>
       </c>
-      <c r="B1178" t="s">
+    </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
         <v>1981</v>
       </c>
+      <c r="B1179" t="s">
+        <v>1982</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1983">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1985">
   <si>
     <t>en</t>
   </si>
@@ -815,6 +815,12 @@
   </si>
   <si>
     <t>Kalih</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>Kaos v kockah</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -6312,7 +6318,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7652,15 +7658,15 @@
         <v>274</v>
       </c>
       <c r="B167" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B168" t="s">
-        <v>276</v>
+        <v>224</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -7676,12 +7682,12 @@
         <v>279</v>
       </c>
       <c r="B170" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B171" t="s">
         <v>281</v>
@@ -7716,28 +7722,28 @@
         <v>288</v>
       </c>
       <c r="B175" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B176" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B177" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B178" t="s">
         <v>292</v>
@@ -7948,12 +7954,12 @@
         <v>343</v>
       </c>
       <c r="B204" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B205" t="s">
         <v>345</v>
@@ -7972,20 +7978,20 @@
         <v>348</v>
       </c>
       <c r="B207" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B208" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B209" t="s">
         <v>351</v>
@@ -8028,12 +8034,12 @@
         <v>360</v>
       </c>
       <c r="B214" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B215" t="s">
         <v>362</v>
@@ -8052,12 +8058,12 @@
         <v>365</v>
       </c>
       <c r="B217" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B218" t="s">
         <v>367</v>
@@ -8068,12 +8074,12 @@
         <v>368</v>
       </c>
       <c r="B219" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B220" t="s">
         <v>370</v>
@@ -8084,20 +8090,20 @@
         <v>371</v>
       </c>
       <c r="B221" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B222" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B223" t="s">
         <v>374</v>
@@ -8124,20 +8130,20 @@
         <v>379</v>
       </c>
       <c r="B226" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B227" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B228" t="s">
         <v>382</v>
@@ -8156,20 +8162,20 @@
         <v>385</v>
       </c>
       <c r="B230" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B231" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B232" t="s">
         <v>388</v>
@@ -8188,20 +8194,20 @@
         <v>391</v>
       </c>
       <c r="B234" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B235" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B236" t="s">
         <v>394</v>
@@ -8244,36 +8250,36 @@
         <v>403</v>
       </c>
       <c r="B241" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B242" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B243" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B244" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B245" t="s">
         <v>408</v>
@@ -8300,12 +8306,12 @@
         <v>413</v>
       </c>
       <c r="B248" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B249" t="s">
         <v>415</v>
@@ -8316,12 +8322,12 @@
         <v>416</v>
       </c>
       <c r="B250" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B251" t="s">
         <v>418</v>
@@ -8332,20 +8338,20 @@
         <v>419</v>
       </c>
       <c r="B252" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B253" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B254" t="s">
         <v>422</v>
@@ -8356,12 +8362,12 @@
         <v>423</v>
       </c>
       <c r="B255" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B256" t="s">
         <v>425</v>
@@ -8428,20 +8434,20 @@
         <v>440</v>
       </c>
       <c r="B264" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B265" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B266" t="s">
         <v>443</v>
@@ -8460,44 +8466,44 @@
         <v>446</v>
       </c>
       <c r="B268" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B269" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B270" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B271" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B272" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B273" t="s">
         <v>452</v>
@@ -8508,20 +8514,20 @@
         <v>453</v>
       </c>
       <c r="B274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B275" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B276" t="s">
         <v>456</v>
@@ -8564,20 +8570,20 @@
         <v>465</v>
       </c>
       <c r="B281" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B282" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B283" t="s">
         <v>468</v>
@@ -8588,20 +8594,20 @@
         <v>469</v>
       </c>
       <c r="B284" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B285" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B286" t="s">
         <v>472</v>
@@ -8628,12 +8634,12 @@
         <v>477</v>
       </c>
       <c r="B289" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B290" t="s">
         <v>479</v>
@@ -8668,20 +8674,20 @@
         <v>486</v>
       </c>
       <c r="B294" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B295" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B296" t="s">
         <v>489</v>
@@ -8708,20 +8714,20 @@
         <v>494</v>
       </c>
       <c r="B299" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B300" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B301" t="s">
         <v>497</v>
@@ -8732,12 +8738,12 @@
         <v>498</v>
       </c>
       <c r="B302" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B303" t="s">
         <v>500</v>
@@ -8780,20 +8786,20 @@
         <v>509</v>
       </c>
       <c r="B308" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B309" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B310" t="s">
         <v>512</v>
@@ -8812,20 +8818,20 @@
         <v>515</v>
       </c>
       <c r="B312" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B313" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B314" t="s">
         <v>518</v>
@@ -8836,20 +8842,20 @@
         <v>519</v>
       </c>
       <c r="B315" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B316" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B317" t="s">
         <v>522</v>
@@ -8860,36 +8866,36 @@
         <v>523</v>
       </c>
       <c r="B318" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B319" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B320" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B321" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B322" t="s">
         <v>528</v>
@@ -8908,20 +8914,20 @@
         <v>531</v>
       </c>
       <c r="B324" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B325" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B326" t="s">
         <v>534</v>
@@ -8956,12 +8962,12 @@
         <v>541</v>
       </c>
       <c r="B330" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B331" t="s">
         <v>543</v>
@@ -9028,12 +9034,12 @@
         <v>558</v>
       </c>
       <c r="B339" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B340" t="s">
         <v>560</v>
@@ -9052,12 +9058,12 @@
         <v>563</v>
       </c>
       <c r="B342" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B343" t="s">
         <v>565</v>
@@ -9220,12 +9226,12 @@
         <v>604</v>
       </c>
       <c r="B363" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B364" t="s">
         <v>606</v>
@@ -9756,20 +9762,20 @@
         <v>737</v>
       </c>
       <c r="B430" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B431" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B432" t="s">
         <v>740</v>
@@ -9780,20 +9786,20 @@
         <v>741</v>
       </c>
       <c r="B433" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B434" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B435" t="s">
         <v>744</v>
@@ -9868,12 +9874,12 @@
         <v>761</v>
       </c>
       <c r="B444" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B445" t="s">
         <v>763</v>
@@ -9884,12 +9890,12 @@
         <v>764</v>
       </c>
       <c r="B446" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B447" t="s">
         <v>766</v>
@@ -9900,12 +9906,12 @@
         <v>767</v>
       </c>
       <c r="B448" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B449" t="s">
         <v>769</v>
@@ -9940,20 +9946,20 @@
         <v>776</v>
       </c>
       <c r="B453" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B454" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B455" t="s">
         <v>779</v>
@@ -9980,12 +9986,12 @@
         <v>784</v>
       </c>
       <c r="B458" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B459" t="s">
         <v>786</v>
@@ -10020,36 +10026,36 @@
         <v>793</v>
       </c>
       <c r="B463" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B464" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B465" t="s">
-        <v>522</v>
+        <v>796</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B466" t="s">
-        <v>796</v>
+        <v>524</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B467" t="s">
         <v>798</v>
@@ -10060,12 +10066,12 @@
         <v>799</v>
       </c>
       <c r="B468" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B469" t="s">
         <v>801</v>
@@ -10084,36 +10090,36 @@
         <v>804</v>
       </c>
       <c r="B471" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B472" t="s">
-        <v>522</v>
+        <v>806</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B473" t="s">
-        <v>806</v>
+        <v>524</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B474" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B475" t="s">
         <v>809</v>
@@ -10124,12 +10130,12 @@
         <v>810</v>
       </c>
       <c r="B476" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B477" t="s">
         <v>812</v>
@@ -10164,20 +10170,20 @@
         <v>819</v>
       </c>
       <c r="B481" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B482" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B483" t="s">
         <v>822</v>
@@ -10188,12 +10194,12 @@
         <v>823</v>
       </c>
       <c r="B484" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B485" t="s">
         <v>825</v>
@@ -10204,36 +10210,36 @@
         <v>826</v>
       </c>
       <c r="B486" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B487" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B488" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B489" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B490" t="s">
         <v>831</v>
@@ -10388,12 +10394,12 @@
         <v>868</v>
       </c>
       <c r="B509" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B510" t="s">
         <v>870</v>
@@ -10412,12 +10418,12 @@
         <v>873</v>
       </c>
       <c r="B512" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B513" t="s">
         <v>875</v>
@@ -10468,20 +10474,20 @@
         <v>886</v>
       </c>
       <c r="B519" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B520" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B521" t="s">
         <v>889</v>
@@ -10564,12 +10570,12 @@
         <v>908</v>
       </c>
       <c r="B531" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B532" t="s">
         <v>910</v>
@@ -10588,20 +10594,20 @@
         <v>913</v>
       </c>
       <c r="B534" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B535" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B536" t="s">
         <v>916</v>
@@ -10620,28 +10626,28 @@
         <v>919</v>
       </c>
       <c r="B538" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B539" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B540" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B541" t="s">
         <v>923</v>
@@ -10676,20 +10682,20 @@
         <v>930</v>
       </c>
       <c r="B545" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B546" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B547" t="s">
         <v>933</v>
@@ -10708,20 +10714,20 @@
         <v>936</v>
       </c>
       <c r="B549" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B550" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B551" t="s">
         <v>939</v>
@@ -10748,12 +10754,12 @@
         <v>944</v>
       </c>
       <c r="B554" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B555" t="s">
         <v>946</v>
@@ -10812,28 +10818,28 @@
         <v>959</v>
       </c>
       <c r="B562" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B563" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B564" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B565" t="s">
         <v>963</v>
@@ -10852,12 +10858,12 @@
         <v>966</v>
       </c>
       <c r="B567" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B568" t="s">
         <v>968</v>
@@ -10908,12 +10914,12 @@
         <v>979</v>
       </c>
       <c r="B574" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B575" t="s">
         <v>981</v>
@@ -10924,28 +10930,28 @@
         <v>982</v>
       </c>
       <c r="B576" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B577" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B578" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B579" t="s">
         <v>986</v>
@@ -10964,12 +10970,12 @@
         <v>989</v>
       </c>
       <c r="B581" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B582" t="s">
         <v>991</v>
@@ -11044,12 +11050,12 @@
         <v>1008</v>
       </c>
       <c r="B591" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B592" t="s">
         <v>1010</v>
@@ -11060,12 +11066,12 @@
         <v>1011</v>
       </c>
       <c r="B593" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B594" t="s">
         <v>1013</v>
@@ -11132,20 +11138,20 @@
         <v>1028</v>
       </c>
       <c r="B602" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B603" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B604" t="s">
         <v>1031</v>
@@ -11156,12 +11162,12 @@
         <v>1032</v>
       </c>
       <c r="B605" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B606" t="s">
         <v>1034</v>
@@ -11212,12 +11218,12 @@
         <v>1045</v>
       </c>
       <c r="B612" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B613" t="s">
         <v>1047</v>
@@ -11236,12 +11242,12 @@
         <v>1050</v>
       </c>
       <c r="B615" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B616" t="s">
         <v>1052</v>
@@ -11268,12 +11274,12 @@
         <v>1057</v>
       </c>
       <c r="B619" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B620" t="s">
         <v>1059</v>
@@ -11284,12 +11290,12 @@
         <v>1060</v>
       </c>
       <c r="B621" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B622" t="s">
         <v>1062</v>
@@ -11308,12 +11314,12 @@
         <v>1065</v>
       </c>
       <c r="B624" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B625" t="s">
         <v>1067</v>
@@ -11340,44 +11346,44 @@
         <v>1072</v>
       </c>
       <c r="B628" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B629" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B630" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B631" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B632" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B633" t="s">
         <v>1078</v>
@@ -11396,28 +11402,28 @@
         <v>1081</v>
       </c>
       <c r="B635" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B636" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B637" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B638" t="s">
         <v>1085</v>
@@ -11428,12 +11434,12 @@
         <v>1086</v>
       </c>
       <c r="B639" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B640" t="s">
         <v>1088</v>
@@ -11444,12 +11450,12 @@
         <v>1089</v>
       </c>
       <c r="B641" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B642" t="s">
         <v>1091</v>
@@ -11460,20 +11466,20 @@
         <v>1092</v>
       </c>
       <c r="B643" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B644" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B645" t="s">
         <v>1095</v>
@@ -11508,28 +11514,28 @@
         <v>1102</v>
       </c>
       <c r="B649" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B650" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B651" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B652" t="s">
         <v>1106</v>
@@ -11540,12 +11546,12 @@
         <v>1107</v>
       </c>
       <c r="B653" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B654" t="s">
         <v>1109</v>
@@ -11572,12 +11578,12 @@
         <v>1114</v>
       </c>
       <c r="B657" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B658" t="s">
         <v>1116</v>
@@ -11652,12 +11658,12 @@
         <v>1133</v>
       </c>
       <c r="B667" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B668" t="s">
         <v>1135</v>
@@ -11740,12 +11746,12 @@
         <v>1154</v>
       </c>
       <c r="B678" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B679" t="s">
         <v>1156</v>
@@ -11772,20 +11778,20 @@
         <v>1161</v>
       </c>
       <c r="B682" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B683" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B684" t="s">
         <v>1164</v>
@@ -11868,12 +11874,12 @@
         <v>1183</v>
       </c>
       <c r="B694" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B695" t="s">
         <v>1185</v>
@@ -11916,12 +11922,12 @@
         <v>1194</v>
       </c>
       <c r="B700" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B701" t="s">
         <v>1196</v>
@@ -11932,20 +11938,20 @@
         <v>1197</v>
       </c>
       <c r="B702" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B703" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B704" t="s">
         <v>1200</v>
@@ -11956,28 +11962,28 @@
         <v>1201</v>
       </c>
       <c r="B705" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B706" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B707" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B708" t="s">
         <v>1205</v>
@@ -11996,20 +12002,20 @@
         <v>1208</v>
       </c>
       <c r="B710" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B711" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B712" t="s">
         <v>1211</v>
@@ -12036,20 +12042,20 @@
         <v>1216</v>
       </c>
       <c r="B715" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B716" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B717" t="s">
         <v>1219</v>
@@ -12068,12 +12074,12 @@
         <v>1222</v>
       </c>
       <c r="B719" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B720" t="s">
         <v>1224</v>
@@ -12108,20 +12114,20 @@
         <v>1231</v>
       </c>
       <c r="B724" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B725" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B726" t="s">
         <v>1234</v>
@@ -12140,20 +12146,20 @@
         <v>1237</v>
       </c>
       <c r="B728" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B729" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B730" t="s">
         <v>1240</v>
@@ -12164,12 +12170,12 @@
         <v>1241</v>
       </c>
       <c r="B731" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B732" t="s">
         <v>1243</v>
@@ -12196,12 +12202,12 @@
         <v>1248</v>
       </c>
       <c r="B735" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B736" t="s">
         <v>1250</v>
@@ -12220,12 +12226,12 @@
         <v>1253</v>
       </c>
       <c r="B738" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B739" t="s">
         <v>1255</v>
@@ -12252,20 +12258,20 @@
         <v>1260</v>
       </c>
       <c r="B742" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B743" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B744" t="s">
         <v>1263</v>
@@ -12284,20 +12290,20 @@
         <v>1266</v>
       </c>
       <c r="B746" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B747" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B748" t="s">
         <v>1269</v>
@@ -12396,12 +12402,12 @@
         <v>1292</v>
       </c>
       <c r="B760" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B761" t="s">
         <v>1294</v>
@@ -12412,20 +12418,20 @@
         <v>1295</v>
       </c>
       <c r="B762" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B763" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B764" t="s">
         <v>1298</v>
@@ -12468,12 +12474,12 @@
         <v>1307</v>
       </c>
       <c r="B769" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B770" t="s">
         <v>1309</v>
@@ -12572,36 +12578,36 @@
         <v>1332</v>
       </c>
       <c r="B782" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B783" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B784" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B785" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B786" t="s">
         <v>1337</v>
@@ -12620,12 +12626,12 @@
         <v>1340</v>
       </c>
       <c r="B788" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B789" t="s">
         <v>1342</v>
@@ -12636,20 +12642,20 @@
         <v>1343</v>
       </c>
       <c r="B790" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B791" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B792" t="s">
         <v>1346</v>
@@ -12660,36 +12666,36 @@
         <v>1347</v>
       </c>
       <c r="B793" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B794" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B795" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B796" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B797" t="s">
         <v>1352</v>
@@ -12700,20 +12706,20 @@
         <v>1353</v>
       </c>
       <c r="B798" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B799" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B800" t="s">
         <v>1356</v>
@@ -12772,28 +12778,28 @@
         <v>1369</v>
       </c>
       <c r="B807" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B808" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B809" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B810" t="s">
         <v>1373</v>
@@ -12852,12 +12858,12 @@
         <v>1386</v>
       </c>
       <c r="B817" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B818" t="s">
         <v>1388</v>
@@ -12876,12 +12882,12 @@
         <v>1391</v>
       </c>
       <c r="B820" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B821" t="s">
         <v>1393</v>
@@ -12908,12 +12914,12 @@
         <v>1398</v>
       </c>
       <c r="B824" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B825" t="s">
         <v>1400</v>
@@ -12924,12 +12930,12 @@
         <v>1401</v>
       </c>
       <c r="B826" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B827" t="s">
         <v>1403</v>
@@ -12940,12 +12946,12 @@
         <v>1404</v>
       </c>
       <c r="B828" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B829" t="s">
         <v>1406</v>
@@ -12956,12 +12962,12 @@
         <v>1407</v>
       </c>
       <c r="B830" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B831" t="s">
         <v>1409</v>
@@ -12972,36 +12978,36 @@
         <v>1410</v>
       </c>
       <c r="B832" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B833" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B834" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B835" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B836" t="s">
         <v>1415</v>
@@ -13020,12 +13026,12 @@
         <v>1418</v>
       </c>
       <c r="B838" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B839" t="s">
         <v>1420</v>
@@ -13044,12 +13050,12 @@
         <v>1423</v>
       </c>
       <c r="B841" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B842" t="s">
         <v>1425</v>
@@ -13060,36 +13066,36 @@
         <v>1426</v>
       </c>
       <c r="B843" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B844" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B845" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B846" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B847" t="s">
         <v>1431</v>
@@ -13196,60 +13202,60 @@
         <v>1456</v>
       </c>
       <c r="B860" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B861" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B862" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B863" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B864" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B865" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B866" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B867" t="s">
         <v>1464</v>
@@ -13260,28 +13266,28 @@
         <v>1465</v>
       </c>
       <c r="B868" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B869" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B870" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B871" t="s">
         <v>1469</v>
@@ -13292,12 +13298,12 @@
         <v>1470</v>
       </c>
       <c r="B872" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B873" t="s">
         <v>1472</v>
@@ -13348,20 +13354,20 @@
         <v>1483</v>
       </c>
       <c r="B879" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B880" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B881" t="s">
         <v>1486</v>
@@ -13388,20 +13394,20 @@
         <v>1491</v>
       </c>
       <c r="B884" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B885" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B886" t="s">
         <v>1494</v>
@@ -13412,12 +13418,12 @@
         <v>1495</v>
       </c>
       <c r="B887" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B888" t="s">
         <v>1497</v>
@@ -13428,12 +13434,12 @@
         <v>1498</v>
       </c>
       <c r="B889" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B890" t="s">
         <v>1500</v>
@@ -13444,12 +13450,12 @@
         <v>1501</v>
       </c>
       <c r="B891" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B892" t="s">
         <v>1503</v>
@@ -13460,12 +13466,12 @@
         <v>1504</v>
       </c>
       <c r="B893" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B894" t="s">
         <v>1506</v>
@@ -13500,12 +13506,12 @@
         <v>1513</v>
       </c>
       <c r="B898" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B899" t="s">
         <v>1515</v>
@@ -13556,60 +13562,60 @@
         <v>1526</v>
       </c>
       <c r="B905" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B906" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B907" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B908" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B909" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B910" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B911" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B912" t="s">
         <v>1534</v>
@@ -13636,28 +13642,28 @@
         <v>1539</v>
       </c>
       <c r="B915" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B916" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B917" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B918" t="s">
         <v>1543</v>
@@ -13700,20 +13706,20 @@
         <v>1552</v>
       </c>
       <c r="B923" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B924" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B925" t="s">
         <v>1555</v>
@@ -13748,12 +13754,12 @@
         <v>1562</v>
       </c>
       <c r="B929" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B930" t="s">
         <v>1564</v>
@@ -13772,12 +13778,12 @@
         <v>1567</v>
       </c>
       <c r="B932" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B933" t="s">
         <v>1569</v>
@@ -13788,12 +13794,12 @@
         <v>1570</v>
       </c>
       <c r="B934" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B935" t="s">
         <v>1572</v>
@@ -13852,28 +13858,28 @@
         <v>1585</v>
       </c>
       <c r="B942" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B943" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B944" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B945" t="s">
         <v>1589</v>
@@ -13892,44 +13898,44 @@
         <v>1592</v>
       </c>
       <c r="B947" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B948" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B949" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B950" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B951" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B952" t="s">
         <v>1598</v>
@@ -13972,20 +13978,20 @@
         <v>1607</v>
       </c>
       <c r="B957" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B958" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B959" t="s">
         <v>1610</v>
@@ -14020,12 +14026,12 @@
         <v>1617</v>
       </c>
       <c r="B963" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B964" t="s">
         <v>1619</v>
@@ -14044,20 +14050,20 @@
         <v>1622</v>
       </c>
       <c r="B966" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B967" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B968" t="s">
         <v>1625</v>
@@ -14156,28 +14162,28 @@
         <v>1648</v>
       </c>
       <c r="B980" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B981" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B982" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B983" t="s">
         <v>1652</v>
@@ -14188,36 +14194,36 @@
         <v>1653</v>
       </c>
       <c r="B984" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B985" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B986" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B987" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B988" t="s">
         <v>1658</v>
@@ -14228,12 +14234,12 @@
         <v>1659</v>
       </c>
       <c r="B989" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B990" t="s">
         <v>1661</v>
@@ -14268,12 +14274,12 @@
         <v>1668</v>
       </c>
       <c r="B994" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B995" t="s">
         <v>1670</v>
@@ -14292,12 +14298,12 @@
         <v>1673</v>
       </c>
       <c r="B997" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B998" t="s">
         <v>1675</v>
@@ -14348,20 +14354,20 @@
         <v>1686</v>
       </c>
       <c r="B1004" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1005" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1006" t="s">
         <v>1689</v>
@@ -14388,36 +14394,36 @@
         <v>1694</v>
       </c>
       <c r="B1009" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1010" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1011" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1012" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1013" t="s">
         <v>1699</v>
@@ -14436,12 +14442,12 @@
         <v>1702</v>
       </c>
       <c r="B1015" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1016" t="s">
         <v>1704</v>
@@ -14452,20 +14458,20 @@
         <v>1705</v>
       </c>
       <c r="B1017" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1018" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1019" t="s">
         <v>1708</v>
@@ -14484,12 +14490,12 @@
         <v>1711</v>
       </c>
       <c r="B1021" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1022" t="s">
         <v>1713</v>
@@ -14516,12 +14522,12 @@
         <v>1718</v>
       </c>
       <c r="B1025" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1026" t="s">
         <v>1720</v>
@@ -14532,20 +14538,20 @@
         <v>1721</v>
       </c>
       <c r="B1027" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1028" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1029" t="s">
         <v>1724</v>
@@ -14556,52 +14562,52 @@
         <v>1725</v>
       </c>
       <c r="B1030" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1031" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1032" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1033" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1034" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1035" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1036" t="s">
         <v>1732</v>
@@ -14620,12 +14626,12 @@
         <v>1735</v>
       </c>
       <c r="B1038" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1039" t="s">
         <v>1737</v>
@@ -14652,12 +14658,12 @@
         <v>1742</v>
       </c>
       <c r="B1042" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1043" t="s">
         <v>1744</v>
@@ -14676,12 +14682,12 @@
         <v>1747</v>
       </c>
       <c r="B1045" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B1046" t="s">
         <v>1749</v>
@@ -14804,12 +14810,12 @@
         <v>1778</v>
       </c>
       <c r="B1061" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1062" t="s">
         <v>1780</v>
@@ -14908,12 +14914,12 @@
         <v>1803</v>
       </c>
       <c r="B1074" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1075" t="s">
         <v>1805</v>
@@ -14932,20 +14938,20 @@
         <v>1808</v>
       </c>
       <c r="B1077" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1078" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1079" t="s">
         <v>1811</v>
@@ -14956,12 +14962,12 @@
         <v>1812</v>
       </c>
       <c r="B1080" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1081" t="s">
         <v>1814</v>
@@ -14980,12 +14986,12 @@
         <v>1817</v>
       </c>
       <c r="B1083" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1084" t="s">
         <v>1819</v>
@@ -15060,12 +15066,12 @@
         <v>1836</v>
       </c>
       <c r="B1093" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1094" t="s">
         <v>1838</v>
@@ -15108,12 +15114,12 @@
         <v>1847</v>
       </c>
       <c r="B1099" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="B1100" t="s">
         <v>1849</v>
@@ -15132,20 +15138,20 @@
         <v>1852</v>
       </c>
       <c r="B1102" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1103" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1104" t="s">
         <v>1855</v>
@@ -15156,20 +15162,20 @@
         <v>1856</v>
       </c>
       <c r="B1105" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1106" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1107" t="s">
         <v>1859</v>
@@ -15220,12 +15226,12 @@
         <v>1870</v>
       </c>
       <c r="B1113" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1114" t="s">
         <v>1872</v>
@@ -15268,12 +15274,12 @@
         <v>1881</v>
       </c>
       <c r="B1119" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1120" t="s">
         <v>1883</v>
@@ -15380,28 +15386,28 @@
         <v>1908</v>
       </c>
       <c r="B1133" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1134" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1135" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1136" t="s">
         <v>1912</v>
@@ -15412,12 +15418,12 @@
         <v>1913</v>
       </c>
       <c r="B1137" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1138" t="s">
         <v>1915</v>
@@ -15436,28 +15442,28 @@
         <v>1918</v>
       </c>
       <c r="B1140" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1141" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1142" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1143" t="s">
         <v>1922</v>
@@ -15540,12 +15546,12 @@
         <v>1941</v>
       </c>
       <c r="B1153" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1154" t="s">
         <v>1943</v>
@@ -15588,20 +15594,20 @@
         <v>1952</v>
       </c>
       <c r="B1159" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="B1160" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="B1161" t="s">
         <v>1955</v>
@@ -15612,12 +15618,12 @@
         <v>1956</v>
       </c>
       <c r="B1162" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1163" t="s">
         <v>1958</v>
@@ -15636,20 +15642,20 @@
         <v>1961</v>
       </c>
       <c r="B1165" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1166" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="B1167" t="s">
         <v>1964</v>
@@ -15660,36 +15666,36 @@
         <v>1965</v>
       </c>
       <c r="B1168" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1169" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1170" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1171" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B1172" t="s">
         <v>1970</v>
@@ -15708,12 +15714,12 @@
         <v>1973</v>
       </c>
       <c r="B1174" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1175" t="s">
         <v>1975</v>
@@ -15732,12 +15738,12 @@
         <v>1978</v>
       </c>
       <c r="B1177" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1178" t="s">
         <v>1980</v>
@@ -15751,8 +15757,16 @@
         <v>1982</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>1984</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1985">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1987">
   <si>
     <t>en</t>
   </si>
@@ -4400,6 +4400,12 @@
   </si>
   <si>
     <t>Pop Team Epic</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>Izvajalec Popee</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -6318,7 +6324,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13234,36 +13240,36 @@
         <v>1461</v>
       </c>
       <c r="B864" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B865" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B866" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B867" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B868" t="s">
         <v>1466</v>
@@ -13274,28 +13280,28 @@
         <v>1467</v>
       </c>
       <c r="B869" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B870" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B871" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B872" t="s">
         <v>1471</v>
@@ -13306,12 +13312,12 @@
         <v>1472</v>
       </c>
       <c r="B873" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B874" t="s">
         <v>1474</v>
@@ -13362,20 +13368,20 @@
         <v>1485</v>
       </c>
       <c r="B880" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B881" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B882" t="s">
         <v>1488</v>
@@ -13402,20 +13408,20 @@
         <v>1493</v>
       </c>
       <c r="B885" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B886" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B887" t="s">
         <v>1496</v>
@@ -13426,12 +13432,12 @@
         <v>1497</v>
       </c>
       <c r="B888" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B889" t="s">
         <v>1499</v>
@@ -13442,12 +13448,12 @@
         <v>1500</v>
       </c>
       <c r="B890" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B891" t="s">
         <v>1502</v>
@@ -13458,12 +13464,12 @@
         <v>1503</v>
       </c>
       <c r="B892" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B893" t="s">
         <v>1505</v>
@@ -13474,12 +13480,12 @@
         <v>1506</v>
       </c>
       <c r="B894" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B895" t="s">
         <v>1508</v>
@@ -13514,12 +13520,12 @@
         <v>1515</v>
       </c>
       <c r="B899" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B900" t="s">
         <v>1517</v>
@@ -13570,60 +13576,60 @@
         <v>1528</v>
       </c>
       <c r="B906" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B907" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B908" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B909" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B910" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B911" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B912" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B913" t="s">
         <v>1536</v>
@@ -13650,28 +13656,28 @@
         <v>1541</v>
       </c>
       <c r="B916" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B917" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B918" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B919" t="s">
         <v>1545</v>
@@ -13714,20 +13720,20 @@
         <v>1554</v>
       </c>
       <c r="B924" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B925" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B926" t="s">
         <v>1557</v>
@@ -13762,12 +13768,12 @@
         <v>1564</v>
       </c>
       <c r="B930" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B931" t="s">
         <v>1566</v>
@@ -13786,12 +13792,12 @@
         <v>1569</v>
       </c>
       <c r="B933" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B934" t="s">
         <v>1571</v>
@@ -13802,12 +13808,12 @@
         <v>1572</v>
       </c>
       <c r="B935" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B936" t="s">
         <v>1574</v>
@@ -13866,28 +13872,28 @@
         <v>1587</v>
       </c>
       <c r="B943" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B944" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B945" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B946" t="s">
         <v>1591</v>
@@ -13906,44 +13912,44 @@
         <v>1594</v>
       </c>
       <c r="B948" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B949" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B950" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B951" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B952" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B953" t="s">
         <v>1600</v>
@@ -13986,20 +13992,20 @@
         <v>1609</v>
       </c>
       <c r="B958" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B959" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B960" t="s">
         <v>1612</v>
@@ -14034,12 +14040,12 @@
         <v>1619</v>
       </c>
       <c r="B964" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B965" t="s">
         <v>1621</v>
@@ -14058,20 +14064,20 @@
         <v>1624</v>
       </c>
       <c r="B967" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B968" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B969" t="s">
         <v>1627</v>
@@ -14170,28 +14176,28 @@
         <v>1650</v>
       </c>
       <c r="B981" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B982" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B983" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B984" t="s">
         <v>1654</v>
@@ -14202,36 +14208,36 @@
         <v>1655</v>
       </c>
       <c r="B985" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B986" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B987" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B988" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B989" t="s">
         <v>1660</v>
@@ -14242,12 +14248,12 @@
         <v>1661</v>
       </c>
       <c r="B990" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B991" t="s">
         <v>1663</v>
@@ -14282,12 +14288,12 @@
         <v>1670</v>
       </c>
       <c r="B995" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B996" t="s">
         <v>1672</v>
@@ -14306,12 +14312,12 @@
         <v>1675</v>
       </c>
       <c r="B998" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B999" t="s">
         <v>1677</v>
@@ -14362,20 +14368,20 @@
         <v>1688</v>
       </c>
       <c r="B1005" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1006" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1007" t="s">
         <v>1691</v>
@@ -14402,36 +14408,36 @@
         <v>1696</v>
       </c>
       <c r="B1010" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1011" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1012" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1013" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1014" t="s">
         <v>1701</v>
@@ -14450,12 +14456,12 @@
         <v>1704</v>
       </c>
       <c r="B1016" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1017" t="s">
         <v>1706</v>
@@ -14466,20 +14472,20 @@
         <v>1707</v>
       </c>
       <c r="B1018" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1019" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1020" t="s">
         <v>1710</v>
@@ -14498,12 +14504,12 @@
         <v>1713</v>
       </c>
       <c r="B1022" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1023" t="s">
         <v>1715</v>
@@ -14530,12 +14536,12 @@
         <v>1720</v>
       </c>
       <c r="B1026" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1027" t="s">
         <v>1722</v>
@@ -14546,20 +14552,20 @@
         <v>1723</v>
       </c>
       <c r="B1028" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1029" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1030" t="s">
         <v>1726</v>
@@ -14570,52 +14576,52 @@
         <v>1727</v>
       </c>
       <c r="B1031" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1032" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1033" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1034" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1035" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1036" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1037" t="s">
         <v>1734</v>
@@ -14634,12 +14640,12 @@
         <v>1737</v>
       </c>
       <c r="B1039" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1040" t="s">
         <v>1739</v>
@@ -14666,12 +14672,12 @@
         <v>1744</v>
       </c>
       <c r="B1043" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1044" t="s">
         <v>1746</v>
@@ -14690,12 +14696,12 @@
         <v>1749</v>
       </c>
       <c r="B1046" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1047" t="s">
         <v>1751</v>
@@ -14818,12 +14824,12 @@
         <v>1780</v>
       </c>
       <c r="B1062" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1063" t="s">
         <v>1782</v>
@@ -14922,12 +14928,12 @@
         <v>1805</v>
       </c>
       <c r="B1075" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1076" t="s">
         <v>1807</v>
@@ -14946,20 +14952,20 @@
         <v>1810</v>
       </c>
       <c r="B1078" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1079" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1080" t="s">
         <v>1813</v>
@@ -14970,12 +14976,12 @@
         <v>1814</v>
       </c>
       <c r="B1081" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1082" t="s">
         <v>1816</v>
@@ -14994,12 +15000,12 @@
         <v>1819</v>
       </c>
       <c r="B1084" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1085" t="s">
         <v>1821</v>
@@ -15074,12 +15080,12 @@
         <v>1838</v>
       </c>
       <c r="B1094" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1095" t="s">
         <v>1840</v>
@@ -15122,12 +15128,12 @@
         <v>1849</v>
       </c>
       <c r="B1100" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1101" t="s">
         <v>1851</v>
@@ -15146,20 +15152,20 @@
         <v>1854</v>
       </c>
       <c r="B1103" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1104" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1105" t="s">
         <v>1857</v>
@@ -15170,20 +15176,20 @@
         <v>1858</v>
       </c>
       <c r="B1106" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1107" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1108" t="s">
         <v>1861</v>
@@ -15234,12 +15240,12 @@
         <v>1872</v>
       </c>
       <c r="B1114" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1115" t="s">
         <v>1874</v>
@@ -15282,12 +15288,12 @@
         <v>1883</v>
       </c>
       <c r="B1120" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B1121" t="s">
         <v>1885</v>
@@ -15394,28 +15400,28 @@
         <v>1910</v>
       </c>
       <c r="B1134" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1135" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1136" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1137" t="s">
         <v>1914</v>
@@ -15426,12 +15432,12 @@
         <v>1915</v>
       </c>
       <c r="B1138" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1139" t="s">
         <v>1917</v>
@@ -15450,28 +15456,28 @@
         <v>1920</v>
       </c>
       <c r="B1141" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1142" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1143" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1144" t="s">
         <v>1924</v>
@@ -15554,12 +15560,12 @@
         <v>1943</v>
       </c>
       <c r="B1154" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B1155" t="s">
         <v>1945</v>
@@ -15602,20 +15608,20 @@
         <v>1954</v>
       </c>
       <c r="B1160" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B1161" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="B1162" t="s">
         <v>1957</v>
@@ -15626,12 +15632,12 @@
         <v>1958</v>
       </c>
       <c r="B1163" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="B1164" t="s">
         <v>1960</v>
@@ -15650,20 +15656,20 @@
         <v>1963</v>
       </c>
       <c r="B1166" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B1167" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1168" t="s">
         <v>1966</v>
@@ -15674,36 +15680,36 @@
         <v>1967</v>
       </c>
       <c r="B1169" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1170" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B1171" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B1172" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B1173" t="s">
         <v>1972</v>
@@ -15722,12 +15728,12 @@
         <v>1975</v>
       </c>
       <c r="B1175" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1176" t="s">
         <v>1977</v>
@@ -15746,12 +15752,12 @@
         <v>1980</v>
       </c>
       <c r="B1178" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1179" t="s">
         <v>1982</v>
@@ -15765,8 +15771,16 @@
         <v>1984</v>
       </c>
     </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>1986</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1989">
   <si>
     <t>en</t>
   </si>
@@ -5453,6 +5453,12 @@
   </si>
   <si>
     <t>Konstrukcija Tinker's Construct</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>Droben prevzem</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -6324,7 +6330,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14960,20 +14966,20 @@
         <v>1812</v>
       </c>
       <c r="B1079" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1080" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1081" t="s">
         <v>1815</v>
@@ -14984,12 +14990,12 @@
         <v>1816</v>
       </c>
       <c r="B1082" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1083" t="s">
         <v>1818</v>
@@ -15008,12 +15014,12 @@
         <v>1821</v>
       </c>
       <c r="B1085" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1086" t="s">
         <v>1823</v>
@@ -15088,12 +15094,12 @@
         <v>1840</v>
       </c>
       <c r="B1095" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="B1096" t="s">
         <v>1842</v>
@@ -15136,12 +15142,12 @@
         <v>1851</v>
       </c>
       <c r="B1101" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1102" t="s">
         <v>1853</v>
@@ -15160,20 +15166,20 @@
         <v>1856</v>
       </c>
       <c r="B1104" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1105" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="B1106" t="s">
         <v>1859</v>
@@ -15184,20 +15190,20 @@
         <v>1860</v>
       </c>
       <c r="B1107" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1108" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1109" t="s">
         <v>1863</v>
@@ -15248,12 +15254,12 @@
         <v>1874</v>
       </c>
       <c r="B1115" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1116" t="s">
         <v>1876</v>
@@ -15296,12 +15302,12 @@
         <v>1885</v>
       </c>
       <c r="B1121" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="B1122" t="s">
         <v>1887</v>
@@ -15408,28 +15414,28 @@
         <v>1912</v>
       </c>
       <c r="B1135" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1136" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1137" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1138" t="s">
         <v>1916</v>
@@ -15440,12 +15446,12 @@
         <v>1917</v>
       </c>
       <c r="B1139" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1140" t="s">
         <v>1919</v>
@@ -15464,28 +15470,28 @@
         <v>1922</v>
       </c>
       <c r="B1142" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1143" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1144" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1145" t="s">
         <v>1926</v>
@@ -15568,12 +15574,12 @@
         <v>1945</v>
       </c>
       <c r="B1155" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B1156" t="s">
         <v>1947</v>
@@ -15616,20 +15622,20 @@
         <v>1956</v>
       </c>
       <c r="B1161" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="B1162" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B1163" t="s">
         <v>1959</v>
@@ -15640,12 +15646,12 @@
         <v>1960</v>
       </c>
       <c r="B1164" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="B1165" t="s">
         <v>1962</v>
@@ -15664,20 +15670,20 @@
         <v>1965</v>
       </c>
       <c r="B1167" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1168" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1169" t="s">
         <v>1968</v>
@@ -15688,36 +15694,36 @@
         <v>1969</v>
       </c>
       <c r="B1170" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B1171" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B1172" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B1173" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B1174" t="s">
         <v>1974</v>
@@ -15736,12 +15742,12 @@
         <v>1977</v>
       </c>
       <c r="B1176" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B1177" t="s">
         <v>1979</v>
@@ -15760,12 +15766,12 @@
         <v>1982</v>
       </c>
       <c r="B1179" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1180" t="s">
         <v>1984</v>
@@ -15779,8 +15785,16 @@
         <v>1986</v>
       </c>
     </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>1988</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1996">
   <si>
     <t>en</t>
   </si>
@@ -2980,6 +2980,9 @@
     <t>Hypixel</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -3001,6 +3004,12 @@
     <t>Hypixel (orodje)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>Hipiksel (dragulj)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -3019,6 +3028,12 @@
     <t>Hipiksel (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>Hypixel (Predmeti za hišne ljubljenčke)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -3029,6 +3044,12 @@
   </si>
   <si>
     <t>Hipiksel (kamen za preoblikovanje)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>Hipiksel (rune)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -6330,7 +6351,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10974,20 +10995,20 @@
         <v>987</v>
       </c>
       <c r="B580" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
+        <v>988</v>
+      </c>
+      <c r="B581" t="s">
         <v>989</v>
-      </c>
-      <c r="B581" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B582" t="s">
         <v>991</v>
@@ -10998,76 +11019,76 @@
         <v>992</v>
       </c>
       <c r="B583" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
+        <v>993</v>
+      </c>
+      <c r="B584" t="s">
         <v>994</v>
-      </c>
-      <c r="B584" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
+        <v>995</v>
+      </c>
+      <c r="B585" t="s">
         <v>996</v>
-      </c>
-      <c r="B585" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
+        <v>997</v>
+      </c>
+      <c r="B586" t="s">
         <v>998</v>
-      </c>
-      <c r="B586" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
+        <v>999</v>
+      </c>
+      <c r="B587" t="s">
         <v>1000</v>
-      </c>
-      <c r="B587" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B588" t="s">
         <v>1002</v>
-      </c>
-      <c r="B588" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B589" t="s">
         <v>1004</v>
-      </c>
-      <c r="B589" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B590" t="s">
         <v>1006</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B591" t="s">
         <v>1008</v>
-      </c>
-      <c r="B591" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B592" t="s">
         <v>1010</v>
@@ -11086,20 +11107,20 @@
         <v>1013</v>
       </c>
       <c r="B594" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B595" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B596" t="s">
         <v>1017</v>
@@ -11118,44 +11139,44 @@
         <v>1020</v>
       </c>
       <c r="B598" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B599" t="s">
         <v>1022</v>
-      </c>
-      <c r="B599" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B600" t="s">
         <v>1024</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B601" t="s">
         <v>1026</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B602" t="s">
         <v>1028</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B603" t="s">
         <v>1030</v>
@@ -11166,36 +11187,36 @@
         <v>1031</v>
       </c>
       <c r="B604" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B605" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B606" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="B607" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B608" t="s">
         <v>1038</v>
@@ -11214,28 +11235,28 @@
         <v>1041</v>
       </c>
       <c r="B610" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B611" t="s">
         <v>1043</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B612" t="s">
         <v>1045</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B613" t="s">
         <v>1047</v>
@@ -11262,12 +11283,12 @@
         <v>1052</v>
       </c>
       <c r="B616" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B617" t="s">
         <v>1054</v>
@@ -11310,20 +11331,20 @@
         <v>1062</v>
       </c>
       <c r="B622" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B623" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B624" t="s">
         <v>1066</v>
@@ -11334,12 +11355,12 @@
         <v>1067</v>
       </c>
       <c r="B625" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B626" t="s">
         <v>1069</v>
@@ -11374,148 +11395,148 @@
         <v>1075</v>
       </c>
       <c r="B630" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B631" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="B632" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="B633" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B634" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="B635" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B636" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B637" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B638" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B639" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B640" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B641" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B642" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B643" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B644" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B645" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B646" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B647" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B648" t="s">
         <v>1101</v>
@@ -11526,12 +11547,12 @@
         <v>1102</v>
       </c>
       <c r="B649" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B650" t="s">
         <v>1104</v>
@@ -11542,44 +11563,44 @@
         <v>1105</v>
       </c>
       <c r="B651" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B652" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B653" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B654" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B655" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B656" t="s">
         <v>1113</v>
@@ -11630,52 +11651,52 @@
         <v>1123</v>
       </c>
       <c r="B662" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B663" t="s">
         <v>1125</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B664" t="s">
         <v>1127</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B665" t="s">
         <v>1129</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B666" t="s">
         <v>1131</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B667" t="s">
         <v>1133</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B668" t="s">
         <v>1135</v>
@@ -11710,60 +11731,60 @@
         <v>1142</v>
       </c>
       <c r="B672" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B673" t="s">
         <v>1144</v>
-      </c>
-      <c r="B673" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B674" t="s">
         <v>1146</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B675" t="s">
         <v>1148</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B676" t="s">
         <v>1150</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B677" t="s">
         <v>1152</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1153</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B678" t="s">
         <v>1154</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B679" t="s">
         <v>1156</v>
@@ -11806,28 +11827,28 @@
         <v>1164</v>
       </c>
       <c r="B684" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B685" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B686" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B687" t="s">
         <v>1170</v>
@@ -11838,60 +11859,60 @@
         <v>1171</v>
       </c>
       <c r="B688" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B689" t="s">
         <v>1173</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B690" t="s">
         <v>1175</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B691" t="s">
         <v>1177</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B692" t="s">
         <v>1179</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B693" t="s">
         <v>1181</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B694" t="s">
         <v>1183</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B695" t="s">
         <v>1185</v>
@@ -11926,20 +11947,20 @@
         <v>1192</v>
       </c>
       <c r="B699" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B700" t="s">
         <v>1194</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B701" t="s">
         <v>1196</v>
@@ -11958,100 +11979,100 @@
         <v>1199</v>
       </c>
       <c r="B703" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B704" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B705" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B706" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B707" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B708" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B709" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B710" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B711" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B712" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B713" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B714" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B715" t="s">
         <v>1217</v>
@@ -12070,36 +12091,36 @@
         <v>1219</v>
       </c>
       <c r="B717" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B718" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B719" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B720" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B721" t="s">
         <v>1226</v>
@@ -12126,12 +12147,12 @@
         <v>1231</v>
       </c>
       <c r="B724" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B725" t="s">
         <v>1233</v>
@@ -12142,68 +12163,68 @@
         <v>1234</v>
       </c>
       <c r="B726" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B727" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B728" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B729" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B730" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B731" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B732" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B733" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B734" t="s">
         <v>1247</v>
@@ -12246,12 +12267,12 @@
         <v>1255</v>
       </c>
       <c r="B739" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B740" t="s">
         <v>1257</v>
@@ -12286,60 +12307,60 @@
         <v>1263</v>
       </c>
       <c r="B744" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B745" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B746" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B747" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B748" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B749" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B750" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B751" t="s">
         <v>1275</v>
@@ -12350,76 +12371,76 @@
         <v>1276</v>
       </c>
       <c r="B752" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B753" t="s">
         <v>1278</v>
-      </c>
-      <c r="B753" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B754" t="s">
         <v>1280</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B755" t="s">
         <v>1282</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B756" t="s">
         <v>1284</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B757" t="s">
         <v>1286</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B758" t="s">
         <v>1288</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B759" t="s">
         <v>1290</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B760" t="s">
         <v>1292</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B761" t="s">
         <v>1294</v>
@@ -12438,36 +12459,36 @@
         <v>1297</v>
       </c>
       <c r="B763" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B764" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B765" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B766" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B767" t="s">
         <v>1304</v>
@@ -12478,20 +12499,20 @@
         <v>1305</v>
       </c>
       <c r="B768" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B769" t="s">
         <v>1307</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B770" t="s">
         <v>1309</v>
@@ -12526,76 +12547,76 @@
         <v>1316</v>
       </c>
       <c r="B774" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B775" t="s">
         <v>1318</v>
-      </c>
-      <c r="B775" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B776" t="s">
         <v>1320</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B777" t="s">
         <v>1322</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B778" t="s">
         <v>1324</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B779" t="s">
         <v>1326</v>
-      </c>
-      <c r="B779" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B780" t="s">
         <v>1328</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B781" t="s">
         <v>1330</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B782" t="s">
         <v>1332</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B783" t="s">
         <v>1334</v>
@@ -12606,52 +12627,52 @@
         <v>1335</v>
       </c>
       <c r="B784" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B785" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B786" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
       <c r="B787" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="B788" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B789" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B790" t="s">
         <v>1344</v>
@@ -12662,100 +12683,100 @@
         <v>1345</v>
       </c>
       <c r="B791" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B792" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="B793" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B794" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="B795" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="B796" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="B797" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="B798" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B799" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B800" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="B801" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B802" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B803" t="s">
         <v>1362</v>
@@ -12766,36 +12787,36 @@
         <v>1363</v>
       </c>
       <c r="B804" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B805" t="s">
         <v>1365</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1366</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B806" t="s">
         <v>1367</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B807" t="s">
         <v>1369</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B808" t="s">
         <v>1371</v>
@@ -12806,36 +12827,36 @@
         <v>1372</v>
       </c>
       <c r="B809" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B810" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="B811" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="B812" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B813" t="s">
         <v>1379</v>
@@ -12846,36 +12867,36 @@
         <v>1380</v>
       </c>
       <c r="B814" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B815" t="s">
         <v>1382</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B816" t="s">
         <v>1384</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B817" t="s">
         <v>1386</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1387</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B818" t="s">
         <v>1388</v>
@@ -12902,12 +12923,12 @@
         <v>1393</v>
       </c>
       <c r="B821" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B822" t="s">
         <v>1395</v>
@@ -12950,108 +12971,108 @@
         <v>1403</v>
       </c>
       <c r="B827" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B828" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B829" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B830" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B831" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B832" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B833" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B834" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="B835" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="B836" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B837" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B838" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B839" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B840" t="s">
         <v>1422</v>
@@ -13070,12 +13091,12 @@
         <v>1425</v>
       </c>
       <c r="B842" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B843" t="s">
         <v>1427</v>
@@ -13086,52 +13107,52 @@
         <v>1428</v>
       </c>
       <c r="B844" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B845" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B846" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B847" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="B848" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B849" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B850" t="s">
         <v>1437</v>
@@ -13142,84 +13163,84 @@
         <v>1438</v>
       </c>
       <c r="B851" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B852" t="s">
         <v>1440</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B853" t="s">
         <v>1442</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B854" t="s">
         <v>1444</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B855" t="s">
         <v>1446</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B856" t="s">
         <v>1448</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1449</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B857" t="s">
         <v>1450</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B858" t="s">
         <v>1452</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1453</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B859" t="s">
         <v>1454</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B860" t="s">
         <v>1456</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B861" t="s">
         <v>1458</v>
@@ -13230,116 +13251,116 @@
         <v>1459</v>
       </c>
       <c r="B862" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B863" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B864" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B865" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B866" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B867" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B868" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="B869" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B870" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B871" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B872" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B873" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B874" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B875" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B876" t="s">
         <v>1478</v>
@@ -13358,28 +13379,28 @@
         <v>1481</v>
       </c>
       <c r="B878" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B879" t="s">
         <v>1483</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1484</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B880" t="s">
         <v>1485</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="B881" t="s">
         <v>1487</v>
@@ -13390,28 +13411,28 @@
         <v>1488</v>
       </c>
       <c r="B882" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B883" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B884" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B885" t="s">
         <v>1494</v>
@@ -13430,84 +13451,84 @@
         <v>1496</v>
       </c>
       <c r="B887" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B888" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B889" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="B890" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B891" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B892" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B893" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B894" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B895" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B896" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B897" t="s">
         <v>1512</v>
@@ -13526,12 +13547,12 @@
         <v>1515</v>
       </c>
       <c r="B899" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B900" t="s">
         <v>1517</v>
@@ -13566,28 +13587,28 @@
         <v>1524</v>
       </c>
       <c r="B904" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B905" t="s">
         <v>1526</v>
-      </c>
-      <c r="B905" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B906" t="s">
         <v>1528</v>
-      </c>
-      <c r="B906" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B907" t="s">
         <v>1530</v>
@@ -13598,68 +13619,68 @@
         <v>1531</v>
       </c>
       <c r="B908" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B909" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B910" t="s">
-        <v>1533</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="B911" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="B912" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="B913" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="B914" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B915" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B916" t="s">
         <v>1542</v>
@@ -13678,36 +13699,36 @@
         <v>1544</v>
       </c>
       <c r="B918" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B919" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B920" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B921" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B922" t="s">
         <v>1551</v>
@@ -13718,20 +13739,20 @@
         <v>1552</v>
       </c>
       <c r="B923" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B924" t="s">
         <v>1554</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1555</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B925" t="s">
         <v>1556</v>
@@ -13742,28 +13763,28 @@
         <v>1557</v>
       </c>
       <c r="B926" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B927" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B928" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B929" t="s">
         <v>1563</v>
@@ -13774,12 +13795,12 @@
         <v>1564</v>
       </c>
       <c r="B930" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B931" t="s">
         <v>1566</v>
@@ -13806,12 +13827,12 @@
         <v>1571</v>
       </c>
       <c r="B934" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B935" t="s">
         <v>1573</v>
@@ -13822,20 +13843,20 @@
         <v>1574</v>
       </c>
       <c r="B936" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B937" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B938" t="s">
         <v>1578</v>
@@ -13854,36 +13875,36 @@
         <v>1581</v>
       </c>
       <c r="B940" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B941" t="s">
         <v>1583</v>
-      </c>
-      <c r="B941" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B942" t="s">
         <v>1585</v>
-      </c>
-      <c r="B942" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B943" t="s">
         <v>1587</v>
-      </c>
-      <c r="B943" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B944" t="s">
         <v>1589</v>
@@ -13894,92 +13915,92 @@
         <v>1590</v>
       </c>
       <c r="B945" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B946" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="B947" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B948" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B949" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B950" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B951" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B952" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="B953" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="B954" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B955" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B956" t="s">
         <v>1606</v>
@@ -13990,20 +14011,20 @@
         <v>1607</v>
       </c>
       <c r="B957" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B958" t="s">
         <v>1609</v>
-      </c>
-      <c r="B958" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B959" t="s">
         <v>1611</v>
@@ -14014,28 +14035,28 @@
         <v>1612</v>
       </c>
       <c r="B960" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B961" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B962" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B963" t="s">
         <v>1618</v>
@@ -14046,12 +14067,12 @@
         <v>1619</v>
       </c>
       <c r="B964" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="B965" t="s">
         <v>1621</v>
@@ -14078,36 +14099,36 @@
         <v>1626</v>
       </c>
       <c r="B968" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B969" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B970" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B971" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B972" t="s">
         <v>1633</v>
@@ -14118,76 +14139,76 @@
         <v>1634</v>
       </c>
       <c r="B973" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B974" t="s">
         <v>1636</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B975" t="s">
         <v>1638</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B976" t="s">
         <v>1640</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1641</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B977" t="s">
         <v>1642</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B978" t="s">
         <v>1644</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B979" t="s">
         <v>1646</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B980" t="s">
         <v>1648</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B981" t="s">
         <v>1650</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1651</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="B982" t="s">
         <v>1652</v>
@@ -14198,84 +14219,84 @@
         <v>1653</v>
       </c>
       <c r="B983" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B984" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B985" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B986" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B987" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B988" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B989" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="B990" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="B991" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B992" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B993" t="s">
         <v>1667</v>
@@ -14294,12 +14315,12 @@
         <v>1670</v>
       </c>
       <c r="B995" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B996" t="s">
         <v>1672</v>
@@ -14326,12 +14347,12 @@
         <v>1677</v>
       </c>
       <c r="B999" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1000" t="s">
         <v>1679</v>
@@ -14358,28 +14379,28 @@
         <v>1684</v>
       </c>
       <c r="B1003" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B1004" t="s">
         <v>1686</v>
-      </c>
-      <c r="B1004" t="s">
-        <v>1687</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1687</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1688</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1689</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B1006" t="s">
         <v>1690</v>
@@ -14390,28 +14411,28 @@
         <v>1691</v>
       </c>
       <c r="B1007" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1008" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1009" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1010" t="s">
         <v>1697</v>
@@ -14430,52 +14451,52 @@
         <v>1699</v>
       </c>
       <c r="B1012" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1013" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B1014" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="B1015" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="B1016" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1017" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1018" t="s">
         <v>1708</v>
@@ -14486,44 +14507,44 @@
         <v>1709</v>
       </c>
       <c r="B1019" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1020" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B1021" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1022" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1023" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1024" t="s">
         <v>1717</v>
@@ -14566,100 +14587,100 @@
         <v>1725</v>
       </c>
       <c r="B1029" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1030" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B1031" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1032" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="B1033" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B1034" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="B1035" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="B1036" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="B1037" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="B1038" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B1039" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1040" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1041" t="s">
         <v>1741</v>
@@ -14710,12 +14731,12 @@
         <v>1751</v>
       </c>
       <c r="B1047" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1048" t="s">
         <v>1753</v>
@@ -14742,100 +14763,100 @@
         <v>1758</v>
       </c>
       <c r="B1051" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B1052" t="s">
         <v>1760</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1761</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B1053" t="s">
         <v>1762</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>1763</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1764</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1765</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1766</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1767</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1768</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1769</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1770</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1772</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1774</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1777</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1778</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="B1063" t="s">
         <v>1782</v>
@@ -14870,76 +14891,76 @@
         <v>1789</v>
       </c>
       <c r="B1067" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1791</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1792</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1793</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1794</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1794</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1795</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1796</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1797</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1798</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1799</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1073" t="s">
         <v>1801</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B1074" t="s">
         <v>1803</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1805</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B1076" t="s">
         <v>1807</v>
@@ -14982,36 +15003,36 @@
         <v>1815</v>
       </c>
       <c r="B1081" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1082" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1083" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B1084" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1085" t="s">
         <v>1822</v>
@@ -15022,12 +15043,12 @@
         <v>1823</v>
       </c>
       <c r="B1086" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1087" t="s">
         <v>1825</v>
@@ -15054,52 +15075,52 @@
         <v>1830</v>
       </c>
       <c r="B1090" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1091" t="s">
         <v>1832</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B1092" t="s">
         <v>1834</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B1093" t="s">
         <v>1836</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1838</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="B1096" t="s">
         <v>1842</v>
@@ -15134,20 +15155,20 @@
         <v>1849</v>
       </c>
       <c r="B1100" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1851</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B1102" t="s">
         <v>1853</v>
@@ -15174,60 +15195,60 @@
         <v>1858</v>
       </c>
       <c r="B1105" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1106" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1107" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1108" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="B1109" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B1110" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1111" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B1112" t="s">
         <v>1869</v>
@@ -15238,28 +15259,28 @@
         <v>1870</v>
       </c>
       <c r="B1113" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1114" t="s">
         <v>1872</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1115" t="s">
         <v>1874</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B1116" t="s">
         <v>1876</v>
@@ -15294,20 +15315,20 @@
         <v>1883</v>
       </c>
       <c r="B1120" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1885</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B1122" t="s">
         <v>1887</v>
@@ -15342,84 +15363,84 @@
         <v>1894</v>
       </c>
       <c r="B1126" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1896</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1898</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1899</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1900</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1901</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1902</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1903</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1904</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1905</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1906</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1907</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1907</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1908</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1909</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1910</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1911</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1912</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1913</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1136" t="s">
         <v>1914</v>
@@ -15430,44 +15451,44 @@
         <v>1915</v>
       </c>
       <c r="B1137" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1138" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="B1139" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="B1140" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="B1141" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1142" t="s">
         <v>1923</v>
@@ -15478,44 +15499,44 @@
         <v>1924</v>
       </c>
       <c r="B1143" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1144" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1145" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B1146" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B1147" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1148" t="s">
         <v>1932</v>
@@ -15526,60 +15547,60 @@
         <v>1933</v>
       </c>
       <c r="B1149" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1150" t="s">
         <v>1935</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>1936</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1151" t="s">
         <v>1937</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>1938</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1152" t="s">
         <v>1939</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>1940</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1153" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>1942</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1942</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1943</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1944</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1945</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1946</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1947</v>
+        <v>1946</v>
       </c>
       <c r="B1156" t="s">
         <v>1947</v>
@@ -15614,20 +15635,20 @@
         <v>1954</v>
       </c>
       <c r="B1160" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1161" t="s">
         <v>1956</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>1957</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B1162" t="s">
         <v>1958</v>
@@ -15638,36 +15659,36 @@
         <v>1959</v>
       </c>
       <c r="B1163" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B1164" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1165" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B1166" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="B1167" t="s">
         <v>1966</v>
@@ -15678,84 +15699,84 @@
         <v>1967</v>
       </c>
       <c r="B1168" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1169" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B1170" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B1171" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="B1172" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B1173" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="B1174" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="B1175" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B1176" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1177" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1178" t="s">
         <v>1981</v>
@@ -15774,12 +15795,12 @@
         <v>1984</v>
       </c>
       <c r="B1180" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1181" t="s">
         <v>1986</v>
@@ -15793,8 +15814,40 @@
         <v>1988</v>
       </c>
     </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>1995</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1998">
   <si>
     <t>en</t>
   </si>
@@ -4481,6 +4481,12 @@
   </si>
   <si>
     <t>Profesor Layton</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Projekt Zomboid</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -6351,7 +6357,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13435,20 +13441,20 @@
         <v>1494</v>
       </c>
       <c r="B885" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B886" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B887" t="s">
         <v>1497</v>
@@ -13475,20 +13481,20 @@
         <v>1502</v>
       </c>
       <c r="B890" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B891" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B892" t="s">
         <v>1505</v>
@@ -13499,12 +13505,12 @@
         <v>1506</v>
       </c>
       <c r="B893" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B894" t="s">
         <v>1508</v>
@@ -13515,12 +13521,12 @@
         <v>1509</v>
       </c>
       <c r="B895" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B896" t="s">
         <v>1511</v>
@@ -13531,12 +13537,12 @@
         <v>1512</v>
       </c>
       <c r="B897" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B898" t="s">
         <v>1514</v>
@@ -13547,12 +13553,12 @@
         <v>1515</v>
       </c>
       <c r="B899" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B900" t="s">
         <v>1517</v>
@@ -13587,12 +13593,12 @@
         <v>1524</v>
       </c>
       <c r="B904" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B905" t="s">
         <v>1526</v>
@@ -13643,60 +13649,60 @@
         <v>1537</v>
       </c>
       <c r="B911" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B912" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B913" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B914" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B915" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B916" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B917" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B918" t="s">
         <v>1545</v>
@@ -13723,28 +13729,28 @@
         <v>1550</v>
       </c>
       <c r="B921" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B922" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B923" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B924" t="s">
         <v>1554</v>
@@ -13787,20 +13793,20 @@
         <v>1563</v>
       </c>
       <c r="B929" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B930" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B931" t="s">
         <v>1566</v>
@@ -13835,12 +13841,12 @@
         <v>1573</v>
       </c>
       <c r="B935" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B936" t="s">
         <v>1575</v>
@@ -13859,12 +13865,12 @@
         <v>1578</v>
       </c>
       <c r="B938" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B939" t="s">
         <v>1580</v>
@@ -13875,12 +13881,12 @@
         <v>1581</v>
       </c>
       <c r="B940" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B941" t="s">
         <v>1583</v>
@@ -13939,28 +13945,28 @@
         <v>1596</v>
       </c>
       <c r="B948" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B949" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B950" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B951" t="s">
         <v>1600</v>
@@ -13979,44 +13985,44 @@
         <v>1603</v>
       </c>
       <c r="B953" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B954" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B955" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B956" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B957" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B958" t="s">
         <v>1609</v>
@@ -14059,20 +14065,20 @@
         <v>1618</v>
       </c>
       <c r="B963" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B964" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B965" t="s">
         <v>1621</v>
@@ -14107,12 +14113,12 @@
         <v>1628</v>
       </c>
       <c r="B969" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B970" t="s">
         <v>1630</v>
@@ -14131,20 +14137,20 @@
         <v>1633</v>
       </c>
       <c r="B972" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B973" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B974" t="s">
         <v>1636</v>
@@ -14243,28 +14249,28 @@
         <v>1659</v>
       </c>
       <c r="B986" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B987" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B988" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B989" t="s">
         <v>1663</v>
@@ -14275,36 +14281,36 @@
         <v>1664</v>
       </c>
       <c r="B990" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B991" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B992" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B993" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B994" t="s">
         <v>1669</v>
@@ -14315,12 +14321,12 @@
         <v>1670</v>
       </c>
       <c r="B995" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B996" t="s">
         <v>1672</v>
@@ -14355,12 +14361,12 @@
         <v>1679</v>
       </c>
       <c r="B1000" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1001" t="s">
         <v>1681</v>
@@ -14379,12 +14385,12 @@
         <v>1684</v>
       </c>
       <c r="B1003" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1004" t="s">
         <v>1686</v>
@@ -14435,20 +14441,20 @@
         <v>1697</v>
       </c>
       <c r="B1010" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1011" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1012" t="s">
         <v>1700</v>
@@ -14475,36 +14481,36 @@
         <v>1705</v>
       </c>
       <c r="B1015" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1016" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1017" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1018" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1019" t="s">
         <v>1710</v>
@@ -14523,12 +14529,12 @@
         <v>1713</v>
       </c>
       <c r="B1021" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1022" t="s">
         <v>1715</v>
@@ -14539,20 +14545,20 @@
         <v>1716</v>
       </c>
       <c r="B1023" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1024" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1025" t="s">
         <v>1719</v>
@@ -14571,12 +14577,12 @@
         <v>1722</v>
       </c>
       <c r="B1027" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1028" t="s">
         <v>1724</v>
@@ -14603,12 +14609,12 @@
         <v>1729</v>
       </c>
       <c r="B1031" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1032" t="s">
         <v>1731</v>
@@ -14619,20 +14625,20 @@
         <v>1732</v>
       </c>
       <c r="B1033" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1034" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1035" t="s">
         <v>1735</v>
@@ -14643,52 +14649,52 @@
         <v>1736</v>
       </c>
       <c r="B1036" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1037" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1038" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1039" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1040" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1041" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1042" t="s">
         <v>1743</v>
@@ -14707,12 +14713,12 @@
         <v>1746</v>
       </c>
       <c r="B1044" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1045" t="s">
         <v>1748</v>
@@ -14739,12 +14745,12 @@
         <v>1753</v>
       </c>
       <c r="B1048" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1049" t="s">
         <v>1755</v>
@@ -14763,12 +14769,12 @@
         <v>1758</v>
       </c>
       <c r="B1051" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1052" t="s">
         <v>1760</v>
@@ -14891,12 +14897,12 @@
         <v>1789</v>
       </c>
       <c r="B1067" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1068" t="s">
         <v>1791</v>
@@ -14995,12 +15001,12 @@
         <v>1814</v>
       </c>
       <c r="B1080" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1081" t="s">
         <v>1816</v>
@@ -15027,20 +15033,20 @@
         <v>1821</v>
       </c>
       <c r="B1084" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1085" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1086" t="s">
         <v>1824</v>
@@ -15051,12 +15057,12 @@
         <v>1825</v>
       </c>
       <c r="B1087" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1088" t="s">
         <v>1827</v>
@@ -15075,12 +15081,12 @@
         <v>1830</v>
       </c>
       <c r="B1090" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1091" t="s">
         <v>1832</v>
@@ -15155,12 +15161,12 @@
         <v>1849</v>
       </c>
       <c r="B1100" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1101" t="s">
         <v>1851</v>
@@ -15203,12 +15209,12 @@
         <v>1860</v>
       </c>
       <c r="B1106" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1107" t="s">
         <v>1862</v>
@@ -15227,20 +15233,20 @@
         <v>1865</v>
       </c>
       <c r="B1109" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1110" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1111" t="s">
         <v>1868</v>
@@ -15251,20 +15257,20 @@
         <v>1869</v>
       </c>
       <c r="B1112" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1113" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1114" t="s">
         <v>1872</v>
@@ -15315,12 +15321,12 @@
         <v>1883</v>
       </c>
       <c r="B1120" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B1121" t="s">
         <v>1885</v>
@@ -15363,12 +15369,12 @@
         <v>1894</v>
       </c>
       <c r="B1126" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1127" t="s">
         <v>1896</v>
@@ -15475,28 +15481,28 @@
         <v>1921</v>
       </c>
       <c r="B1140" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1141" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1142" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1143" t="s">
         <v>1925</v>
@@ -15507,12 +15513,12 @@
         <v>1926</v>
       </c>
       <c r="B1144" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1145" t="s">
         <v>1928</v>
@@ -15531,28 +15537,28 @@
         <v>1931</v>
       </c>
       <c r="B1147" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1148" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1149" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1150" t="s">
         <v>1935</v>
@@ -15635,12 +15641,12 @@
         <v>1954</v>
       </c>
       <c r="B1160" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="B1161" t="s">
         <v>1956</v>
@@ -15683,20 +15689,20 @@
         <v>1965</v>
       </c>
       <c r="B1166" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1167" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="B1168" t="s">
         <v>1968</v>
@@ -15707,12 +15713,12 @@
         <v>1969</v>
       </c>
       <c r="B1169" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B1170" t="s">
         <v>1971</v>
@@ -15731,20 +15737,20 @@
         <v>1974</v>
       </c>
       <c r="B1172" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1173" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1174" t="s">
         <v>1977</v>
@@ -15755,36 +15761,36 @@
         <v>1978</v>
       </c>
       <c r="B1175" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1176" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1177" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1178" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1179" t="s">
         <v>1983</v>
@@ -15803,12 +15809,12 @@
         <v>1986</v>
       </c>
       <c r="B1181" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1182" t="s">
         <v>1988</v>
@@ -15827,12 +15833,12 @@
         <v>1991</v>
       </c>
       <c r="B1184" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1185" t="s">
         <v>1993</v>
@@ -15846,8 +15852,16 @@
         <v>1995</v>
       </c>
     </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>1997</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1999">
   <si>
     <t>en</t>
   </si>
@@ -356,6 +356,9 @@
   </si>
   <si>
     <t>Baka in test</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -6357,7 +6360,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6913,20 +6916,20 @@
         <v>113</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
+        <v>114</v>
+      </c>
+      <c r="B70" t="s">
         <v>115</v>
-      </c>
-      <c r="B70" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B71" t="s">
         <v>117</v>
@@ -6961,12 +6964,12 @@
         <v>121</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B76" t="s">
         <v>123</v>
@@ -6977,20 +6980,20 @@
         <v>124</v>
       </c>
       <c r="B77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>125</v>
+      </c>
+      <c r="B78" t="s">
         <v>126</v>
-      </c>
-      <c r="B78" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B79" t="s">
         <v>128</v>
@@ -7001,12 +7004,12 @@
         <v>129</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B81" t="s">
         <v>131</v>
@@ -7017,28 +7020,28 @@
         <v>132</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
+        <v>133</v>
+      </c>
+      <c r="B83" t="s">
         <v>134</v>
-      </c>
-      <c r="B83" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
+        <v>135</v>
+      </c>
+      <c r="B84" t="s">
         <v>136</v>
-      </c>
-      <c r="B84" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
@@ -7049,36 +7052,36 @@
         <v>139</v>
       </c>
       <c r="B86" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
+        <v>140</v>
+      </c>
+      <c r="B87" t="s">
         <v>141</v>
-      </c>
-      <c r="B87" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
+        <v>142</v>
+      </c>
+      <c r="B88" t="s">
         <v>143</v>
-      </c>
-      <c r="B88" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>144</v>
+      </c>
+      <c r="B89" t="s">
         <v>145</v>
-      </c>
-      <c r="B89" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B90" t="s">
         <v>147</v>
@@ -7097,20 +7100,20 @@
         <v>149</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
+        <v>150</v>
+      </c>
+      <c r="B93" t="s">
         <v>151</v>
-      </c>
-      <c r="B93" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B94" t="s">
         <v>153</v>
@@ -7121,12 +7124,12 @@
         <v>154</v>
       </c>
       <c r="B95" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B96" t="s">
         <v>156</v>
@@ -7153,44 +7156,44 @@
         <v>159</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
+        <v>160</v>
+      </c>
+      <c r="B100" t="s">
         <v>161</v>
-      </c>
-      <c r="B100" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
+        <v>162</v>
+      </c>
+      <c r="B101" t="s">
         <v>163</v>
-      </c>
-      <c r="B101" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
+        <v>164</v>
+      </c>
+      <c r="B102" t="s">
         <v>165</v>
-      </c>
-      <c r="B102" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
+        <v>166</v>
+      </c>
+      <c r="B103" t="s">
         <v>167</v>
-      </c>
-      <c r="B103" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B104" t="s">
         <v>169</v>
@@ -7209,12 +7212,12 @@
         <v>171</v>
       </c>
       <c r="B106" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B107" t="s">
         <v>173</v>
@@ -7225,28 +7228,28 @@
         <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>175</v>
+      </c>
+      <c r="B109" t="s">
         <v>176</v>
-      </c>
-      <c r="B109" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>177</v>
+      </c>
+      <c r="B110" t="s">
         <v>178</v>
-      </c>
-      <c r="B110" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B111" t="s">
         <v>180</v>
@@ -7265,20 +7268,20 @@
         <v>182</v>
       </c>
       <c r="B113" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
+        <v>183</v>
+      </c>
+      <c r="B114" t="s">
         <v>184</v>
-      </c>
-      <c r="B114" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
         <v>186</v>
@@ -7289,36 +7292,36 @@
         <v>187</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>188</v>
+      </c>
+      <c r="B117" t="s">
         <v>189</v>
-      </c>
-      <c r="B117" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>190</v>
+      </c>
+      <c r="B118" t="s">
         <v>191</v>
-      </c>
-      <c r="B118" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>192</v>
+      </c>
+      <c r="B119" t="s">
         <v>193</v>
-      </c>
-      <c r="B119" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B120" t="s">
         <v>195</v>
@@ -7353,12 +7356,12 @@
         <v>199</v>
       </c>
       <c r="B124" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B125" t="s">
         <v>201</v>
@@ -7369,36 +7372,36 @@
         <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" t="s">
         <v>204</v>
-      </c>
-      <c r="B127" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>205</v>
+      </c>
+      <c r="B128" t="s">
         <v>206</v>
-      </c>
-      <c r="B128" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>207</v>
+      </c>
+      <c r="B129" t="s">
         <v>208</v>
-      </c>
-      <c r="B129" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B130" t="s">
         <v>210</v>
@@ -7433,28 +7436,28 @@
         <v>214</v>
       </c>
       <c r="B134" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>215</v>
+      </c>
+      <c r="B135" t="s">
         <v>216</v>
-      </c>
-      <c r="B135" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>217</v>
+      </c>
+      <c r="B136" t="s">
         <v>218</v>
-      </c>
-      <c r="B136" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B137" t="s">
         <v>220</v>
@@ -7465,52 +7468,52 @@
         <v>221</v>
       </c>
       <c r="B138" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>222</v>
+      </c>
+      <c r="B139" t="s">
         <v>223</v>
-      </c>
-      <c r="B139" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
+        <v>224</v>
+      </c>
+      <c r="B140" t="s">
         <v>225</v>
-      </c>
-      <c r="B140" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
+        <v>226</v>
+      </c>
+      <c r="B141" t="s">
         <v>227</v>
-      </c>
-      <c r="B141" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
+        <v>228</v>
+      </c>
+      <c r="B142" t="s">
         <v>229</v>
-      </c>
-      <c r="B142" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
+        <v>230</v>
+      </c>
+      <c r="B143" t="s">
         <v>231</v>
-      </c>
-      <c r="B143" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B144" t="s">
         <v>233</v>
@@ -7521,36 +7524,36 @@
         <v>234</v>
       </c>
       <c r="B145" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
+        <v>235</v>
+      </c>
+      <c r="B146" t="s">
         <v>236</v>
-      </c>
-      <c r="B146" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
+        <v>237</v>
+      </c>
+      <c r="B147" t="s">
         <v>238</v>
-      </c>
-      <c r="B147" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>239</v>
+      </c>
+      <c r="B148" t="s">
         <v>240</v>
-      </c>
-      <c r="B148" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B149" t="s">
         <v>242</v>
@@ -7561,12 +7564,12 @@
         <v>243</v>
       </c>
       <c r="B150" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B151" t="s">
         <v>245</v>
@@ -7585,52 +7588,52 @@
         <v>247</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>248</v>
+      </c>
+      <c r="B154" t="s">
         <v>249</v>
-      </c>
-      <c r="B154" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>250</v>
+      </c>
+      <c r="B155" t="s">
         <v>251</v>
-      </c>
-      <c r="B155" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>252</v>
+      </c>
+      <c r="B156" t="s">
         <v>253</v>
-      </c>
-      <c r="B156" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>254</v>
+      </c>
+      <c r="B157" t="s">
         <v>255</v>
-      </c>
-      <c r="B157" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>256</v>
+      </c>
+      <c r="B158" t="s">
         <v>257</v>
-      </c>
-      <c r="B158" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B159" t="s">
         <v>259</v>
@@ -7641,71 +7644,71 @@
         <v>260</v>
       </c>
       <c r="B160" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>261</v>
+      </c>
+      <c r="B161" t="s">
         <v>262</v>
-      </c>
-      <c r="B161" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>263</v>
+      </c>
+      <c r="B162" t="s">
         <v>264</v>
-      </c>
-      <c r="B162" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>265</v>
+      </c>
+      <c r="B163" t="s">
         <v>266</v>
-      </c>
-      <c r="B163" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>267</v>
+      </c>
+      <c r="B164" t="s">
         <v>268</v>
-      </c>
-      <c r="B164" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>269</v>
+      </c>
+      <c r="B165" t="s">
         <v>270</v>
-      </c>
-      <c r="B165" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
+        <v>271</v>
+      </c>
+      <c r="B166" t="s">
         <v>272</v>
-      </c>
-      <c r="B166" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
+        <v>273</v>
+      </c>
+      <c r="B167" t="s">
         <v>274</v>
-      </c>
-      <c r="B167" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>275</v>
+      </c>
+      <c r="B168" t="s">
         <v>276</v>
-      </c>
-      <c r="B168" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -7713,20 +7716,20 @@
         <v>277</v>
       </c>
       <c r="B169" t="s">
-        <v>278</v>
+        <v>225</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>278</v>
+      </c>
+      <c r="B170" t="s">
         <v>279</v>
-      </c>
-      <c r="B170" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B171" t="s">
         <v>281</v>
@@ -7737,36 +7740,36 @@
         <v>282</v>
       </c>
       <c r="B172" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>283</v>
+      </c>
+      <c r="B173" t="s">
         <v>284</v>
-      </c>
-      <c r="B173" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
+        <v>285</v>
+      </c>
+      <c r="B174" t="s">
         <v>286</v>
-      </c>
-      <c r="B174" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
+        <v>287</v>
+      </c>
+      <c r="B175" t="s">
         <v>288</v>
-      </c>
-      <c r="B175" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B176" t="s">
         <v>290</v>
@@ -7793,212 +7796,212 @@
         <v>293</v>
       </c>
       <c r="B179" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
+        <v>294</v>
+      </c>
+      <c r="B180" t="s">
         <v>295</v>
-      </c>
-      <c r="B180" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
+        <v>296</v>
+      </c>
+      <c r="B181" t="s">
         <v>297</v>
-      </c>
-      <c r="B181" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
+        <v>298</v>
+      </c>
+      <c r="B182" t="s">
         <v>299</v>
-      </c>
-      <c r="B182" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
+        <v>300</v>
+      </c>
+      <c r="B183" t="s">
         <v>301</v>
-      </c>
-      <c r="B183" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
+        <v>302</v>
+      </c>
+      <c r="B184" t="s">
         <v>303</v>
-      </c>
-      <c r="B184" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
+        <v>304</v>
+      </c>
+      <c r="B185" t="s">
         <v>305</v>
-      </c>
-      <c r="B185" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
+        <v>306</v>
+      </c>
+      <c r="B186" t="s">
         <v>307</v>
-      </c>
-      <c r="B186" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
+        <v>308</v>
+      </c>
+      <c r="B187" t="s">
         <v>309</v>
-      </c>
-      <c r="B187" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
+        <v>310</v>
+      </c>
+      <c r="B188" t="s">
         <v>311</v>
-      </c>
-      <c r="B188" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
+        <v>312</v>
+      </c>
+      <c r="B189" t="s">
         <v>313</v>
-      </c>
-      <c r="B189" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
+        <v>314</v>
+      </c>
+      <c r="B190" t="s">
         <v>315</v>
-      </c>
-      <c r="B190" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
+        <v>316</v>
+      </c>
+      <c r="B191" t="s">
         <v>317</v>
-      </c>
-      <c r="B191" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
+        <v>318</v>
+      </c>
+      <c r="B192" t="s">
         <v>319</v>
-      </c>
-      <c r="B192" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
+        <v>320</v>
+      </c>
+      <c r="B193" t="s">
         <v>321</v>
-      </c>
-      <c r="B193" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
+        <v>322</v>
+      </c>
+      <c r="B194" t="s">
         <v>323</v>
-      </c>
-      <c r="B194" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
+        <v>324</v>
+      </c>
+      <c r="B195" t="s">
         <v>325</v>
-      </c>
-      <c r="B195" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
+        <v>326</v>
+      </c>
+      <c r="B196" t="s">
         <v>327</v>
-      </c>
-      <c r="B196" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
+        <v>328</v>
+      </c>
+      <c r="B197" t="s">
         <v>329</v>
-      </c>
-      <c r="B197" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
+        <v>330</v>
+      </c>
+      <c r="B198" t="s">
         <v>331</v>
-      </c>
-      <c r="B198" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
+        <v>332</v>
+      </c>
+      <c r="B199" t="s">
         <v>333</v>
-      </c>
-      <c r="B199" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
+        <v>334</v>
+      </c>
+      <c r="B200" t="s">
         <v>335</v>
-      </c>
-      <c r="B200" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
+        <v>336</v>
+      </c>
+      <c r="B201" t="s">
         <v>337</v>
-      </c>
-      <c r="B201" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
+        <v>338</v>
+      </c>
+      <c r="B202" t="s">
         <v>339</v>
-      </c>
-      <c r="B202" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
+        <v>340</v>
+      </c>
+      <c r="B203" t="s">
         <v>341</v>
-      </c>
-      <c r="B203" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
+        <v>342</v>
+      </c>
+      <c r="B204" t="s">
         <v>343</v>
-      </c>
-      <c r="B204" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B205" t="s">
         <v>345</v>
@@ -8009,20 +8012,20 @@
         <v>346</v>
       </c>
       <c r="B206" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
+        <v>347</v>
+      </c>
+      <c r="B207" t="s">
         <v>348</v>
-      </c>
-      <c r="B207" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B208" t="s">
         <v>350</v>
@@ -8041,44 +8044,44 @@
         <v>352</v>
       </c>
       <c r="B210" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
+        <v>353</v>
+      </c>
+      <c r="B211" t="s">
         <v>354</v>
-      </c>
-      <c r="B211" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
+        <v>355</v>
+      </c>
+      <c r="B212" t="s">
         <v>356</v>
-      </c>
-      <c r="B212" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
+        <v>357</v>
+      </c>
+      <c r="B213" t="s">
         <v>358</v>
-      </c>
-      <c r="B213" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
+        <v>359</v>
+      </c>
+      <c r="B214" t="s">
         <v>360</v>
-      </c>
-      <c r="B214" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B215" t="s">
         <v>362</v>
@@ -8089,20 +8092,20 @@
         <v>363</v>
       </c>
       <c r="B216" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
+        <v>364</v>
+      </c>
+      <c r="B217" t="s">
         <v>365</v>
-      </c>
-      <c r="B217" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B218" t="s">
         <v>367</v>
@@ -8113,12 +8116,12 @@
         <v>368</v>
       </c>
       <c r="B219" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B220" t="s">
         <v>370</v>
@@ -8129,12 +8132,12 @@
         <v>371</v>
       </c>
       <c r="B221" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B222" t="s">
         <v>373</v>
@@ -8153,28 +8156,28 @@
         <v>375</v>
       </c>
       <c r="B224" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
+        <v>376</v>
+      </c>
+      <c r="B225" t="s">
         <v>377</v>
-      </c>
-      <c r="B225" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
+        <v>378</v>
+      </c>
+      <c r="B226" t="s">
         <v>379</v>
-      </c>
-      <c r="B226" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B227" t="s">
         <v>381</v>
@@ -8193,20 +8196,20 @@
         <v>383</v>
       </c>
       <c r="B229" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
+        <v>384</v>
+      </c>
+      <c r="B230" t="s">
         <v>385</v>
-      </c>
-      <c r="B230" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B231" t="s">
         <v>387</v>
@@ -8225,20 +8228,20 @@
         <v>389</v>
       </c>
       <c r="B233" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
+        <v>390</v>
+      </c>
+      <c r="B234" t="s">
         <v>391</v>
-      </c>
-      <c r="B234" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B235" t="s">
         <v>393</v>
@@ -8257,44 +8260,44 @@
         <v>395</v>
       </c>
       <c r="B237" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
+        <v>396</v>
+      </c>
+      <c r="B238" t="s">
         <v>397</v>
-      </c>
-      <c r="B238" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
+        <v>398</v>
+      </c>
+      <c r="B239" t="s">
         <v>399</v>
-      </c>
-      <c r="B239" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
+        <v>400</v>
+      </c>
+      <c r="B240" t="s">
         <v>401</v>
-      </c>
-      <c r="B240" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
+        <v>402</v>
+      </c>
+      <c r="B241" t="s">
         <v>403</v>
-      </c>
-      <c r="B241" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B242" t="s">
         <v>405</v>
@@ -8329,28 +8332,28 @@
         <v>409</v>
       </c>
       <c r="B246" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
+        <v>410</v>
+      </c>
+      <c r="B247" t="s">
         <v>411</v>
-      </c>
-      <c r="B247" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
+        <v>412</v>
+      </c>
+      <c r="B248" t="s">
         <v>413</v>
-      </c>
-      <c r="B248" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B249" t="s">
         <v>415</v>
@@ -8361,12 +8364,12 @@
         <v>416</v>
       </c>
       <c r="B250" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B251" t="s">
         <v>418</v>
@@ -8377,12 +8380,12 @@
         <v>419</v>
       </c>
       <c r="B252" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B253" t="s">
         <v>421</v>
@@ -8401,12 +8404,12 @@
         <v>423</v>
       </c>
       <c r="B255" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B256" t="s">
         <v>425</v>
@@ -8417,68 +8420,68 @@
         <v>426</v>
       </c>
       <c r="B257" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
+        <v>427</v>
+      </c>
+      <c r="B258" t="s">
         <v>428</v>
-      </c>
-      <c r="B258" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
+        <v>429</v>
+      </c>
+      <c r="B259" t="s">
         <v>430</v>
-      </c>
-      <c r="B259" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
+        <v>431</v>
+      </c>
+      <c r="B260" t="s">
         <v>432</v>
-      </c>
-      <c r="B260" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
+        <v>433</v>
+      </c>
+      <c r="B261" t="s">
         <v>434</v>
-      </c>
-      <c r="B261" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
+        <v>435</v>
+      </c>
+      <c r="B262" t="s">
         <v>436</v>
-      </c>
-      <c r="B262" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
+        <v>437</v>
+      </c>
+      <c r="B263" t="s">
         <v>438</v>
-      </c>
-      <c r="B263" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
+        <v>439</v>
+      </c>
+      <c r="B264" t="s">
         <v>440</v>
-      </c>
-      <c r="B264" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B265" t="s">
         <v>442</v>
@@ -8497,20 +8500,20 @@
         <v>444</v>
       </c>
       <c r="B267" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
+        <v>445</v>
+      </c>
+      <c r="B268" t="s">
         <v>446</v>
-      </c>
-      <c r="B268" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B269" t="s">
         <v>448</v>
@@ -8553,12 +8556,12 @@
         <v>453</v>
       </c>
       <c r="B274" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B275" t="s">
         <v>455</v>
@@ -8577,44 +8580,44 @@
         <v>457</v>
       </c>
       <c r="B277" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
+        <v>458</v>
+      </c>
+      <c r="B278" t="s">
         <v>459</v>
-      </c>
-      <c r="B278" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
+        <v>460</v>
+      </c>
+      <c r="B279" t="s">
         <v>461</v>
-      </c>
-      <c r="B279" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
+        <v>462</v>
+      </c>
+      <c r="B280" t="s">
         <v>463</v>
-      </c>
-      <c r="B280" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
+        <v>464</v>
+      </c>
+      <c r="B281" t="s">
         <v>465</v>
-      </c>
-      <c r="B281" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B282" t="s">
         <v>467</v>
@@ -8633,12 +8636,12 @@
         <v>469</v>
       </c>
       <c r="B284" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B285" t="s">
         <v>471</v>
@@ -8657,28 +8660,28 @@
         <v>473</v>
       </c>
       <c r="B287" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
+        <v>474</v>
+      </c>
+      <c r="B288" t="s">
         <v>475</v>
-      </c>
-      <c r="B288" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
+        <v>476</v>
+      </c>
+      <c r="B289" t="s">
         <v>477</v>
-      </c>
-      <c r="B289" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B290" t="s">
         <v>479</v>
@@ -8689,36 +8692,36 @@
         <v>480</v>
       </c>
       <c r="B291" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
+        <v>481</v>
+      </c>
+      <c r="B292" t="s">
         <v>482</v>
-      </c>
-      <c r="B292" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
+        <v>483</v>
+      </c>
+      <c r="B293" t="s">
         <v>484</v>
-      </c>
-      <c r="B293" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
+        <v>485</v>
+      </c>
+      <c r="B294" t="s">
         <v>486</v>
-      </c>
-      <c r="B294" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B295" t="s">
         <v>488</v>
@@ -8737,28 +8740,28 @@
         <v>490</v>
       </c>
       <c r="B297" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
+        <v>491</v>
+      </c>
+      <c r="B298" t="s">
         <v>492</v>
-      </c>
-      <c r="B298" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
+        <v>493</v>
+      </c>
+      <c r="B299" t="s">
         <v>494</v>
-      </c>
-      <c r="B299" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B300" t="s">
         <v>496</v>
@@ -8777,12 +8780,12 @@
         <v>498</v>
       </c>
       <c r="B302" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B303" t="s">
         <v>500</v>
@@ -8793,44 +8796,44 @@
         <v>501</v>
       </c>
       <c r="B304" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
+        <v>502</v>
+      </c>
+      <c r="B305" t="s">
         <v>503</v>
-      </c>
-      <c r="B305" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
+        <v>504</v>
+      </c>
+      <c r="B306" t="s">
         <v>505</v>
-      </c>
-      <c r="B306" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
+        <v>506</v>
+      </c>
+      <c r="B307" t="s">
         <v>507</v>
-      </c>
-      <c r="B307" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
+        <v>508</v>
+      </c>
+      <c r="B308" t="s">
         <v>509</v>
-      </c>
-      <c r="B308" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B309" t="s">
         <v>511</v>
@@ -8849,20 +8852,20 @@
         <v>513</v>
       </c>
       <c r="B311" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
+        <v>514</v>
+      </c>
+      <c r="B312" t="s">
         <v>515</v>
-      </c>
-      <c r="B312" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B313" t="s">
         <v>517</v>
@@ -8881,12 +8884,12 @@
         <v>519</v>
       </c>
       <c r="B315" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B316" t="s">
         <v>521</v>
@@ -8905,12 +8908,12 @@
         <v>523</v>
       </c>
       <c r="B318" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B319" t="s">
         <v>525</v>
@@ -8945,20 +8948,20 @@
         <v>529</v>
       </c>
       <c r="B323" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
+        <v>530</v>
+      </c>
+      <c r="B324" t="s">
         <v>531</v>
-      </c>
-      <c r="B324" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B325" t="s">
         <v>533</v>
@@ -8977,36 +8980,36 @@
         <v>535</v>
       </c>
       <c r="B327" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
+        <v>536</v>
+      </c>
+      <c r="B328" t="s">
         <v>537</v>
-      </c>
-      <c r="B328" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
+        <v>538</v>
+      </c>
+      <c r="B329" t="s">
         <v>539</v>
-      </c>
-      <c r="B329" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
+        <v>540</v>
+      </c>
+      <c r="B330" t="s">
         <v>541</v>
-      </c>
-      <c r="B330" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B331" t="s">
         <v>543</v>
@@ -9017,68 +9020,68 @@
         <v>544</v>
       </c>
       <c r="B332" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
+        <v>545</v>
+      </c>
+      <c r="B333" t="s">
         <v>546</v>
-      </c>
-      <c r="B333" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
+        <v>547</v>
+      </c>
+      <c r="B334" t="s">
         <v>548</v>
-      </c>
-      <c r="B334" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
+        <v>549</v>
+      </c>
+      <c r="B335" t="s">
         <v>550</v>
-      </c>
-      <c r="B335" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
+        <v>551</v>
+      </c>
+      <c r="B336" t="s">
         <v>552</v>
-      </c>
-      <c r="B336" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
+        <v>553</v>
+      </c>
+      <c r="B337" t="s">
         <v>554</v>
-      </c>
-      <c r="B337" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
+        <v>555</v>
+      </c>
+      <c r="B338" t="s">
         <v>556</v>
-      </c>
-      <c r="B338" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
+        <v>557</v>
+      </c>
+      <c r="B339" t="s">
         <v>558</v>
-      </c>
-      <c r="B339" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B340" t="s">
         <v>560</v>
@@ -9089,20 +9092,20 @@
         <v>561</v>
       </c>
       <c r="B341" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
+        <v>562</v>
+      </c>
+      <c r="B342" t="s">
         <v>563</v>
-      </c>
-      <c r="B342" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B343" t="s">
         <v>565</v>
@@ -9113,164 +9116,164 @@
         <v>566</v>
       </c>
       <c r="B344" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
+        <v>567</v>
+      </c>
+      <c r="B345" t="s">
         <v>568</v>
-      </c>
-      <c r="B345" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
+        <v>569</v>
+      </c>
+      <c r="B346" t="s">
         <v>570</v>
-      </c>
-      <c r="B346" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
+        <v>571</v>
+      </c>
+      <c r="B347" t="s">
         <v>572</v>
-      </c>
-      <c r="B347" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
+        <v>573</v>
+      </c>
+      <c r="B348" t="s">
         <v>574</v>
-      </c>
-      <c r="B348" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
+        <v>575</v>
+      </c>
+      <c r="B349" t="s">
         <v>576</v>
-      </c>
-      <c r="B349" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>577</v>
+      </c>
+      <c r="B350" t="s">
         <v>578</v>
-      </c>
-      <c r="B350" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>579</v>
+      </c>
+      <c r="B351" t="s">
         <v>580</v>
-      </c>
-      <c r="B351" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>581</v>
+      </c>
+      <c r="B352" t="s">
         <v>582</v>
-      </c>
-      <c r="B352" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>583</v>
+      </c>
+      <c r="B353" t="s">
         <v>584</v>
-      </c>
-      <c r="B353" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>585</v>
+      </c>
+      <c r="B354" t="s">
         <v>586</v>
-      </c>
-      <c r="B354" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>587</v>
+      </c>
+      <c r="B355" t="s">
         <v>588</v>
-      </c>
-      <c r="B355" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>589</v>
+      </c>
+      <c r="B356" t="s">
         <v>590</v>
-      </c>
-      <c r="B356" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>591</v>
+      </c>
+      <c r="B357" t="s">
         <v>592</v>
-      </c>
-      <c r="B357" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>593</v>
+      </c>
+      <c r="B358" t="s">
         <v>594</v>
-      </c>
-      <c r="B358" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
+        <v>595</v>
+      </c>
+      <c r="B359" t="s">
         <v>596</v>
-      </c>
-      <c r="B359" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
+        <v>597</v>
+      </c>
+      <c r="B360" t="s">
         <v>598</v>
-      </c>
-      <c r="B360" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
+        <v>599</v>
+      </c>
+      <c r="B361" t="s">
         <v>600</v>
-      </c>
-      <c r="B361" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
+        <v>601</v>
+      </c>
+      <c r="B362" t="s">
         <v>602</v>
-      </c>
-      <c r="B362" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
+        <v>603</v>
+      </c>
+      <c r="B363" t="s">
         <v>604</v>
-      </c>
-      <c r="B363" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B364" t="s">
         <v>606</v>
@@ -9281,532 +9284,532 @@
         <v>607</v>
       </c>
       <c r="B365" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
+        <v>608</v>
+      </c>
+      <c r="B366" t="s">
         <v>609</v>
-      </c>
-      <c r="B366" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
+        <v>610</v>
+      </c>
+      <c r="B367" t="s">
         <v>611</v>
-      </c>
-      <c r="B367" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
+        <v>612</v>
+      </c>
+      <c r="B368" t="s">
         <v>613</v>
-      </c>
-      <c r="B368" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
+        <v>614</v>
+      </c>
+      <c r="B369" t="s">
         <v>615</v>
-      </c>
-      <c r="B369" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
+        <v>616</v>
+      </c>
+      <c r="B370" t="s">
         <v>617</v>
-      </c>
-      <c r="B370" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>618</v>
+      </c>
+      <c r="B371" t="s">
         <v>619</v>
-      </c>
-      <c r="B371" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
+        <v>620</v>
+      </c>
+      <c r="B372" t="s">
         <v>621</v>
-      </c>
-      <c r="B372" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>622</v>
+      </c>
+      <c r="B373" t="s">
         <v>623</v>
-      </c>
-      <c r="B373" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
+        <v>624</v>
+      </c>
+      <c r="B374" t="s">
         <v>625</v>
-      </c>
-      <c r="B374" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
+        <v>626</v>
+      </c>
+      <c r="B375" t="s">
         <v>627</v>
-      </c>
-      <c r="B375" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
+        <v>628</v>
+      </c>
+      <c r="B376" t="s">
         <v>629</v>
-      </c>
-      <c r="B376" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
+        <v>630</v>
+      </c>
+      <c r="B377" t="s">
         <v>631</v>
-      </c>
-      <c r="B377" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
+        <v>632</v>
+      </c>
+      <c r="B378" t="s">
         <v>633</v>
-      </c>
-      <c r="B378" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
+        <v>634</v>
+      </c>
+      <c r="B379" t="s">
         <v>635</v>
-      </c>
-      <c r="B379" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
+        <v>636</v>
+      </c>
+      <c r="B380" t="s">
         <v>637</v>
-      </c>
-      <c r="B380" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
+        <v>638</v>
+      </c>
+      <c r="B381" t="s">
         <v>639</v>
-      </c>
-      <c r="B381" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
+        <v>640</v>
+      </c>
+      <c r="B382" t="s">
         <v>641</v>
-      </c>
-      <c r="B382" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
+        <v>642</v>
+      </c>
+      <c r="B383" t="s">
         <v>643</v>
-      </c>
-      <c r="B383" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
+        <v>644</v>
+      </c>
+      <c r="B384" t="s">
         <v>645</v>
-      </c>
-      <c r="B384" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
+        <v>646</v>
+      </c>
+      <c r="B385" t="s">
         <v>647</v>
-      </c>
-      <c r="B385" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
+        <v>648</v>
+      </c>
+      <c r="B386" t="s">
         <v>649</v>
-      </c>
-      <c r="B386" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
+        <v>650</v>
+      </c>
+      <c r="B387" t="s">
         <v>651</v>
-      </c>
-      <c r="B387" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
+        <v>652</v>
+      </c>
+      <c r="B388" t="s">
         <v>653</v>
-      </c>
-      <c r="B388" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
+        <v>654</v>
+      </c>
+      <c r="B389" t="s">
         <v>655</v>
-      </c>
-      <c r="B389" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
+        <v>656</v>
+      </c>
+      <c r="B390" t="s">
         <v>657</v>
-      </c>
-      <c r="B390" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
+        <v>658</v>
+      </c>
+      <c r="B391" t="s">
         <v>659</v>
-      </c>
-      <c r="B391" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
+        <v>660</v>
+      </c>
+      <c r="B392" t="s">
         <v>661</v>
-      </c>
-      <c r="B392" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
+        <v>662</v>
+      </c>
+      <c r="B393" t="s">
         <v>663</v>
-      </c>
-      <c r="B393" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
+        <v>664</v>
+      </c>
+      <c r="B394" t="s">
         <v>665</v>
-      </c>
-      <c r="B394" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
+        <v>666</v>
+      </c>
+      <c r="B395" t="s">
         <v>667</v>
-      </c>
-      <c r="B395" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
+        <v>668</v>
+      </c>
+      <c r="B396" t="s">
         <v>669</v>
-      </c>
-      <c r="B396" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
+        <v>670</v>
+      </c>
+      <c r="B397" t="s">
         <v>671</v>
-      </c>
-      <c r="B397" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
+        <v>672</v>
+      </c>
+      <c r="B398" t="s">
         <v>673</v>
-      </c>
-      <c r="B398" t="s">
-        <v>674</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
+        <v>674</v>
+      </c>
+      <c r="B399" t="s">
         <v>675</v>
-      </c>
-      <c r="B399" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
+        <v>676</v>
+      </c>
+      <c r="B400" t="s">
         <v>677</v>
-      </c>
-      <c r="B400" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
+        <v>678</v>
+      </c>
+      <c r="B401" t="s">
         <v>679</v>
-      </c>
-      <c r="B401" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
+        <v>680</v>
+      </c>
+      <c r="B402" t="s">
         <v>681</v>
-      </c>
-      <c r="B402" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
+        <v>682</v>
+      </c>
+      <c r="B403" t="s">
         <v>683</v>
-      </c>
-      <c r="B403" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
+        <v>684</v>
+      </c>
+      <c r="B404" t="s">
         <v>685</v>
-      </c>
-      <c r="B404" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
+        <v>686</v>
+      </c>
+      <c r="B405" t="s">
         <v>687</v>
-      </c>
-      <c r="B405" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
+        <v>688</v>
+      </c>
+      <c r="B406" t="s">
         <v>689</v>
-      </c>
-      <c r="B406" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
+        <v>690</v>
+      </c>
+      <c r="B407" t="s">
         <v>691</v>
-      </c>
-      <c r="B407" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
+        <v>692</v>
+      </c>
+      <c r="B408" t="s">
         <v>693</v>
-      </c>
-      <c r="B408" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
+        <v>694</v>
+      </c>
+      <c r="B409" t="s">
         <v>695</v>
-      </c>
-      <c r="B409" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
+        <v>696</v>
+      </c>
+      <c r="B410" t="s">
         <v>697</v>
-      </c>
-      <c r="B410" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
+        <v>698</v>
+      </c>
+      <c r="B411" t="s">
         <v>699</v>
-      </c>
-      <c r="B411" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
+        <v>700</v>
+      </c>
+      <c r="B412" t="s">
         <v>701</v>
-      </c>
-      <c r="B412" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
+        <v>702</v>
+      </c>
+      <c r="B413" t="s">
         <v>703</v>
-      </c>
-      <c r="B413" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
+        <v>704</v>
+      </c>
+      <c r="B414" t="s">
         <v>705</v>
-      </c>
-      <c r="B414" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
+        <v>706</v>
+      </c>
+      <c r="B415" t="s">
         <v>707</v>
-      </c>
-      <c r="B415" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
+        <v>708</v>
+      </c>
+      <c r="B416" t="s">
         <v>709</v>
-      </c>
-      <c r="B416" t="s">
-        <v>710</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
+        <v>710</v>
+      </c>
+      <c r="B417" t="s">
         <v>711</v>
-      </c>
-      <c r="B417" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
+        <v>712</v>
+      </c>
+      <c r="B418" t="s">
         <v>713</v>
-      </c>
-      <c r="B418" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
+        <v>714</v>
+      </c>
+      <c r="B419" t="s">
         <v>715</v>
-      </c>
-      <c r="B419" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
+        <v>716</v>
+      </c>
+      <c r="B420" t="s">
         <v>717</v>
-      </c>
-      <c r="B420" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>718</v>
+      </c>
+      <c r="B421" t="s">
         <v>719</v>
-      </c>
-      <c r="B421" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
+        <v>720</v>
+      </c>
+      <c r="B422" t="s">
         <v>721</v>
-      </c>
-      <c r="B422" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
+        <v>722</v>
+      </c>
+      <c r="B423" t="s">
         <v>723</v>
-      </c>
-      <c r="B423" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
+        <v>724</v>
+      </c>
+      <c r="B424" t="s">
         <v>725</v>
-      </c>
-      <c r="B424" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
+        <v>726</v>
+      </c>
+      <c r="B425" t="s">
         <v>727</v>
-      </c>
-      <c r="B425" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
+        <v>728</v>
+      </c>
+      <c r="B426" t="s">
         <v>729</v>
-      </c>
-      <c r="B426" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
+        <v>730</v>
+      </c>
+      <c r="B427" t="s">
         <v>731</v>
-      </c>
-      <c r="B427" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
+        <v>732</v>
+      </c>
+      <c r="B428" t="s">
         <v>733</v>
-      </c>
-      <c r="B428" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
+        <v>734</v>
+      </c>
+      <c r="B429" t="s">
         <v>735</v>
-      </c>
-      <c r="B429" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>736</v>
+      </c>
+      <c r="B430" t="s">
         <v>737</v>
-      </c>
-      <c r="B430" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B431" t="s">
         <v>739</v>
@@ -9825,12 +9828,12 @@
         <v>741</v>
       </c>
       <c r="B433" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B434" t="s">
         <v>743</v>
@@ -9849,76 +9852,76 @@
         <v>745</v>
       </c>
       <c r="B436" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
+        <v>746</v>
+      </c>
+      <c r="B437" t="s">
         <v>747</v>
-      </c>
-      <c r="B437" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
+        <v>748</v>
+      </c>
+      <c r="B438" t="s">
         <v>749</v>
-      </c>
-      <c r="B438" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
+        <v>750</v>
+      </c>
+      <c r="B439" t="s">
         <v>751</v>
-      </c>
-      <c r="B439" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
+        <v>752</v>
+      </c>
+      <c r="B440" t="s">
         <v>753</v>
-      </c>
-      <c r="B440" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
+        <v>754</v>
+      </c>
+      <c r="B441" t="s">
         <v>755</v>
-      </c>
-      <c r="B441" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
+        <v>756</v>
+      </c>
+      <c r="B442" t="s">
         <v>757</v>
-      </c>
-      <c r="B442" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
+        <v>758</v>
+      </c>
+      <c r="B443" t="s">
         <v>759</v>
-      </c>
-      <c r="B443" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
+        <v>760</v>
+      </c>
+      <c r="B444" t="s">
         <v>761</v>
-      </c>
-      <c r="B444" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B445" t="s">
         <v>763</v>
@@ -9929,12 +9932,12 @@
         <v>764</v>
       </c>
       <c r="B446" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B447" t="s">
         <v>766</v>
@@ -9945,12 +9948,12 @@
         <v>767</v>
       </c>
       <c r="B448" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B449" t="s">
         <v>769</v>
@@ -9961,36 +9964,36 @@
         <v>770</v>
       </c>
       <c r="B450" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
+        <v>771</v>
+      </c>
+      <c r="B451" t="s">
         <v>772</v>
-      </c>
-      <c r="B451" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
+        <v>773</v>
+      </c>
+      <c r="B452" t="s">
         <v>774</v>
-      </c>
-      <c r="B452" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
+        <v>775</v>
+      </c>
+      <c r="B453" t="s">
         <v>776</v>
-      </c>
-      <c r="B453" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B454" t="s">
         <v>778</v>
@@ -10009,28 +10012,28 @@
         <v>780</v>
       </c>
       <c r="B456" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
+        <v>781</v>
+      </c>
+      <c r="B457" t="s">
         <v>782</v>
-      </c>
-      <c r="B457" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
+        <v>783</v>
+      </c>
+      <c r="B458" t="s">
         <v>784</v>
-      </c>
-      <c r="B458" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B459" t="s">
         <v>786</v>
@@ -10041,36 +10044,36 @@
         <v>787</v>
       </c>
       <c r="B460" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>788</v>
+      </c>
+      <c r="B461" t="s">
         <v>789</v>
-      </c>
-      <c r="B461" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>790</v>
+      </c>
+      <c r="B462" t="s">
         <v>791</v>
-      </c>
-      <c r="B462" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
+        <v>792</v>
+      </c>
+      <c r="B463" t="s">
         <v>793</v>
-      </c>
-      <c r="B463" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B464" t="s">
         <v>795</v>
@@ -10089,7 +10092,7 @@
         <v>797</v>
       </c>
       <c r="B466" t="s">
-        <v>524</v>
+        <v>797</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -10097,7 +10100,7 @@
         <v>798</v>
       </c>
       <c r="B467" t="s">
-        <v>798</v>
+        <v>525</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -10105,12 +10108,12 @@
         <v>799</v>
       </c>
       <c r="B468" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B469" t="s">
         <v>801</v>
@@ -10121,20 +10124,20 @@
         <v>802</v>
       </c>
       <c r="B470" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
+        <v>803</v>
+      </c>
+      <c r="B471" t="s">
         <v>804</v>
-      </c>
-      <c r="B471" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B472" t="s">
         <v>806</v>
@@ -10145,7 +10148,7 @@
         <v>807</v>
       </c>
       <c r="B473" t="s">
-        <v>524</v>
+        <v>807</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -10153,7 +10156,7 @@
         <v>808</v>
       </c>
       <c r="B474" t="s">
-        <v>808</v>
+        <v>525</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -10169,12 +10172,12 @@
         <v>810</v>
       </c>
       <c r="B476" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B477" t="s">
         <v>812</v>
@@ -10185,36 +10188,36 @@
         <v>813</v>
       </c>
       <c r="B478" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
+        <v>814</v>
+      </c>
+      <c r="B479" t="s">
         <v>815</v>
-      </c>
-      <c r="B479" t="s">
-        <v>816</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
+        <v>816</v>
+      </c>
+      <c r="B480" t="s">
         <v>817</v>
-      </c>
-      <c r="B480" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
+        <v>818</v>
+      </c>
+      <c r="B481" t="s">
         <v>819</v>
-      </c>
-      <c r="B481" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B482" t="s">
         <v>821</v>
@@ -10233,12 +10236,12 @@
         <v>823</v>
       </c>
       <c r="B484" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B485" t="s">
         <v>825</v>
@@ -10249,12 +10252,12 @@
         <v>826</v>
       </c>
       <c r="B486" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B487" t="s">
         <v>828</v>
@@ -10289,156 +10292,156 @@
         <v>832</v>
       </c>
       <c r="B491" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
+        <v>833</v>
+      </c>
+      <c r="B492" t="s">
         <v>834</v>
-      </c>
-      <c r="B492" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>835</v>
+      </c>
+      <c r="B493" t="s">
         <v>836</v>
-      </c>
-      <c r="B493" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>837</v>
+      </c>
+      <c r="B494" t="s">
         <v>838</v>
-      </c>
-      <c r="B494" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>839</v>
+      </c>
+      <c r="B495" t="s">
         <v>840</v>
-      </c>
-      <c r="B495" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>841</v>
+      </c>
+      <c r="B496" t="s">
         <v>842</v>
-      </c>
-      <c r="B496" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>843</v>
+      </c>
+      <c r="B497" t="s">
         <v>844</v>
-      </c>
-      <c r="B497" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>845</v>
+      </c>
+      <c r="B498" t="s">
         <v>846</v>
-      </c>
-      <c r="B498" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>847</v>
+      </c>
+      <c r="B499" t="s">
         <v>848</v>
-      </c>
-      <c r="B499" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>849</v>
+      </c>
+      <c r="B500" t="s">
         <v>850</v>
-      </c>
-      <c r="B500" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>851</v>
+      </c>
+      <c r="B501" t="s">
         <v>852</v>
-      </c>
-      <c r="B501" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>853</v>
+      </c>
+      <c r="B502" t="s">
         <v>854</v>
-      </c>
-      <c r="B502" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>855</v>
+      </c>
+      <c r="B503" t="s">
         <v>856</v>
-      </c>
-      <c r="B503" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>857</v>
+      </c>
+      <c r="B504" t="s">
         <v>858</v>
-      </c>
-      <c r="B504" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>859</v>
+      </c>
+      <c r="B505" t="s">
         <v>860</v>
-      </c>
-      <c r="B505" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>861</v>
+      </c>
+      <c r="B506" t="s">
         <v>862</v>
-      </c>
-      <c r="B506" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>863</v>
+      </c>
+      <c r="B507" t="s">
         <v>864</v>
-      </c>
-      <c r="B507" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>865</v>
+      </c>
+      <c r="B508" t="s">
         <v>866</v>
-      </c>
-      <c r="B508" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>867</v>
+      </c>
+      <c r="B509" t="s">
         <v>868</v>
-      </c>
-      <c r="B509" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B510" t="s">
         <v>870</v>
@@ -10449,20 +10452,20 @@
         <v>871</v>
       </c>
       <c r="B511" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
+        <v>872</v>
+      </c>
+      <c r="B512" t="s">
         <v>873</v>
-      </c>
-      <c r="B512" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B513" t="s">
         <v>875</v>
@@ -10473,52 +10476,52 @@
         <v>876</v>
       </c>
       <c r="B514" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
+        <v>877</v>
+      </c>
+      <c r="B515" t="s">
         <v>878</v>
-      </c>
-      <c r="B515" t="s">
-        <v>879</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
+        <v>879</v>
+      </c>
+      <c r="B516" t="s">
         <v>880</v>
-      </c>
-      <c r="B516" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
+        <v>881</v>
+      </c>
+      <c r="B517" t="s">
         <v>882</v>
-      </c>
-      <c r="B517" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
+        <v>883</v>
+      </c>
+      <c r="B518" t="s">
         <v>884</v>
-      </c>
-      <c r="B518" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
+        <v>885</v>
+      </c>
+      <c r="B519" t="s">
         <v>886</v>
-      </c>
-      <c r="B519" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B520" t="s">
         <v>888</v>
@@ -10537,84 +10540,84 @@
         <v>890</v>
       </c>
       <c r="B522" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
+        <v>891</v>
+      </c>
+      <c r="B523" t="s">
         <v>892</v>
-      </c>
-      <c r="B523" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
+        <v>893</v>
+      </c>
+      <c r="B524" t="s">
         <v>894</v>
-      </c>
-      <c r="B524" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
+        <v>895</v>
+      </c>
+      <c r="B525" t="s">
         <v>896</v>
-      </c>
-      <c r="B525" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
+        <v>897</v>
+      </c>
+      <c r="B526" t="s">
         <v>898</v>
-      </c>
-      <c r="B526" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
+        <v>899</v>
+      </c>
+      <c r="B527" t="s">
         <v>900</v>
-      </c>
-      <c r="B527" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>901</v>
+      </c>
+      <c r="B528" t="s">
         <v>902</v>
-      </c>
-      <c r="B528" t="s">
-        <v>903</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>903</v>
+      </c>
+      <c r="B529" t="s">
         <v>904</v>
-      </c>
-      <c r="B529" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>905</v>
+      </c>
+      <c r="B530" t="s">
         <v>906</v>
-      </c>
-      <c r="B530" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>907</v>
+      </c>
+      <c r="B531" t="s">
         <v>908</v>
-      </c>
-      <c r="B531" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B532" t="s">
         <v>910</v>
@@ -10625,20 +10628,20 @@
         <v>911</v>
       </c>
       <c r="B533" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
+        <v>912</v>
+      </c>
+      <c r="B534" t="s">
         <v>913</v>
-      </c>
-      <c r="B534" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B535" t="s">
         <v>915</v>
@@ -10657,20 +10660,20 @@
         <v>917</v>
       </c>
       <c r="B537" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
+        <v>918</v>
+      </c>
+      <c r="B538" t="s">
         <v>919</v>
-      </c>
-      <c r="B538" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B539" t="s">
         <v>921</v>
@@ -10697,36 +10700,36 @@
         <v>924</v>
       </c>
       <c r="B542" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
+        <v>925</v>
+      </c>
+      <c r="B543" t="s">
         <v>926</v>
-      </c>
-      <c r="B543" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
+        <v>927</v>
+      </c>
+      <c r="B544" t="s">
         <v>928</v>
-      </c>
-      <c r="B544" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
+        <v>929</v>
+      </c>
+      <c r="B545" t="s">
         <v>930</v>
-      </c>
-      <c r="B545" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B546" t="s">
         <v>932</v>
@@ -10745,20 +10748,20 @@
         <v>934</v>
       </c>
       <c r="B548" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
+        <v>935</v>
+      </c>
+      <c r="B549" t="s">
         <v>936</v>
-      </c>
-      <c r="B549" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B550" t="s">
         <v>938</v>
@@ -10777,28 +10780,28 @@
         <v>940</v>
       </c>
       <c r="B552" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
+        <v>941</v>
+      </c>
+      <c r="B553" t="s">
         <v>942</v>
-      </c>
-      <c r="B553" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
+        <v>943</v>
+      </c>
+      <c r="B554" t="s">
         <v>944</v>
-      </c>
-      <c r="B554" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B555" t="s">
         <v>946</v>
@@ -10809,60 +10812,60 @@
         <v>947</v>
       </c>
       <c r="B556" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
+        <v>948</v>
+      </c>
+      <c r="B557" t="s">
         <v>949</v>
-      </c>
-      <c r="B557" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
+        <v>950</v>
+      </c>
+      <c r="B558" t="s">
         <v>951</v>
-      </c>
-      <c r="B558" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>952</v>
+      </c>
+      <c r="B559" t="s">
         <v>953</v>
-      </c>
-      <c r="B559" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>954</v>
+      </c>
+      <c r="B560" t="s">
         <v>955</v>
-      </c>
-      <c r="B560" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>956</v>
+      </c>
+      <c r="B561" t="s">
         <v>957</v>
-      </c>
-      <c r="B561" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>958</v>
+      </c>
+      <c r="B562" t="s">
         <v>959</v>
-      </c>
-      <c r="B562" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B563" t="s">
         <v>961</v>
@@ -10889,20 +10892,20 @@
         <v>964</v>
       </c>
       <c r="B566" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
+        <v>965</v>
+      </c>
+      <c r="B567" t="s">
         <v>966</v>
-      </c>
-      <c r="B567" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B568" t="s">
         <v>968</v>
@@ -10913,52 +10916,52 @@
         <v>969</v>
       </c>
       <c r="B569" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
+        <v>970</v>
+      </c>
+      <c r="B570" t="s">
         <v>971</v>
-      </c>
-      <c r="B570" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
+        <v>972</v>
+      </c>
+      <c r="B571" t="s">
         <v>973</v>
-      </c>
-      <c r="B571" t="s">
-        <v>974</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
+        <v>974</v>
+      </c>
+      <c r="B572" t="s">
         <v>975</v>
-      </c>
-      <c r="B572" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
+        <v>976</v>
+      </c>
+      <c r="B573" t="s">
         <v>977</v>
-      </c>
-      <c r="B573" t="s">
-        <v>978</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
+        <v>978</v>
+      </c>
+      <c r="B574" t="s">
         <v>979</v>
-      </c>
-      <c r="B574" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B575" t="s">
         <v>981</v>
@@ -10969,12 +10972,12 @@
         <v>982</v>
       </c>
       <c r="B576" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B577" t="s">
         <v>984</v>
@@ -11009,20 +11012,20 @@
         <v>988</v>
       </c>
       <c r="B581" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
+        <v>989</v>
+      </c>
+      <c r="B582" t="s">
         <v>990</v>
-      </c>
-      <c r="B582" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B583" t="s">
         <v>992</v>
@@ -11033,100 +11036,100 @@
         <v>993</v>
       </c>
       <c r="B584" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
+        <v>994</v>
+      </c>
+      <c r="B585" t="s">
         <v>995</v>
-      </c>
-      <c r="B585" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
+        <v>996</v>
+      </c>
+      <c r="B586" t="s">
         <v>997</v>
-      </c>
-      <c r="B586" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
+        <v>998</v>
+      </c>
+      <c r="B587" t="s">
         <v>999</v>
-      </c>
-      <c r="B587" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B588" t="s">
         <v>1001</v>
-      </c>
-      <c r="B588" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B589" t="s">
         <v>1003</v>
-      </c>
-      <c r="B589" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B590" t="s">
         <v>1005</v>
-      </c>
-      <c r="B590" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B591" t="s">
         <v>1007</v>
-      </c>
-      <c r="B591" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B592" t="s">
         <v>1009</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B593" t="s">
         <v>1011</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B594" t="s">
         <v>1013</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B595" t="s">
         <v>1015</v>
-      </c>
-      <c r="B595" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B596" t="s">
         <v>1017</v>
@@ -11137,12 +11140,12 @@
         <v>1018</v>
       </c>
       <c r="B597" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B598" t="s">
         <v>1020</v>
@@ -11153,68 +11156,68 @@
         <v>1021</v>
       </c>
       <c r="B599" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B600" t="s">
         <v>1023</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B601" t="s">
         <v>1025</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B602" t="s">
         <v>1027</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B603" t="s">
         <v>1029</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B604" t="s">
         <v>1031</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B605" t="s">
         <v>1033</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1034</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B606" t="s">
         <v>1035</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B607" t="s">
         <v>1037</v>
@@ -11233,12 +11236,12 @@
         <v>1039</v>
       </c>
       <c r="B609" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B610" t="s">
         <v>1041</v>
@@ -11249,52 +11252,52 @@
         <v>1042</v>
       </c>
       <c r="B611" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B612" t="s">
         <v>1044</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B613" t="s">
         <v>1046</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B614" t="s">
         <v>1048</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B615" t="s">
         <v>1050</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B616" t="s">
         <v>1052</v>
-      </c>
-      <c r="B616" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B617" t="s">
         <v>1054</v>
@@ -11305,20 +11308,20 @@
         <v>1055</v>
       </c>
       <c r="B618" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B619" t="s">
         <v>1057</v>
-      </c>
-      <c r="B619" t="s">
-        <v>1058</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B620" t="s">
         <v>1059</v>
@@ -11329,28 +11332,28 @@
         <v>1060</v>
       </c>
       <c r="B621" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B622" t="s">
         <v>1062</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B623" t="s">
         <v>1064</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B624" t="s">
         <v>1066</v>
@@ -11361,12 +11364,12 @@
         <v>1067</v>
       </c>
       <c r="B625" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B626" t="s">
         <v>1069</v>
@@ -11377,20 +11380,20 @@
         <v>1070</v>
       </c>
       <c r="B627" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B628" t="s">
         <v>1072</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1073</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B629" t="s">
         <v>1074</v>
@@ -11401,28 +11404,28 @@
         <v>1075</v>
       </c>
       <c r="B630" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B631" t="s">
         <v>1077</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B632" t="s">
         <v>1079</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B633" t="s">
         <v>1081</v>
@@ -11465,20 +11468,20 @@
         <v>1086</v>
       </c>
       <c r="B638" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B639" t="s">
         <v>1088</v>
-      </c>
-      <c r="B639" t="s">
-        <v>1089</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B640" t="s">
         <v>1090</v>
@@ -11505,12 +11508,12 @@
         <v>1093</v>
       </c>
       <c r="B643" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B644" t="s">
         <v>1095</v>
@@ -11521,12 +11524,12 @@
         <v>1096</v>
       </c>
       <c r="B645" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B646" t="s">
         <v>1098</v>
@@ -11537,12 +11540,12 @@
         <v>1099</v>
       </c>
       <c r="B647" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B648" t="s">
         <v>1101</v>
@@ -11561,36 +11564,36 @@
         <v>1103</v>
       </c>
       <c r="B650" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B651" t="s">
         <v>1105</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1106</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B652" t="s">
         <v>1107</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B653" t="s">
         <v>1109</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B654" t="s">
         <v>1111</v>
@@ -11617,12 +11620,12 @@
         <v>1114</v>
       </c>
       <c r="B657" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B658" t="s">
         <v>1116</v>
@@ -11633,28 +11636,28 @@
         <v>1117</v>
       </c>
       <c r="B659" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B660" t="s">
         <v>1119</v>
-      </c>
-      <c r="B660" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B661" t="s">
         <v>1121</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B662" t="s">
         <v>1123</v>
@@ -11665,76 +11668,76 @@
         <v>1124</v>
       </c>
       <c r="B663" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B664" t="s">
         <v>1126</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B665" t="s">
         <v>1128</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B666" t="s">
         <v>1130</v>
-      </c>
-      <c r="B666" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B667" t="s">
         <v>1132</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B668" t="s">
         <v>1134</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B669" t="s">
         <v>1136</v>
-      </c>
-      <c r="B669" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B670" t="s">
         <v>1138</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B671" t="s">
         <v>1140</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B672" t="s">
         <v>1142</v>
@@ -11745,84 +11748,84 @@
         <v>1143</v>
       </c>
       <c r="B673" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B674" t="s">
         <v>1145</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B675" t="s">
         <v>1147</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B676" t="s">
         <v>1149</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B677" t="s">
         <v>1151</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B678" t="s">
         <v>1153</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B679" t="s">
         <v>1155</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B680" t="s">
         <v>1157</v>
-      </c>
-      <c r="B680" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B681" t="s">
         <v>1159</v>
-      </c>
-      <c r="B681" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B682" t="s">
         <v>1161</v>
-      </c>
-      <c r="B682" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B683" t="s">
         <v>1163</v>
@@ -11833,28 +11836,28 @@
         <v>1164</v>
       </c>
       <c r="B684" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B685" t="s">
         <v>1166</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B686" t="s">
         <v>1168</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B687" t="s">
         <v>1170</v>
@@ -11873,84 +11876,84 @@
         <v>1172</v>
       </c>
       <c r="B689" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B690" t="s">
         <v>1174</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1175</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B691" t="s">
         <v>1176</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B692" t="s">
         <v>1178</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B693" t="s">
         <v>1180</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B694" t="s">
         <v>1182</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B695" t="s">
         <v>1184</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B696" t="s">
         <v>1186</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B697" t="s">
         <v>1188</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B698" t="s">
         <v>1190</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B699" t="s">
         <v>1192</v>
@@ -11961,44 +11964,44 @@
         <v>1193</v>
       </c>
       <c r="B700" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B701" t="s">
         <v>1195</v>
-      </c>
-      <c r="B701" t="s">
-        <v>1196</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B702" t="s">
         <v>1197</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B703" t="s">
         <v>1199</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B704" t="s">
         <v>1201</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B705" t="s">
         <v>1203</v>
@@ -12009,12 +12012,12 @@
         <v>1204</v>
       </c>
       <c r="B706" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B707" t="s">
         <v>1206</v>
@@ -12033,12 +12036,12 @@
         <v>1208</v>
       </c>
       <c r="B709" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B710" t="s">
         <v>1210</v>
@@ -12065,20 +12068,20 @@
         <v>1213</v>
       </c>
       <c r="B713" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B714" t="s">
         <v>1215</v>
-      </c>
-      <c r="B714" t="s">
-        <v>1216</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B715" t="s">
         <v>1217</v>
@@ -12097,28 +12100,28 @@
         <v>1219</v>
       </c>
       <c r="B717" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B718" t="s">
         <v>1221</v>
-      </c>
-      <c r="B718" t="s">
-        <v>1222</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B719" t="s">
         <v>1223</v>
-      </c>
-      <c r="B719" t="s">
-        <v>1224</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B720" t="s">
         <v>1225</v>
@@ -12137,20 +12140,20 @@
         <v>1227</v>
       </c>
       <c r="B722" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B723" t="s">
         <v>1229</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B724" t="s">
         <v>1231</v>
@@ -12161,36 +12164,36 @@
         <v>1232</v>
       </c>
       <c r="B725" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B726" t="s">
         <v>1234</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B727" t="s">
         <v>1236</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B728" t="s">
         <v>1238</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B729" t="s">
         <v>1240</v>
@@ -12209,20 +12212,20 @@
         <v>1242</v>
       </c>
       <c r="B731" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B732" t="s">
         <v>1244</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B733" t="s">
         <v>1246</v>
@@ -12241,12 +12244,12 @@
         <v>1248</v>
       </c>
       <c r="B735" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B736" t="s">
         <v>1250</v>
@@ -12257,28 +12260,28 @@
         <v>1251</v>
       </c>
       <c r="B737" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B738" t="s">
         <v>1253</v>
-      </c>
-      <c r="B738" t="s">
-        <v>1254</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B739" t="s">
         <v>1255</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1256</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B740" t="s">
         <v>1257</v>
@@ -12289,20 +12292,20 @@
         <v>1258</v>
       </c>
       <c r="B741" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B742" t="s">
         <v>1260</v>
-      </c>
-      <c r="B742" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B743" t="s">
         <v>1262</v>
@@ -12313,28 +12316,28 @@
         <v>1263</v>
       </c>
       <c r="B744" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B745" t="s">
         <v>1265</v>
-      </c>
-      <c r="B745" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B746" t="s">
         <v>1267</v>
-      </c>
-      <c r="B746" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B747" t="s">
         <v>1269</v>
@@ -12353,20 +12356,20 @@
         <v>1271</v>
       </c>
       <c r="B749" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B750" t="s">
         <v>1273</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1274</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="B751" t="s">
         <v>1275</v>
@@ -12385,100 +12388,100 @@
         <v>1277</v>
       </c>
       <c r="B753" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B754" t="s">
         <v>1279</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B755" t="s">
         <v>1281</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1282</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B756" t="s">
         <v>1283</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B757" t="s">
         <v>1285</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B758" t="s">
         <v>1287</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B759" t="s">
         <v>1289</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B760" t="s">
         <v>1291</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B761" t="s">
         <v>1293</v>
-      </c>
-      <c r="B761" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B762" t="s">
         <v>1295</v>
-      </c>
-      <c r="B762" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B763" t="s">
         <v>1297</v>
-      </c>
-      <c r="B763" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B764" t="s">
         <v>1299</v>
-      </c>
-      <c r="B764" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B765" t="s">
         <v>1301</v>
@@ -12489,12 +12492,12 @@
         <v>1302</v>
       </c>
       <c r="B766" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B767" t="s">
         <v>1304</v>
@@ -12513,44 +12516,44 @@
         <v>1306</v>
       </c>
       <c r="B769" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B770" t="s">
         <v>1308</v>
-      </c>
-      <c r="B770" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B771" t="s">
         <v>1310</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B772" t="s">
         <v>1312</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B773" t="s">
         <v>1314</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="B774" t="s">
         <v>1316</v>
@@ -12561,100 +12564,100 @@
         <v>1317</v>
       </c>
       <c r="B775" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B776" t="s">
         <v>1319</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B777" t="s">
         <v>1321</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B778" t="s">
         <v>1323</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B779" t="s">
         <v>1325</v>
-      </c>
-      <c r="B779" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B780" t="s">
         <v>1327</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B781" t="s">
         <v>1329</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B782" t="s">
         <v>1331</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B783" t="s">
         <v>1333</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B784" t="s">
         <v>1335</v>
-      </c>
-      <c r="B784" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B785" t="s">
         <v>1337</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B786" t="s">
         <v>1339</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B787" t="s">
         <v>1341</v>
@@ -12689,20 +12692,20 @@
         <v>1345</v>
       </c>
       <c r="B791" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B792" t="s">
         <v>1347</v>
-      </c>
-      <c r="B792" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B793" t="s">
         <v>1349</v>
@@ -12713,12 +12716,12 @@
         <v>1350</v>
       </c>
       <c r="B794" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B795" t="s">
         <v>1352</v>
@@ -12737,12 +12740,12 @@
         <v>1354</v>
       </c>
       <c r="B797" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B798" t="s">
         <v>1356</v>
@@ -12777,12 +12780,12 @@
         <v>1360</v>
       </c>
       <c r="B802" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B803" t="s">
         <v>1362</v>
@@ -12801,60 +12804,60 @@
         <v>1364</v>
       </c>
       <c r="B805" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B806" t="s">
         <v>1366</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B807" t="s">
         <v>1368</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B808" t="s">
         <v>1370</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B809" t="s">
         <v>1372</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B810" t="s">
         <v>1374</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B811" t="s">
         <v>1376</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1377</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B812" t="s">
         <v>1378</v>
@@ -12881,60 +12884,60 @@
         <v>1381</v>
       </c>
       <c r="B815" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B816" t="s">
         <v>1383</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B817" t="s">
         <v>1385</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B818" t="s">
         <v>1387</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B819" t="s">
         <v>1389</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B820" t="s">
         <v>1391</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B821" t="s">
         <v>1393</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="B822" t="s">
         <v>1395</v>
@@ -12945,20 +12948,20 @@
         <v>1396</v>
       </c>
       <c r="B823" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B824" t="s">
         <v>1398</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B825" t="s">
         <v>1400</v>
@@ -12969,28 +12972,28 @@
         <v>1401</v>
       </c>
       <c r="B826" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B827" t="s">
         <v>1403</v>
-      </c>
-      <c r="B827" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B828" t="s">
         <v>1405</v>
-      </c>
-      <c r="B828" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="B829" t="s">
         <v>1407</v>
@@ -13001,12 +13004,12 @@
         <v>1408</v>
       </c>
       <c r="B830" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B831" t="s">
         <v>1410</v>
@@ -13017,12 +13020,12 @@
         <v>1411</v>
       </c>
       <c r="B832" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B833" t="s">
         <v>1413</v>
@@ -13033,12 +13036,12 @@
         <v>1414</v>
       </c>
       <c r="B834" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B835" t="s">
         <v>1416</v>
@@ -13049,12 +13052,12 @@
         <v>1417</v>
       </c>
       <c r="B836" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B837" t="s">
         <v>1419</v>
@@ -13089,20 +13092,20 @@
         <v>1423</v>
       </c>
       <c r="B841" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B842" t="s">
         <v>1425</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B843" t="s">
         <v>1427</v>
@@ -13113,20 +13116,20 @@
         <v>1428</v>
       </c>
       <c r="B844" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B845" t="s">
         <v>1430</v>
-      </c>
-      <c r="B845" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B846" t="s">
         <v>1432</v>
@@ -13137,12 +13140,12 @@
         <v>1433</v>
       </c>
       <c r="B847" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B848" t="s">
         <v>1435</v>
@@ -13177,108 +13180,108 @@
         <v>1439</v>
       </c>
       <c r="B852" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B853" t="s">
         <v>1441</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B854" t="s">
         <v>1443</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B855" t="s">
         <v>1445</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B856" t="s">
         <v>1447</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B857" t="s">
         <v>1449</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B858" t="s">
         <v>1451</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B859" t="s">
         <v>1453</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B860" t="s">
         <v>1455</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B861" t="s">
         <v>1457</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B862" t="s">
         <v>1459</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B863" t="s">
         <v>1461</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1462</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B864" t="s">
         <v>1463</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B865" t="s">
         <v>1465</v>
@@ -13305,12 +13308,12 @@
         <v>1468</v>
       </c>
       <c r="B868" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B869" t="s">
         <v>1470</v>
@@ -13345,12 +13348,12 @@
         <v>1474</v>
       </c>
       <c r="B873" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B874" t="s">
         <v>1476</v>
@@ -13377,12 +13380,12 @@
         <v>1479</v>
       </c>
       <c r="B877" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="B878" t="s">
         <v>1481</v>
@@ -13393,60 +13396,60 @@
         <v>1482</v>
       </c>
       <c r="B879" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B880" t="s">
         <v>1484</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1485</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B881" t="s">
         <v>1486</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1487</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B882" t="s">
         <v>1488</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B883" t="s">
         <v>1490</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B884" t="s">
         <v>1492</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B885" t="s">
         <v>1494</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B886" t="s">
         <v>1496</v>
@@ -13465,28 +13468,28 @@
         <v>1498</v>
       </c>
       <c r="B888" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B889" t="s">
         <v>1500</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1501</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B890" t="s">
         <v>1502</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B891" t="s">
         <v>1504</v>
@@ -13505,12 +13508,12 @@
         <v>1506</v>
       </c>
       <c r="B893" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="B894" t="s">
         <v>1508</v>
@@ -13521,12 +13524,12 @@
         <v>1509</v>
       </c>
       <c r="B895" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B896" t="s">
         <v>1511</v>
@@ -13537,12 +13540,12 @@
         <v>1512</v>
       </c>
       <c r="B897" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="B898" t="s">
         <v>1514</v>
@@ -13553,12 +13556,12 @@
         <v>1515</v>
       </c>
       <c r="B899" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B900" t="s">
         <v>1517</v>
@@ -13569,36 +13572,36 @@
         <v>1518</v>
       </c>
       <c r="B901" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B902" t="s">
         <v>1520</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B903" t="s">
         <v>1522</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B904" t="s">
         <v>1524</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1525</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B905" t="s">
         <v>1526</v>
@@ -13609,52 +13612,52 @@
         <v>1527</v>
       </c>
       <c r="B906" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B907" t="s">
         <v>1529</v>
-      </c>
-      <c r="B907" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B908" t="s">
         <v>1531</v>
-      </c>
-      <c r="B908" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B909" t="s">
         <v>1533</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1534</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B910" t="s">
         <v>1535</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B911" t="s">
         <v>1537</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1538</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B912" t="s">
         <v>1539</v>
@@ -13713,28 +13716,28 @@
         <v>1546</v>
       </c>
       <c r="B919" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B920" t="s">
         <v>1548</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B921" t="s">
         <v>1550</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1551</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B922" t="s">
         <v>1552</v>
@@ -13761,44 +13764,44 @@
         <v>1555</v>
       </c>
       <c r="B925" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B926" t="s">
         <v>1557</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B927" t="s">
         <v>1559</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B928" t="s">
         <v>1561</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B929" t="s">
         <v>1563</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B930" t="s">
         <v>1565</v>
@@ -13817,36 +13820,36 @@
         <v>1567</v>
       </c>
       <c r="B932" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B933" t="s">
         <v>1569</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B934" t="s">
         <v>1571</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B935" t="s">
         <v>1573</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B936" t="s">
         <v>1575</v>
@@ -13857,20 +13860,20 @@
         <v>1576</v>
       </c>
       <c r="B937" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B938" t="s">
         <v>1578</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1579</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="B939" t="s">
         <v>1580</v>
@@ -13881,12 +13884,12 @@
         <v>1581</v>
       </c>
       <c r="B940" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B941" t="s">
         <v>1583</v>
@@ -13897,60 +13900,60 @@
         <v>1584</v>
       </c>
       <c r="B942" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B943" t="s">
         <v>1586</v>
-      </c>
-      <c r="B943" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B944" t="s">
         <v>1588</v>
-      </c>
-      <c r="B944" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B945" t="s">
         <v>1590</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B946" t="s">
         <v>1592</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1593</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B947" t="s">
         <v>1594</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1595</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B948" t="s">
         <v>1596</v>
-      </c>
-      <c r="B948" t="s">
-        <v>1597</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B949" t="s">
         <v>1598</v>
@@ -13977,20 +13980,20 @@
         <v>1601</v>
       </c>
       <c r="B952" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B953" t="s">
         <v>1603</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B954" t="s">
         <v>1605</v>
@@ -14033,44 +14036,44 @@
         <v>1610</v>
       </c>
       <c r="B959" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B960" t="s">
         <v>1612</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B961" t="s">
         <v>1614</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B962" t="s">
         <v>1616</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B963" t="s">
         <v>1618</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="B964" t="s">
         <v>1620</v>
@@ -14089,36 +14092,36 @@
         <v>1622</v>
       </c>
       <c r="B966" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B967" t="s">
         <v>1624</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B968" t="s">
         <v>1626</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B969" t="s">
         <v>1628</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="B970" t="s">
         <v>1630</v>
@@ -14129,20 +14132,20 @@
         <v>1631</v>
       </c>
       <c r="B971" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B972" t="s">
         <v>1633</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B973" t="s">
         <v>1635</v>
@@ -14161,100 +14164,100 @@
         <v>1637</v>
       </c>
       <c r="B975" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B976" t="s">
         <v>1639</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1640</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B977" t="s">
         <v>1641</v>
-      </c>
-      <c r="B977" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B978" t="s">
         <v>1643</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B979" t="s">
         <v>1645</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1646</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B980" t="s">
         <v>1647</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B981" t="s">
         <v>1649</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B982" t="s">
         <v>1651</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1652</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B983" t="s">
         <v>1653</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B984" t="s">
         <v>1655</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1656</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B985" t="s">
         <v>1657</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B986" t="s">
         <v>1659</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B987" t="s">
         <v>1661</v>
@@ -14281,12 +14284,12 @@
         <v>1664</v>
       </c>
       <c r="B990" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B991" t="s">
         <v>1666</v>
@@ -14321,12 +14324,12 @@
         <v>1670</v>
       </c>
       <c r="B995" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B996" t="s">
         <v>1672</v>
@@ -14337,36 +14340,36 @@
         <v>1673</v>
       </c>
       <c r="B997" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B998" t="s">
         <v>1675</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1676</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B999" t="s">
         <v>1677</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1679</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1001" t="s">
         <v>1681</v>
@@ -14377,20 +14380,20 @@
         <v>1682</v>
       </c>
       <c r="B1002" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1684</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1685</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1004" t="s">
         <v>1686</v>
@@ -14401,52 +14404,52 @@
         <v>1687</v>
       </c>
       <c r="B1005" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1689</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1690</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1691</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B1008" t="s">
         <v>1693</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B1009" t="s">
         <v>1695</v>
-      </c>
-      <c r="B1009" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1697</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1698</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="B1011" t="s">
         <v>1699</v>
@@ -14465,28 +14468,28 @@
         <v>1701</v>
       </c>
       <c r="B1013" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1703</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1705</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="B1016" t="s">
         <v>1707</v>
@@ -14521,20 +14524,20 @@
         <v>1711</v>
       </c>
       <c r="B1020" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1021" t="s">
         <v>1713</v>
-      </c>
-      <c r="B1021" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B1022" t="s">
         <v>1715</v>
@@ -14545,12 +14548,12 @@
         <v>1716</v>
       </c>
       <c r="B1023" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B1024" t="s">
         <v>1718</v>
@@ -14569,20 +14572,20 @@
         <v>1720</v>
       </c>
       <c r="B1026" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1027" t="s">
         <v>1722</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1028" t="s">
         <v>1724</v>
@@ -14593,28 +14596,28 @@
         <v>1725</v>
       </c>
       <c r="B1029" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1030" t="s">
         <v>1727</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1031" t="s">
         <v>1729</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B1032" t="s">
         <v>1731</v>
@@ -14625,12 +14628,12 @@
         <v>1732</v>
       </c>
       <c r="B1033" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B1034" t="s">
         <v>1734</v>
@@ -14649,12 +14652,12 @@
         <v>1736</v>
       </c>
       <c r="B1036" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B1037" t="s">
         <v>1738</v>
@@ -14705,20 +14708,20 @@
         <v>1744</v>
       </c>
       <c r="B1043" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1044" t="s">
         <v>1746</v>
-      </c>
-      <c r="B1044" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B1045" t="s">
         <v>1748</v>
@@ -14729,28 +14732,28 @@
         <v>1749</v>
       </c>
       <c r="B1046" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1751</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1753</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B1049" t="s">
         <v>1755</v>
@@ -14761,20 +14764,20 @@
         <v>1756</v>
       </c>
       <c r="B1050" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B1051" t="s">
         <v>1758</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1052" t="s">
         <v>1760</v>
@@ -14785,124 +14788,124 @@
         <v>1761</v>
       </c>
       <c r="B1053" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1762</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1763</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1764</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1765</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1766</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1767</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1768</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1769</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1771</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1774</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1775</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1776</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1777</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1778</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1779</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1781</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1783</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1784</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1785</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1787</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1789</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B1068" t="s">
         <v>1791</v>
@@ -14913,100 +14916,100 @@
         <v>1792</v>
       </c>
       <c r="B1069" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1794</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1796</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1798</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1073" t="s">
         <v>1800</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>1801</v>
+      </c>
+      <c r="B1074" t="s">
         <v>1802</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>1803</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1804</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1805</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1076" t="s">
         <v>1806</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B1077" t="s">
         <v>1808</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B1078" t="s">
         <v>1810</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>1811</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1079" t="s">
         <v>1812</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1080" t="s">
         <v>1814</v>
-      </c>
-      <c r="B1080" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B1081" t="s">
         <v>1816</v>
@@ -15017,28 +15020,28 @@
         <v>1817</v>
       </c>
       <c r="B1082" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1083" t="s">
         <v>1819</v>
-      </c>
-      <c r="B1083" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
+        <v>1820</v>
+      </c>
+      <c r="B1084" t="s">
         <v>1821</v>
-      </c>
-      <c r="B1084" t="s">
-        <v>1822</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="B1085" t="s">
         <v>1823</v>
@@ -15057,12 +15060,12 @@
         <v>1825</v>
       </c>
       <c r="B1087" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B1088" t="s">
         <v>1827</v>
@@ -15073,20 +15076,20 @@
         <v>1828</v>
       </c>
       <c r="B1089" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1830</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="B1091" t="s">
         <v>1832</v>
@@ -15097,76 +15100,76 @@
         <v>1833</v>
       </c>
       <c r="B1092" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1093" t="s">
         <v>1835</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1837</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1839</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1841</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1843</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1845</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1847</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B1101" t="s">
         <v>1851</v>
@@ -15177,44 +15180,44 @@
         <v>1852</v>
       </c>
       <c r="B1102" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1103" t="s">
         <v>1854</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1104" t="s">
         <v>1856</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1858</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B1106" t="s">
         <v>1860</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="B1107" t="s">
         <v>1862</v>
@@ -15225,20 +15228,20 @@
         <v>1863</v>
       </c>
       <c r="B1108" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1865</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="B1110" t="s">
         <v>1867</v>
@@ -15257,12 +15260,12 @@
         <v>1869</v>
       </c>
       <c r="B1112" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B1113" t="s">
         <v>1871</v>
@@ -15281,52 +15284,52 @@
         <v>1873</v>
       </c>
       <c r="B1115" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1875</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1876</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1877</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1878</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1879</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1119" t="s">
         <v>1881</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1883</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="B1121" t="s">
         <v>1885</v>
@@ -15337,44 +15340,44 @@
         <v>1886</v>
       </c>
       <c r="B1122" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1888</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1890</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1891</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1892</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1893</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1894</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B1127" t="s">
         <v>1896</v>
@@ -15385,108 +15388,108 @@
         <v>1897</v>
       </c>
       <c r="B1128" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1899</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1901</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1903</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1904</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1905</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1906</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1906</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1907</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1908</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1909</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1910</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1911</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1912</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1912</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1913</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1914</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1915</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1916</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1916</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1917</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1918</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1918</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1919</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1920</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1920</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1921</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1922</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B1141" t="s">
         <v>1923</v>
@@ -15513,12 +15516,12 @@
         <v>1926</v>
       </c>
       <c r="B1144" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B1145" t="s">
         <v>1928</v>
@@ -15529,20 +15532,20 @@
         <v>1929</v>
       </c>
       <c r="B1146" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1931</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1932</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B1148" t="s">
         <v>1933</v>
@@ -15569,84 +15572,84 @@
         <v>1936</v>
       </c>
       <c r="B1151" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1152" t="s">
         <v>1938</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>1939</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B1153" t="s">
         <v>1940</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>1941</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1942</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1943</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1944</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1945</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1945</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1946</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1947</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1948</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1949</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1158" t="s">
         <v>1950</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>1951</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B1159" t="s">
         <v>1952</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>1953</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B1160" t="s">
         <v>1954</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>1955</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B1161" t="s">
         <v>1956</v>
@@ -15657,44 +15660,44 @@
         <v>1957</v>
       </c>
       <c r="B1162" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1959</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1960</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1961</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1962</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1963</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1964</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1166" t="s">
         <v>1965</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>1966</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B1167" t="s">
         <v>1967</v>
@@ -15713,12 +15716,12 @@
         <v>1969</v>
       </c>
       <c r="B1169" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B1170" t="s">
         <v>1971</v>
@@ -15729,20 +15732,20 @@
         <v>1972</v>
       </c>
       <c r="B1171" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1172" t="s">
         <v>1974</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>1975</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B1173" t="s">
         <v>1976</v>
@@ -15761,12 +15764,12 @@
         <v>1978</v>
       </c>
       <c r="B1175" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B1176" t="s">
         <v>1980</v>
@@ -15801,20 +15804,20 @@
         <v>1984</v>
       </c>
       <c r="B1180" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1181" t="s">
         <v>1986</v>
-      </c>
-      <c r="B1181" t="s">
-        <v>1987</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B1182" t="s">
         <v>1988</v>
@@ -15825,20 +15828,20 @@
         <v>1989</v>
       </c>
       <c r="B1183" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B1184" t="s">
         <v>1991</v>
-      </c>
-      <c r="B1184" t="s">
-        <v>1992</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B1185" t="s">
         <v>1993</v>
@@ -15849,19 +15852,27 @@
         <v>1994</v>
       </c>
       <c r="B1186" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1187" t="s">
         <v>1996</v>
       </c>
-      <c r="B1187" t="s">
+    </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
         <v>1997</v>
       </c>
+      <c r="B1188" t="s">
+        <v>1998</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2001">
   <si>
     <t>en</t>
   </si>
@@ -4808,6 +4808,12 @@
   </si>
   <si>
     <t>Sence Mordorja</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Morski pes</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -6360,7 +6366,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13964,28 +13970,28 @@
         <v>1599</v>
       </c>
       <c r="B950" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B951" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B952" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B953" t="s">
         <v>1603</v>
@@ -14004,44 +14010,44 @@
         <v>1606</v>
       </c>
       <c r="B955" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B956" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B957" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B958" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B959" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B960" t="s">
         <v>1612</v>
@@ -14084,20 +14090,20 @@
         <v>1621</v>
       </c>
       <c r="B965" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B966" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B967" t="s">
         <v>1624</v>
@@ -14132,12 +14138,12 @@
         <v>1631</v>
       </c>
       <c r="B971" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B972" t="s">
         <v>1633</v>
@@ -14156,20 +14162,20 @@
         <v>1636</v>
       </c>
       <c r="B974" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B975" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B976" t="s">
         <v>1639</v>
@@ -14268,28 +14274,28 @@
         <v>1662</v>
       </c>
       <c r="B988" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B989" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B990" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B991" t="s">
         <v>1666</v>
@@ -14300,36 +14306,36 @@
         <v>1667</v>
       </c>
       <c r="B992" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B993" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B994" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B995" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B996" t="s">
         <v>1672</v>
@@ -14340,12 +14346,12 @@
         <v>1673</v>
       </c>
       <c r="B997" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B998" t="s">
         <v>1675</v>
@@ -14380,12 +14386,12 @@
         <v>1682</v>
       </c>
       <c r="B1002" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1003" t="s">
         <v>1684</v>
@@ -14404,12 +14410,12 @@
         <v>1687</v>
       </c>
       <c r="B1005" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1006" t="s">
         <v>1689</v>
@@ -14460,20 +14466,20 @@
         <v>1700</v>
       </c>
       <c r="B1012" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1013" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1014" t="s">
         <v>1703</v>
@@ -14500,36 +14506,36 @@
         <v>1708</v>
       </c>
       <c r="B1017" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1018" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1019" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1020" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1021" t="s">
         <v>1713</v>
@@ -14548,12 +14554,12 @@
         <v>1716</v>
       </c>
       <c r="B1023" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1024" t="s">
         <v>1718</v>
@@ -14564,20 +14570,20 @@
         <v>1719</v>
       </c>
       <c r="B1025" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1026" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1027" t="s">
         <v>1722</v>
@@ -14596,12 +14602,12 @@
         <v>1725</v>
       </c>
       <c r="B1029" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1030" t="s">
         <v>1727</v>
@@ -14628,12 +14634,12 @@
         <v>1732</v>
       </c>
       <c r="B1033" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1034" t="s">
         <v>1734</v>
@@ -14644,20 +14650,20 @@
         <v>1735</v>
       </c>
       <c r="B1035" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1036" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1037" t="s">
         <v>1738</v>
@@ -14668,52 +14674,52 @@
         <v>1739</v>
       </c>
       <c r="B1038" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1039" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1040" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1041" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1042" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1043" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1044" t="s">
         <v>1746</v>
@@ -14732,12 +14738,12 @@
         <v>1749</v>
       </c>
       <c r="B1046" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1047" t="s">
         <v>1751</v>
@@ -14764,12 +14770,12 @@
         <v>1756</v>
       </c>
       <c r="B1050" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B1051" t="s">
         <v>1758</v>
@@ -14788,12 +14794,12 @@
         <v>1761</v>
       </c>
       <c r="B1053" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B1054" t="s">
         <v>1763</v>
@@ -14916,12 +14922,12 @@
         <v>1792</v>
       </c>
       <c r="B1069" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1070" t="s">
         <v>1794</v>
@@ -15020,12 +15026,12 @@
         <v>1817</v>
       </c>
       <c r="B1082" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1083" t="s">
         <v>1819</v>
@@ -15052,20 +15058,20 @@
         <v>1824</v>
       </c>
       <c r="B1086" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1087" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1088" t="s">
         <v>1827</v>
@@ -15076,12 +15082,12 @@
         <v>1828</v>
       </c>
       <c r="B1089" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1090" t="s">
         <v>1830</v>
@@ -15100,12 +15106,12 @@
         <v>1833</v>
       </c>
       <c r="B1092" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1093" t="s">
         <v>1835</v>
@@ -15180,12 +15186,12 @@
         <v>1852</v>
       </c>
       <c r="B1102" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1103" t="s">
         <v>1854</v>
@@ -15228,12 +15234,12 @@
         <v>1863</v>
       </c>
       <c r="B1108" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1109" t="s">
         <v>1865</v>
@@ -15252,20 +15258,20 @@
         <v>1868</v>
       </c>
       <c r="B1111" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1112" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1113" t="s">
         <v>1871</v>
@@ -15276,20 +15282,20 @@
         <v>1872</v>
       </c>
       <c r="B1114" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1115" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1116" t="s">
         <v>1875</v>
@@ -15340,12 +15346,12 @@
         <v>1886</v>
       </c>
       <c r="B1122" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B1123" t="s">
         <v>1888</v>
@@ -15388,12 +15394,12 @@
         <v>1897</v>
       </c>
       <c r="B1128" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1129" t="s">
         <v>1899</v>
@@ -15500,28 +15506,28 @@
         <v>1924</v>
       </c>
       <c r="B1142" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1143" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1144" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1145" t="s">
         <v>1928</v>
@@ -15532,12 +15538,12 @@
         <v>1929</v>
       </c>
       <c r="B1146" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1147" t="s">
         <v>1931</v>
@@ -15556,28 +15562,28 @@
         <v>1934</v>
       </c>
       <c r="B1149" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1150" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B1151" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1152" t="s">
         <v>1938</v>
@@ -15660,12 +15666,12 @@
         <v>1957</v>
       </c>
       <c r="B1162" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="B1163" t="s">
         <v>1959</v>
@@ -15708,20 +15714,20 @@
         <v>1968</v>
       </c>
       <c r="B1168" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="B1169" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="B1170" t="s">
         <v>1971</v>
@@ -15732,12 +15738,12 @@
         <v>1972</v>
       </c>
       <c r="B1171" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B1172" t="s">
         <v>1974</v>
@@ -15756,20 +15762,20 @@
         <v>1977</v>
       </c>
       <c r="B1174" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B1175" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1176" t="s">
         <v>1980</v>
@@ -15780,36 +15786,36 @@
         <v>1981</v>
       </c>
       <c r="B1177" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1178" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1179" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1180" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1181" t="s">
         <v>1986</v>
@@ -15828,12 +15834,12 @@
         <v>1989</v>
       </c>
       <c r="B1183" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1184" t="s">
         <v>1991</v>
@@ -15852,12 +15858,12 @@
         <v>1994</v>
       </c>
       <c r="B1186" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B1187" t="s">
         <v>1996</v>
@@ -15871,8 +15877,16 @@
         <v>1998</v>
       </c>
     </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>2000</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -1615,6 +1615,12 @@
     <t>Pravljice</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
+    <t>Jesenski padec</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -6014,12 +6020,6 @@
   </si>
   <si>
     <t>Hypixel (mutacije) Oznaka</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
-  </si>
-  <si>
-    <t>Jesenski padec</t>
   </si>
 </sst>
 </file>
@@ -8978,20 +8978,20 @@
         <v>534</v>
       </c>
       <c r="B326" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B327" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B328" t="s">
         <v>537</v>
@@ -9026,12 +9026,12 @@
         <v>544</v>
       </c>
       <c r="B332" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B333" t="s">
         <v>546</v>
@@ -9098,12 +9098,12 @@
         <v>561</v>
       </c>
       <c r="B341" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B342" t="s">
         <v>563</v>
@@ -9122,12 +9122,12 @@
         <v>566</v>
       </c>
       <c r="B344" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B345" t="s">
         <v>568</v>
@@ -9290,12 +9290,12 @@
         <v>607</v>
       </c>
       <c r="B365" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B366" t="s">
         <v>609</v>
@@ -9826,20 +9826,20 @@
         <v>740</v>
       </c>
       <c r="B432" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B433" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B434" t="s">
         <v>743</v>
@@ -9850,20 +9850,20 @@
         <v>744</v>
       </c>
       <c r="B435" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B436" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B437" t="s">
         <v>747</v>
@@ -9938,12 +9938,12 @@
         <v>764</v>
       </c>
       <c r="B446" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B447" t="s">
         <v>766</v>
@@ -9954,12 +9954,12 @@
         <v>767</v>
       </c>
       <c r="B448" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B449" t="s">
         <v>769</v>
@@ -9970,12 +9970,12 @@
         <v>770</v>
       </c>
       <c r="B450" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B451" t="s">
         <v>772</v>
@@ -10010,20 +10010,20 @@
         <v>779</v>
       </c>
       <c r="B455" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B456" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B457" t="s">
         <v>782</v>
@@ -10050,12 +10050,12 @@
         <v>787</v>
       </c>
       <c r="B460" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B461" t="s">
         <v>789</v>
@@ -10090,36 +10090,36 @@
         <v>796</v>
       </c>
       <c r="B465" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B466" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B467" t="s">
-        <v>525</v>
+        <v>799</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B468" t="s">
-        <v>799</v>
+        <v>525</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B469" t="s">
         <v>801</v>
@@ -10130,12 +10130,12 @@
         <v>802</v>
       </c>
       <c r="B470" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B471" t="s">
         <v>804</v>
@@ -10154,36 +10154,36 @@
         <v>807</v>
       </c>
       <c r="B473" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B474" t="s">
-        <v>525</v>
+        <v>809</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B475" t="s">
-        <v>809</v>
+        <v>525</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B476" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B477" t="s">
         <v>812</v>
@@ -10194,12 +10194,12 @@
         <v>813</v>
       </c>
       <c r="B478" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B479" t="s">
         <v>815</v>
@@ -10234,20 +10234,20 @@
         <v>822</v>
       </c>
       <c r="B483" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B484" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B485" t="s">
         <v>825</v>
@@ -10258,12 +10258,12 @@
         <v>826</v>
       </c>
       <c r="B486" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B487" t="s">
         <v>828</v>
@@ -10274,36 +10274,36 @@
         <v>829</v>
       </c>
       <c r="B488" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B489" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B490" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B491" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B492" t="s">
         <v>834</v>
@@ -10458,12 +10458,12 @@
         <v>871</v>
       </c>
       <c r="B511" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B512" t="s">
         <v>873</v>
@@ -10482,12 +10482,12 @@
         <v>876</v>
       </c>
       <c r="B514" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B515" t="s">
         <v>878</v>
@@ -10538,20 +10538,20 @@
         <v>889</v>
       </c>
       <c r="B521" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B522" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B523" t="s">
         <v>892</v>
@@ -10634,12 +10634,12 @@
         <v>911</v>
       </c>
       <c r="B533" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B534" t="s">
         <v>913</v>
@@ -10658,20 +10658,20 @@
         <v>916</v>
       </c>
       <c r="B536" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B537" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B538" t="s">
         <v>919</v>
@@ -10690,28 +10690,28 @@
         <v>922</v>
       </c>
       <c r="B540" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B541" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B542" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B543" t="s">
         <v>926</v>
@@ -10746,20 +10746,20 @@
         <v>933</v>
       </c>
       <c r="B547" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B548" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B549" t="s">
         <v>936</v>
@@ -10778,20 +10778,20 @@
         <v>939</v>
       </c>
       <c r="B551" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B552" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B553" t="s">
         <v>942</v>
@@ -10818,12 +10818,12 @@
         <v>947</v>
       </c>
       <c r="B556" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B557" t="s">
         <v>949</v>
@@ -10882,28 +10882,28 @@
         <v>962</v>
       </c>
       <c r="B564" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B565" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B566" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B567" t="s">
         <v>966</v>
@@ -10922,12 +10922,12 @@
         <v>969</v>
       </c>
       <c r="B569" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B570" t="s">
         <v>971</v>
@@ -10978,12 +10978,12 @@
         <v>982</v>
       </c>
       <c r="B576" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B577" t="s">
         <v>984</v>
@@ -10994,36 +10994,36 @@
         <v>985</v>
       </c>
       <c r="B578" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B579" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B580" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B581" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B582" t="s">
         <v>990</v>
@@ -11042,12 +11042,12 @@
         <v>993</v>
       </c>
       <c r="B584" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B585" t="s">
         <v>995</v>
@@ -11146,12 +11146,12 @@
         <v>1018</v>
       </c>
       <c r="B597" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B598" t="s">
         <v>1020</v>
@@ -11162,12 +11162,12 @@
         <v>1021</v>
       </c>
       <c r="B599" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B600" t="s">
         <v>1023</v>
@@ -11234,20 +11234,20 @@
         <v>1038</v>
       </c>
       <c r="B608" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B609" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B610" t="s">
         <v>1041</v>
@@ -11258,12 +11258,12 @@
         <v>1042</v>
       </c>
       <c r="B611" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B612" t="s">
         <v>1044</v>
@@ -11314,12 +11314,12 @@
         <v>1055</v>
       </c>
       <c r="B618" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B619" t="s">
         <v>1057</v>
@@ -11338,12 +11338,12 @@
         <v>1060</v>
       </c>
       <c r="B621" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B622" t="s">
         <v>1062</v>
@@ -11370,12 +11370,12 @@
         <v>1067</v>
       </c>
       <c r="B625" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B626" t="s">
         <v>1069</v>
@@ -11386,12 +11386,12 @@
         <v>1070</v>
       </c>
       <c r="B627" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B628" t="s">
         <v>1072</v>
@@ -11410,12 +11410,12 @@
         <v>1075</v>
       </c>
       <c r="B630" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B631" t="s">
         <v>1077</v>
@@ -11442,44 +11442,44 @@
         <v>1082</v>
       </c>
       <c r="B634" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B635" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B636" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B637" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B638" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B639" t="s">
         <v>1088</v>
@@ -11498,28 +11498,28 @@
         <v>1091</v>
       </c>
       <c r="B641" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B642" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B643" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B644" t="s">
         <v>1095</v>
@@ -11530,12 +11530,12 @@
         <v>1096</v>
       </c>
       <c r="B645" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B646" t="s">
         <v>1098</v>
@@ -11546,12 +11546,12 @@
         <v>1099</v>
       </c>
       <c r="B647" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B648" t="s">
         <v>1101</v>
@@ -11562,20 +11562,20 @@
         <v>1102</v>
       </c>
       <c r="B649" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B650" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B651" t="s">
         <v>1105</v>
@@ -11610,28 +11610,28 @@
         <v>1112</v>
       </c>
       <c r="B655" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B656" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B657" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B658" t="s">
         <v>1116</v>
@@ -11642,12 +11642,12 @@
         <v>1117</v>
       </c>
       <c r="B659" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B660" t="s">
         <v>1119</v>
@@ -11674,12 +11674,12 @@
         <v>1124</v>
       </c>
       <c r="B663" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B664" t="s">
         <v>1126</v>
@@ -11754,12 +11754,12 @@
         <v>1143</v>
       </c>
       <c r="B673" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B674" t="s">
         <v>1145</v>
@@ -11842,12 +11842,12 @@
         <v>1164</v>
       </c>
       <c r="B684" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B685" t="s">
         <v>1166</v>
@@ -11874,20 +11874,20 @@
         <v>1171</v>
       </c>
       <c r="B688" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B689" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B690" t="s">
         <v>1174</v>
@@ -11970,12 +11970,12 @@
         <v>1193</v>
       </c>
       <c r="B700" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B701" t="s">
         <v>1195</v>
@@ -12018,12 +12018,12 @@
         <v>1204</v>
       </c>
       <c r="B706" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B707" t="s">
         <v>1206</v>
@@ -12034,20 +12034,20 @@
         <v>1207</v>
       </c>
       <c r="B708" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B709" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B710" t="s">
         <v>1210</v>
@@ -12058,28 +12058,28 @@
         <v>1211</v>
       </c>
       <c r="B711" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B712" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B713" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B714" t="s">
         <v>1215</v>
@@ -12098,20 +12098,20 @@
         <v>1218</v>
       </c>
       <c r="B716" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B717" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B718" t="s">
         <v>1221</v>
@@ -12138,20 +12138,20 @@
         <v>1226</v>
       </c>
       <c r="B721" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B722" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B723" t="s">
         <v>1229</v>
@@ -12170,12 +12170,12 @@
         <v>1232</v>
       </c>
       <c r="B725" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B726" t="s">
         <v>1234</v>
@@ -12210,20 +12210,20 @@
         <v>1241</v>
       </c>
       <c r="B730" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B731" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B732" t="s">
         <v>1244</v>
@@ -12242,20 +12242,20 @@
         <v>1247</v>
       </c>
       <c r="B734" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B735" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B736" t="s">
         <v>1250</v>
@@ -12266,12 +12266,12 @@
         <v>1251</v>
       </c>
       <c r="B737" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B738" t="s">
         <v>1253</v>
@@ -12298,12 +12298,12 @@
         <v>1258</v>
       </c>
       <c r="B741" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B742" t="s">
         <v>1260</v>
@@ -12322,12 +12322,12 @@
         <v>1263</v>
       </c>
       <c r="B744" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B745" t="s">
         <v>1265</v>
@@ -12354,20 +12354,20 @@
         <v>1270</v>
       </c>
       <c r="B748" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B749" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B750" t="s">
         <v>1273</v>
@@ -12386,20 +12386,20 @@
         <v>1276</v>
       </c>
       <c r="B752" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B753" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B754" t="s">
         <v>1279</v>
@@ -12498,12 +12498,12 @@
         <v>1302</v>
       </c>
       <c r="B766" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B767" t="s">
         <v>1304</v>
@@ -12514,20 +12514,20 @@
         <v>1305</v>
       </c>
       <c r="B768" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B769" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B770" t="s">
         <v>1308</v>
@@ -12570,12 +12570,12 @@
         <v>1317</v>
       </c>
       <c r="B775" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B776" t="s">
         <v>1319</v>
@@ -12674,36 +12674,36 @@
         <v>1342</v>
       </c>
       <c r="B788" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B789" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B790" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B791" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B792" t="s">
         <v>1347</v>
@@ -12722,12 +12722,12 @@
         <v>1350</v>
       </c>
       <c r="B794" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B795" t="s">
         <v>1352</v>
@@ -12738,20 +12738,20 @@
         <v>1353</v>
       </c>
       <c r="B796" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B797" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B798" t="s">
         <v>1356</v>
@@ -12762,36 +12762,36 @@
         <v>1357</v>
       </c>
       <c r="B799" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B800" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B801" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B802" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B803" t="s">
         <v>1362</v>
@@ -12802,20 +12802,20 @@
         <v>1363</v>
       </c>
       <c r="B804" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B805" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B806" t="s">
         <v>1366</v>
@@ -12874,28 +12874,28 @@
         <v>1379</v>
       </c>
       <c r="B813" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B814" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B815" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B816" t="s">
         <v>1383</v>
@@ -12954,12 +12954,12 @@
         <v>1396</v>
       </c>
       <c r="B823" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B824" t="s">
         <v>1398</v>
@@ -12978,12 +12978,12 @@
         <v>1401</v>
       </c>
       <c r="B826" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B827" t="s">
         <v>1403</v>
@@ -13010,12 +13010,12 @@
         <v>1408</v>
       </c>
       <c r="B830" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B831" t="s">
         <v>1410</v>
@@ -13026,12 +13026,12 @@
         <v>1411</v>
       </c>
       <c r="B832" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B833" t="s">
         <v>1413</v>
@@ -13042,12 +13042,12 @@
         <v>1414</v>
       </c>
       <c r="B834" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B835" t="s">
         <v>1416</v>
@@ -13058,12 +13058,12 @@
         <v>1417</v>
       </c>
       <c r="B836" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B837" t="s">
         <v>1419</v>
@@ -13074,36 +13074,36 @@
         <v>1420</v>
       </c>
       <c r="B838" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B839" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B840" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B841" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B842" t="s">
         <v>1425</v>
@@ -13122,12 +13122,12 @@
         <v>1428</v>
       </c>
       <c r="B844" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B845" t="s">
         <v>1430</v>
@@ -13146,12 +13146,12 @@
         <v>1433</v>
       </c>
       <c r="B847" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B848" t="s">
         <v>1435</v>
@@ -13162,36 +13162,36 @@
         <v>1436</v>
       </c>
       <c r="B849" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B850" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B851" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B852" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B853" t="s">
         <v>1441</v>
@@ -13298,28 +13298,28 @@
         <v>1466</v>
       </c>
       <c r="B866" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B867" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B868" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B869" t="s">
         <v>1470</v>
@@ -13330,36 +13330,36 @@
         <v>1471</v>
       </c>
       <c r="B870" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B871" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B872" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B873" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B874" t="s">
         <v>1476</v>
@@ -13370,28 +13370,28 @@
         <v>1477</v>
       </c>
       <c r="B875" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B876" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B877" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B878" t="s">
         <v>1481</v>
@@ -13402,12 +13402,12 @@
         <v>1482</v>
       </c>
       <c r="B879" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B880" t="s">
         <v>1484</v>
@@ -13466,20 +13466,20 @@
         <v>1497</v>
       </c>
       <c r="B887" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B888" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B889" t="s">
         <v>1500</v>
@@ -13506,20 +13506,20 @@
         <v>1505</v>
       </c>
       <c r="B892" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B893" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B894" t="s">
         <v>1508</v>
@@ -13530,12 +13530,12 @@
         <v>1509</v>
       </c>
       <c r="B895" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B896" t="s">
         <v>1511</v>
@@ -13546,12 +13546,12 @@
         <v>1512</v>
       </c>
       <c r="B897" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B898" t="s">
         <v>1514</v>
@@ -13562,12 +13562,12 @@
         <v>1515</v>
       </c>
       <c r="B899" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B900" t="s">
         <v>1517</v>
@@ -13578,12 +13578,12 @@
         <v>1518</v>
       </c>
       <c r="B901" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B902" t="s">
         <v>1520</v>
@@ -13618,12 +13618,12 @@
         <v>1527</v>
       </c>
       <c r="B906" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B907" t="s">
         <v>1529</v>
@@ -13674,60 +13674,60 @@
         <v>1540</v>
       </c>
       <c r="B913" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B914" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B915" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B916" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B917" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B918" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B919" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B920" t="s">
         <v>1548</v>
@@ -13754,28 +13754,28 @@
         <v>1553</v>
       </c>
       <c r="B923" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B924" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B925" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B926" t="s">
         <v>1557</v>
@@ -13818,20 +13818,20 @@
         <v>1566</v>
       </c>
       <c r="B931" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B932" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B933" t="s">
         <v>1569</v>
@@ -13866,12 +13866,12 @@
         <v>1576</v>
       </c>
       <c r="B937" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B938" t="s">
         <v>1578</v>
@@ -13890,12 +13890,12 @@
         <v>1581</v>
       </c>
       <c r="B940" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B941" t="s">
         <v>1583</v>
@@ -13906,12 +13906,12 @@
         <v>1584</v>
       </c>
       <c r="B942" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B943" t="s">
         <v>1586</v>
@@ -13978,28 +13978,28 @@
         <v>1601</v>
       </c>
       <c r="B951" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B952" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B953" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B954" t="s">
         <v>1605</v>
@@ -14018,44 +14018,44 @@
         <v>1608</v>
       </c>
       <c r="B956" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B957" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B958" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B959" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B960" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B961" t="s">
         <v>1614</v>
@@ -14098,20 +14098,20 @@
         <v>1623</v>
       </c>
       <c r="B966" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B967" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B968" t="s">
         <v>1626</v>
@@ -14146,12 +14146,12 @@
         <v>1633</v>
       </c>
       <c r="B972" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B973" t="s">
         <v>1635</v>
@@ -14170,20 +14170,20 @@
         <v>1638</v>
       </c>
       <c r="B975" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B976" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B977" t="s">
         <v>1641</v>
@@ -14282,28 +14282,28 @@
         <v>1664</v>
       </c>
       <c r="B989" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B990" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B991" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B992" t="s">
         <v>1668</v>
@@ -14314,36 +14314,36 @@
         <v>1669</v>
       </c>
       <c r="B993" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B994" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B995" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B996" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B997" t="s">
         <v>1674</v>
@@ -14354,12 +14354,12 @@
         <v>1675</v>
       </c>
       <c r="B998" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B999" t="s">
         <v>1677</v>
@@ -14394,12 +14394,12 @@
         <v>1684</v>
       </c>
       <c r="B1003" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1004" t="s">
         <v>1686</v>
@@ -14418,12 +14418,12 @@
         <v>1689</v>
       </c>
       <c r="B1006" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1007" t="s">
         <v>1691</v>
@@ -14474,20 +14474,20 @@
         <v>1702</v>
       </c>
       <c r="B1013" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1014" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1015" t="s">
         <v>1705</v>
@@ -14514,36 +14514,36 @@
         <v>1710</v>
       </c>
       <c r="B1018" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1019" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1020" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1021" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1022" t="s">
         <v>1715</v>
@@ -14562,12 +14562,12 @@
         <v>1718</v>
       </c>
       <c r="B1024" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1025" t="s">
         <v>1720</v>
@@ -14578,20 +14578,20 @@
         <v>1721</v>
       </c>
       <c r="B1026" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1027" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1028" t="s">
         <v>1724</v>
@@ -14610,12 +14610,12 @@
         <v>1727</v>
       </c>
       <c r="B1030" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1031" t="s">
         <v>1729</v>
@@ -14642,12 +14642,12 @@
         <v>1734</v>
       </c>
       <c r="B1034" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1035" t="s">
         <v>1736</v>
@@ -14658,20 +14658,20 @@
         <v>1737</v>
       </c>
       <c r="B1036" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1037" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1038" t="s">
         <v>1740</v>
@@ -14682,52 +14682,52 @@
         <v>1741</v>
       </c>
       <c r="B1039" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1040" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1041" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1042" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1043" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1044" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1045" t="s">
         <v>1748</v>
@@ -14746,12 +14746,12 @@
         <v>1751</v>
       </c>
       <c r="B1047" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1048" t="s">
         <v>1753</v>
@@ -14778,12 +14778,12 @@
         <v>1758</v>
       </c>
       <c r="B1051" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1052" t="s">
         <v>1760</v>
@@ -14802,12 +14802,12 @@
         <v>1763</v>
       </c>
       <c r="B1054" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B1055" t="s">
         <v>1765</v>
@@ -14930,12 +14930,12 @@
         <v>1794</v>
       </c>
       <c r="B1070" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1071" t="s">
         <v>1796</v>
@@ -15034,12 +15034,12 @@
         <v>1819</v>
       </c>
       <c r="B1083" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1084" t="s">
         <v>1821</v>
@@ -15066,20 +15066,20 @@
         <v>1826</v>
       </c>
       <c r="B1087" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="B1088" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1089" t="s">
         <v>1829</v>
@@ -15090,12 +15090,12 @@
         <v>1830</v>
       </c>
       <c r="B1090" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1091" t="s">
         <v>1832</v>
@@ -15114,12 +15114,12 @@
         <v>1835</v>
       </c>
       <c r="B1093" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1094" t="s">
         <v>1837</v>
@@ -15194,12 +15194,12 @@
         <v>1854</v>
       </c>
       <c r="B1103" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1104" t="s">
         <v>1856</v>
@@ -15242,12 +15242,12 @@
         <v>1865</v>
       </c>
       <c r="B1109" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1110" t="s">
         <v>1867</v>
@@ -15266,20 +15266,20 @@
         <v>1870</v>
       </c>
       <c r="B1112" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1113" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1114" t="s">
         <v>1873</v>
@@ -15290,20 +15290,20 @@
         <v>1874</v>
       </c>
       <c r="B1115" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1116" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B1117" t="s">
         <v>1877</v>
@@ -15354,12 +15354,12 @@
         <v>1888</v>
       </c>
       <c r="B1123" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1124" t="s">
         <v>1890</v>
@@ -15402,12 +15402,12 @@
         <v>1899</v>
       </c>
       <c r="B1129" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1130" t="s">
         <v>1901</v>
@@ -15514,28 +15514,28 @@
         <v>1926</v>
       </c>
       <c r="B1143" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1144" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1145" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1146" t="s">
         <v>1930</v>
@@ -15546,12 +15546,12 @@
         <v>1931</v>
       </c>
       <c r="B1147" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1148" t="s">
         <v>1933</v>
@@ -15570,28 +15570,28 @@
         <v>1936</v>
       </c>
       <c r="B1150" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1151" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1152" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B1153" t="s">
         <v>1940</v>
@@ -15674,12 +15674,12 @@
         <v>1959</v>
       </c>
       <c r="B1163" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="B1164" t="s">
         <v>1961</v>
@@ -15722,20 +15722,20 @@
         <v>1970</v>
       </c>
       <c r="B1169" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="B1170" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="B1171" t="s">
         <v>1973</v>
@@ -15746,12 +15746,12 @@
         <v>1974</v>
       </c>
       <c r="B1172" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1173" t="s">
         <v>1976</v>
@@ -15770,20 +15770,20 @@
         <v>1979</v>
       </c>
       <c r="B1175" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1176" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1177" t="s">
         <v>1982</v>
@@ -15794,36 +15794,36 @@
         <v>1983</v>
       </c>
       <c r="B1178" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1179" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1180" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1181" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1182" t="s">
         <v>1988</v>
@@ -15842,12 +15842,12 @@
         <v>1991</v>
       </c>
       <c r="B1184" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1185" t="s">
         <v>1993</v>
@@ -15866,12 +15866,12 @@
         <v>1996</v>
       </c>
       <c r="B1187" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="B1188" t="s">
         <v>1998</v>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2003">
   <si>
     <t>en</t>
   </si>
@@ -4463,6 +4463,12 @@
   </si>
   <si>
     <t>Predator</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>Prazgodovinska bitja</t>
   </si>
   <si>
     <t>Present</t>
@@ -6366,7 +6372,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13410,12 +13416,12 @@
         <v>1484</v>
       </c>
       <c r="B880" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B881" t="s">
         <v>1486</v>
@@ -13474,20 +13480,20 @@
         <v>1499</v>
       </c>
       <c r="B888" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B889" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B890" t="s">
         <v>1502</v>
@@ -13514,20 +13520,20 @@
         <v>1507</v>
       </c>
       <c r="B893" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B894" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B895" t="s">
         <v>1510</v>
@@ -13538,12 +13544,12 @@
         <v>1511</v>
       </c>
       <c r="B896" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B897" t="s">
         <v>1513</v>
@@ -13554,12 +13560,12 @@
         <v>1514</v>
       </c>
       <c r="B898" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B899" t="s">
         <v>1516</v>
@@ -13570,12 +13576,12 @@
         <v>1517</v>
       </c>
       <c r="B900" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B901" t="s">
         <v>1519</v>
@@ -13586,12 +13592,12 @@
         <v>1520</v>
       </c>
       <c r="B902" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B903" t="s">
         <v>1522</v>
@@ -13626,12 +13632,12 @@
         <v>1529</v>
       </c>
       <c r="B907" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B908" t="s">
         <v>1531</v>
@@ -13682,60 +13688,60 @@
         <v>1542</v>
       </c>
       <c r="B914" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B915" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B916" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B917" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B918" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B919" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B920" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B921" t="s">
         <v>1550</v>
@@ -13762,28 +13768,28 @@
         <v>1555</v>
       </c>
       <c r="B924" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B925" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B926" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B927" t="s">
         <v>1559</v>
@@ -13826,20 +13832,20 @@
         <v>1568</v>
       </c>
       <c r="B932" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B933" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B934" t="s">
         <v>1571</v>
@@ -13874,12 +13880,12 @@
         <v>1578</v>
       </c>
       <c r="B938" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B939" t="s">
         <v>1580</v>
@@ -13898,12 +13904,12 @@
         <v>1583</v>
       </c>
       <c r="B941" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B942" t="s">
         <v>1585</v>
@@ -13914,12 +13920,12 @@
         <v>1586</v>
       </c>
       <c r="B943" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B944" t="s">
         <v>1588</v>
@@ -13986,28 +13992,28 @@
         <v>1603</v>
       </c>
       <c r="B952" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B953" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B954" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B955" t="s">
         <v>1607</v>
@@ -14026,44 +14032,44 @@
         <v>1610</v>
       </c>
       <c r="B957" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B958" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B959" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B960" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B961" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B962" t="s">
         <v>1616</v>
@@ -14106,20 +14112,20 @@
         <v>1625</v>
       </c>
       <c r="B967" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B968" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B969" t="s">
         <v>1628</v>
@@ -14154,12 +14160,12 @@
         <v>1635</v>
       </c>
       <c r="B973" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B974" t="s">
         <v>1637</v>
@@ -14178,20 +14184,20 @@
         <v>1640</v>
       </c>
       <c r="B976" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B977" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B978" t="s">
         <v>1643</v>
@@ -14290,28 +14296,28 @@
         <v>1666</v>
       </c>
       <c r="B990" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B991" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B992" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B993" t="s">
         <v>1670</v>
@@ -14322,36 +14328,36 @@
         <v>1671</v>
       </c>
       <c r="B994" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B995" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B996" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B997" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B998" t="s">
         <v>1676</v>
@@ -14362,12 +14368,12 @@
         <v>1677</v>
       </c>
       <c r="B999" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1000" t="s">
         <v>1679</v>
@@ -14402,12 +14408,12 @@
         <v>1686</v>
       </c>
       <c r="B1004" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1005" t="s">
         <v>1688</v>
@@ -14426,12 +14432,12 @@
         <v>1691</v>
       </c>
       <c r="B1007" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1008" t="s">
         <v>1693</v>
@@ -14482,20 +14488,20 @@
         <v>1704</v>
       </c>
       <c r="B1014" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1015" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1016" t="s">
         <v>1707</v>
@@ -14522,36 +14528,36 @@
         <v>1712</v>
       </c>
       <c r="B1019" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1020" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1021" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1022" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1023" t="s">
         <v>1717</v>
@@ -14570,12 +14576,12 @@
         <v>1720</v>
       </c>
       <c r="B1025" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1026" t="s">
         <v>1722</v>
@@ -14586,20 +14592,20 @@
         <v>1723</v>
       </c>
       <c r="B1027" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1028" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1029" t="s">
         <v>1726</v>
@@ -14618,12 +14624,12 @@
         <v>1729</v>
       </c>
       <c r="B1031" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1032" t="s">
         <v>1731</v>
@@ -14650,12 +14656,12 @@
         <v>1736</v>
       </c>
       <c r="B1035" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1036" t="s">
         <v>1738</v>
@@ -14666,20 +14672,20 @@
         <v>1739</v>
       </c>
       <c r="B1037" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1038" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1039" t="s">
         <v>1742</v>
@@ -14690,52 +14696,52 @@
         <v>1743</v>
       </c>
       <c r="B1040" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1041" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1042" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1043" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1044" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B1045" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1046" t="s">
         <v>1750</v>
@@ -14754,12 +14760,12 @@
         <v>1753</v>
       </c>
       <c r="B1048" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1049" t="s">
         <v>1755</v>
@@ -14786,12 +14792,12 @@
         <v>1760</v>
       </c>
       <c r="B1052" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="B1053" t="s">
         <v>1762</v>
@@ -14810,12 +14816,12 @@
         <v>1765</v>
       </c>
       <c r="B1055" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1056" t="s">
         <v>1767</v>
@@ -14938,12 +14944,12 @@
         <v>1796</v>
       </c>
       <c r="B1071" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1072" t="s">
         <v>1798</v>
@@ -15042,12 +15048,12 @@
         <v>1821</v>
       </c>
       <c r="B1084" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1085" t="s">
         <v>1823</v>
@@ -15074,20 +15080,20 @@
         <v>1828</v>
       </c>
       <c r="B1088" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1089" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="B1090" t="s">
         <v>1831</v>
@@ -15098,12 +15104,12 @@
         <v>1832</v>
       </c>
       <c r="B1091" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1092" t="s">
         <v>1834</v>
@@ -15122,12 +15128,12 @@
         <v>1837</v>
       </c>
       <c r="B1094" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="B1095" t="s">
         <v>1839</v>
@@ -15202,12 +15208,12 @@
         <v>1856</v>
       </c>
       <c r="B1104" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="B1105" t="s">
         <v>1858</v>
@@ -15250,12 +15256,12 @@
         <v>1867</v>
       </c>
       <c r="B1110" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B1111" t="s">
         <v>1869</v>
@@ -15274,20 +15280,20 @@
         <v>1872</v>
       </c>
       <c r="B1113" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1114" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1115" t="s">
         <v>1875</v>
@@ -15298,20 +15304,20 @@
         <v>1876</v>
       </c>
       <c r="B1116" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1117" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1118" t="s">
         <v>1879</v>
@@ -15362,12 +15368,12 @@
         <v>1890</v>
       </c>
       <c r="B1124" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1125" t="s">
         <v>1892</v>
@@ -15410,12 +15416,12 @@
         <v>1901</v>
       </c>
       <c r="B1130" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1131" t="s">
         <v>1903</v>
@@ -15522,28 +15528,28 @@
         <v>1928</v>
       </c>
       <c r="B1144" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1145" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1146" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1147" t="s">
         <v>1932</v>
@@ -15554,12 +15560,12 @@
         <v>1933</v>
       </c>
       <c r="B1148" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1149" t="s">
         <v>1935</v>
@@ -15578,28 +15584,28 @@
         <v>1938</v>
       </c>
       <c r="B1151" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="B1152" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1153" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B1154" t="s">
         <v>1942</v>
@@ -15682,12 +15688,12 @@
         <v>1961</v>
       </c>
       <c r="B1164" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="B1165" t="s">
         <v>1963</v>
@@ -15730,20 +15736,20 @@
         <v>1972</v>
       </c>
       <c r="B1170" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="B1171" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="B1172" t="s">
         <v>1975</v>
@@ -15754,12 +15760,12 @@
         <v>1976</v>
       </c>
       <c r="B1173" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1174" t="s">
         <v>1978</v>
@@ -15778,20 +15784,20 @@
         <v>1981</v>
       </c>
       <c r="B1176" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="B1177" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1178" t="s">
         <v>1984</v>
@@ -15802,36 +15808,36 @@
         <v>1985</v>
       </c>
       <c r="B1179" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1180" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1181" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1182" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1183" t="s">
         <v>1990</v>
@@ -15850,12 +15856,12 @@
         <v>1993</v>
       </c>
       <c r="B1185" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1186" t="s">
         <v>1995</v>
@@ -15874,19 +15880,27 @@
         <v>1998</v>
       </c>
       <c r="B1188" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B1189" t="s">
         <v>2000</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>2002</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2005">
   <si>
     <t>en</t>
   </si>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>Nazaj v prihodnost</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>Backrooms (film)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -6372,7 +6378,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6928,12 +6934,12 @@
         <v>113</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B70" t="s">
         <v>115</v>
@@ -6952,36 +6958,36 @@
         <v>118</v>
       </c>
       <c r="B72" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B74" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B75" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B76" t="s">
         <v>123</v>
@@ -6992,12 +6998,12 @@
         <v>124</v>
       </c>
       <c r="B77" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B78" t="s">
         <v>126</v>
@@ -7016,12 +7022,12 @@
         <v>129</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
         <v>131</v>
@@ -7032,12 +7038,12 @@
         <v>132</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B83" t="s">
         <v>134</v>
@@ -7064,12 +7070,12 @@
         <v>139</v>
       </c>
       <c r="B86" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B87" t="s">
         <v>141</v>
@@ -7104,20 +7110,20 @@
         <v>148</v>
       </c>
       <c r="B91" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B92" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B93" t="s">
         <v>151</v>
@@ -7136,12 +7142,12 @@
         <v>154</v>
       </c>
       <c r="B95" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B96" t="s">
         <v>156</v>
@@ -7152,28 +7158,28 @@
         <v>157</v>
       </c>
       <c r="B97" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B98" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B99" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B100" t="s">
         <v>161</v>
@@ -7216,20 +7222,20 @@
         <v>170</v>
       </c>
       <c r="B105" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B107" t="s">
         <v>173</v>
@@ -7240,12 +7246,12 @@
         <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B109" t="s">
         <v>176</v>
@@ -7272,20 +7278,20 @@
         <v>181</v>
       </c>
       <c r="B112" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B113" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B114" t="s">
         <v>184</v>
@@ -7304,12 +7310,12 @@
         <v>187</v>
       </c>
       <c r="B116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B117" t="s">
         <v>189</v>
@@ -7344,36 +7350,36 @@
         <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B122" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B123" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B124" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B125" t="s">
         <v>201</v>
@@ -7384,12 +7390,12 @@
         <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B127" t="s">
         <v>204</v>
@@ -7424,36 +7430,36 @@
         <v>211</v>
       </c>
       <c r="B131" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B132" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B133" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B134" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B135" t="s">
         <v>216</v>
@@ -7480,12 +7486,12 @@
         <v>221</v>
       </c>
       <c r="B138" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B139" t="s">
         <v>223</v>
@@ -7536,12 +7542,12 @@
         <v>234</v>
       </c>
       <c r="B145" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B146" t="s">
         <v>236</v>
@@ -7576,12 +7582,12 @@
         <v>243</v>
       </c>
       <c r="B150" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B151" t="s">
         <v>245</v>
@@ -7592,20 +7598,20 @@
         <v>246</v>
       </c>
       <c r="B152" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B154" t="s">
         <v>249</v>
@@ -7656,12 +7662,12 @@
         <v>260</v>
       </c>
       <c r="B160" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B161" t="s">
         <v>262</v>
@@ -7728,15 +7734,15 @@
         <v>277</v>
       </c>
       <c r="B169" t="s">
-        <v>225</v>
+        <v>278</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B170" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -7752,12 +7758,12 @@
         <v>282</v>
       </c>
       <c r="B172" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B173" t="s">
         <v>284</v>
@@ -7792,28 +7798,28 @@
         <v>291</v>
       </c>
       <c r="B177" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B178" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B179" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B180" t="s">
         <v>295</v>
@@ -8024,12 +8030,12 @@
         <v>346</v>
       </c>
       <c r="B206" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B207" t="s">
         <v>348</v>
@@ -8048,20 +8054,20 @@
         <v>351</v>
       </c>
       <c r="B209" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B210" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B211" t="s">
         <v>354</v>
@@ -8104,12 +8110,12 @@
         <v>363</v>
       </c>
       <c r="B216" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B217" t="s">
         <v>365</v>
@@ -8128,12 +8134,12 @@
         <v>368</v>
       </c>
       <c r="B219" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B220" t="s">
         <v>370</v>
@@ -8144,12 +8150,12 @@
         <v>371</v>
       </c>
       <c r="B221" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B222" t="s">
         <v>373</v>
@@ -8160,20 +8166,20 @@
         <v>374</v>
       </c>
       <c r="B223" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B224" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B225" t="s">
         <v>377</v>
@@ -8200,20 +8206,20 @@
         <v>382</v>
       </c>
       <c r="B228" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B229" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B230" t="s">
         <v>385</v>
@@ -8232,20 +8238,20 @@
         <v>388</v>
       </c>
       <c r="B232" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B233" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B234" t="s">
         <v>391</v>
@@ -8264,20 +8270,20 @@
         <v>394</v>
       </c>
       <c r="B236" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B237" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B238" t="s">
         <v>397</v>
@@ -8320,36 +8326,36 @@
         <v>406</v>
       </c>
       <c r="B243" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B244" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B245" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B246" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B247" t="s">
         <v>411</v>
@@ -8376,12 +8382,12 @@
         <v>416</v>
       </c>
       <c r="B250" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B251" t="s">
         <v>418</v>
@@ -8392,12 +8398,12 @@
         <v>419</v>
       </c>
       <c r="B252" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B253" t="s">
         <v>421</v>
@@ -8408,20 +8414,20 @@
         <v>422</v>
       </c>
       <c r="B254" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B255" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B256" t="s">
         <v>425</v>
@@ -8432,12 +8438,12 @@
         <v>426</v>
       </c>
       <c r="B257" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B258" t="s">
         <v>428</v>
@@ -8504,20 +8510,20 @@
         <v>443</v>
       </c>
       <c r="B266" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B267" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B268" t="s">
         <v>446</v>
@@ -8536,44 +8542,44 @@
         <v>449</v>
       </c>
       <c r="B270" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B271" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B272" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B273" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B275" t="s">
         <v>455</v>
@@ -8584,20 +8590,20 @@
         <v>456</v>
       </c>
       <c r="B276" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B277" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B278" t="s">
         <v>459</v>
@@ -8640,20 +8646,20 @@
         <v>468</v>
       </c>
       <c r="B283" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B284" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B285" t="s">
         <v>471</v>
@@ -8664,20 +8670,20 @@
         <v>472</v>
       </c>
       <c r="B286" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B287" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B288" t="s">
         <v>475</v>
@@ -8704,12 +8710,12 @@
         <v>480</v>
       </c>
       <c r="B291" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B292" t="s">
         <v>482</v>
@@ -8744,20 +8750,20 @@
         <v>489</v>
       </c>
       <c r="B296" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B297" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B298" t="s">
         <v>492</v>
@@ -8784,20 +8790,20 @@
         <v>497</v>
       </c>
       <c r="B301" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B302" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B303" t="s">
         <v>500</v>
@@ -8808,12 +8814,12 @@
         <v>501</v>
       </c>
       <c r="B304" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B305" t="s">
         <v>503</v>
@@ -8856,20 +8862,20 @@
         <v>512</v>
       </c>
       <c r="B310" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B311" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B312" t="s">
         <v>515</v>
@@ -8888,20 +8894,20 @@
         <v>518</v>
       </c>
       <c r="B314" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B315" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B316" t="s">
         <v>521</v>
@@ -8912,20 +8918,20 @@
         <v>522</v>
       </c>
       <c r="B317" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B318" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B319" t="s">
         <v>525</v>
@@ -8936,36 +8942,36 @@
         <v>526</v>
       </c>
       <c r="B320" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B321" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B322" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B323" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B324" t="s">
         <v>531</v>
@@ -8992,20 +8998,20 @@
         <v>536</v>
       </c>
       <c r="B327" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B328" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B329" t="s">
         <v>539</v>
@@ -9040,12 +9046,12 @@
         <v>546</v>
       </c>
       <c r="B333" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B334" t="s">
         <v>548</v>
@@ -9112,12 +9118,12 @@
         <v>563</v>
       </c>
       <c r="B342" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B343" t="s">
         <v>565</v>
@@ -9136,12 +9142,12 @@
         <v>568</v>
       </c>
       <c r="B345" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B346" t="s">
         <v>570</v>
@@ -9304,12 +9310,12 @@
         <v>609</v>
       </c>
       <c r="B366" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B367" t="s">
         <v>611</v>
@@ -9840,20 +9846,20 @@
         <v>742</v>
       </c>
       <c r="B433" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B434" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B435" t="s">
         <v>745</v>
@@ -9864,20 +9870,20 @@
         <v>746</v>
       </c>
       <c r="B436" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B437" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B438" t="s">
         <v>749</v>
@@ -9952,12 +9958,12 @@
         <v>766</v>
       </c>
       <c r="B447" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B448" t="s">
         <v>768</v>
@@ -9968,12 +9974,12 @@
         <v>769</v>
       </c>
       <c r="B449" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B450" t="s">
         <v>771</v>
@@ -9984,12 +9990,12 @@
         <v>772</v>
       </c>
       <c r="B451" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B452" t="s">
         <v>774</v>
@@ -10024,20 +10030,20 @@
         <v>781</v>
       </c>
       <c r="B456" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B457" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B458" t="s">
         <v>784</v>
@@ -10064,12 +10070,12 @@
         <v>789</v>
       </c>
       <c r="B461" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B462" t="s">
         <v>791</v>
@@ -10104,36 +10110,36 @@
         <v>798</v>
       </c>
       <c r="B466" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B467" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B468" t="s">
-        <v>525</v>
+        <v>801</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B469" t="s">
-        <v>801</v>
+        <v>527</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B470" t="s">
         <v>803</v>
@@ -10144,12 +10150,12 @@
         <v>804</v>
       </c>
       <c r="B471" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B472" t="s">
         <v>806</v>
@@ -10168,36 +10174,36 @@
         <v>809</v>
       </c>
       <c r="B474" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B475" t="s">
-        <v>525</v>
+        <v>811</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B476" t="s">
-        <v>811</v>
+        <v>527</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B477" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B478" t="s">
         <v>814</v>
@@ -10208,12 +10214,12 @@
         <v>815</v>
       </c>
       <c r="B479" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B480" t="s">
         <v>817</v>
@@ -10248,20 +10254,20 @@
         <v>824</v>
       </c>
       <c r="B484" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B485" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B486" t="s">
         <v>827</v>
@@ -10272,12 +10278,12 @@
         <v>828</v>
       </c>
       <c r="B487" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B488" t="s">
         <v>830</v>
@@ -10288,36 +10294,36 @@
         <v>831</v>
       </c>
       <c r="B489" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B490" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B491" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B492" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B493" t="s">
         <v>836</v>
@@ -10472,12 +10478,12 @@
         <v>873</v>
       </c>
       <c r="B512" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B513" t="s">
         <v>875</v>
@@ -10496,12 +10502,12 @@
         <v>878</v>
       </c>
       <c r="B515" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B516" t="s">
         <v>880</v>
@@ -10552,20 +10558,20 @@
         <v>891</v>
       </c>
       <c r="B522" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B523" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B524" t="s">
         <v>894</v>
@@ -10648,12 +10654,12 @@
         <v>913</v>
       </c>
       <c r="B534" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B535" t="s">
         <v>915</v>
@@ -10672,20 +10678,20 @@
         <v>918</v>
       </c>
       <c r="B537" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B538" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B539" t="s">
         <v>921</v>
@@ -10704,28 +10710,28 @@
         <v>924</v>
       </c>
       <c r="B541" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B542" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B543" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B544" t="s">
         <v>928</v>
@@ -10760,20 +10766,20 @@
         <v>935</v>
       </c>
       <c r="B548" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B549" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B550" t="s">
         <v>938</v>
@@ -10792,20 +10798,20 @@
         <v>941</v>
       </c>
       <c r="B552" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B553" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B554" t="s">
         <v>944</v>
@@ -10832,12 +10838,12 @@
         <v>949</v>
       </c>
       <c r="B557" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B558" t="s">
         <v>951</v>
@@ -10896,28 +10902,28 @@
         <v>964</v>
       </c>
       <c r="B565" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B566" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B567" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B568" t="s">
         <v>968</v>
@@ -10936,12 +10942,12 @@
         <v>971</v>
       </c>
       <c r="B570" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B571" t="s">
         <v>973</v>
@@ -10992,12 +10998,12 @@
         <v>984</v>
       </c>
       <c r="B577" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B578" t="s">
         <v>986</v>
@@ -11008,36 +11014,36 @@
         <v>987</v>
       </c>
       <c r="B579" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B580" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B581" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B582" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B583" t="s">
         <v>992</v>
@@ -11056,12 +11062,12 @@
         <v>995</v>
       </c>
       <c r="B585" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B586" t="s">
         <v>997</v>
@@ -11160,12 +11166,12 @@
         <v>1020</v>
       </c>
       <c r="B598" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B599" t="s">
         <v>1022</v>
@@ -11176,12 +11182,12 @@
         <v>1023</v>
       </c>
       <c r="B600" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B601" t="s">
         <v>1025</v>
@@ -11248,20 +11254,20 @@
         <v>1040</v>
       </c>
       <c r="B609" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B610" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B611" t="s">
         <v>1043</v>
@@ -11272,12 +11278,12 @@
         <v>1044</v>
       </c>
       <c r="B612" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B613" t="s">
         <v>1046</v>
@@ -11328,12 +11334,12 @@
         <v>1057</v>
       </c>
       <c r="B619" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B620" t="s">
         <v>1059</v>
@@ -11352,12 +11358,12 @@
         <v>1062</v>
       </c>
       <c r="B622" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B623" t="s">
         <v>1064</v>
@@ -11384,12 +11390,12 @@
         <v>1069</v>
       </c>
       <c r="B626" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B627" t="s">
         <v>1071</v>
@@ -11400,12 +11406,12 @@
         <v>1072</v>
       </c>
       <c r="B628" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B629" t="s">
         <v>1074</v>
@@ -11424,12 +11430,12 @@
         <v>1077</v>
       </c>
       <c r="B631" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B632" t="s">
         <v>1079</v>
@@ -11456,44 +11462,44 @@
         <v>1084</v>
       </c>
       <c r="B635" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B636" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B637" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B638" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B639" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B640" t="s">
         <v>1090</v>
@@ -11512,28 +11518,28 @@
         <v>1093</v>
       </c>
       <c r="B642" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B643" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B644" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B645" t="s">
         <v>1097</v>
@@ -11544,12 +11550,12 @@
         <v>1098</v>
       </c>
       <c r="B646" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B647" t="s">
         <v>1100</v>
@@ -11560,12 +11566,12 @@
         <v>1101</v>
       </c>
       <c r="B648" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B649" t="s">
         <v>1103</v>
@@ -11576,20 +11582,20 @@
         <v>1104</v>
       </c>
       <c r="B650" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B651" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B652" t="s">
         <v>1107</v>
@@ -11624,28 +11630,28 @@
         <v>1114</v>
       </c>
       <c r="B656" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B657" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B658" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B659" t="s">
         <v>1118</v>
@@ -11656,12 +11662,12 @@
         <v>1119</v>
       </c>
       <c r="B660" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B661" t="s">
         <v>1121</v>
@@ -11688,12 +11694,12 @@
         <v>1126</v>
       </c>
       <c r="B664" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B665" t="s">
         <v>1128</v>
@@ -11768,12 +11774,12 @@
         <v>1145</v>
       </c>
       <c r="B674" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B675" t="s">
         <v>1147</v>
@@ -11856,12 +11862,12 @@
         <v>1166</v>
       </c>
       <c r="B685" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B686" t="s">
         <v>1168</v>
@@ -11888,20 +11894,20 @@
         <v>1173</v>
       </c>
       <c r="B689" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B690" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B691" t="s">
         <v>1176</v>
@@ -11984,12 +11990,12 @@
         <v>1195</v>
       </c>
       <c r="B701" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B702" t="s">
         <v>1197</v>
@@ -12032,12 +12038,12 @@
         <v>1206</v>
       </c>
       <c r="B707" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B708" t="s">
         <v>1208</v>
@@ -12048,20 +12054,20 @@
         <v>1209</v>
       </c>
       <c r="B709" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B710" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B711" t="s">
         <v>1212</v>
@@ -12072,28 +12078,28 @@
         <v>1213</v>
       </c>
       <c r="B712" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B713" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B714" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B715" t="s">
         <v>1217</v>
@@ -12112,20 +12118,20 @@
         <v>1220</v>
       </c>
       <c r="B717" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B718" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B719" t="s">
         <v>1223</v>
@@ -12152,20 +12158,20 @@
         <v>1228</v>
       </c>
       <c r="B722" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B723" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B724" t="s">
         <v>1231</v>
@@ -12184,12 +12190,12 @@
         <v>1234</v>
       </c>
       <c r="B726" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B727" t="s">
         <v>1236</v>
@@ -12224,20 +12230,20 @@
         <v>1243</v>
       </c>
       <c r="B731" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B732" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B733" t="s">
         <v>1246</v>
@@ -12256,20 +12262,20 @@
         <v>1249</v>
       </c>
       <c r="B735" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B736" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B737" t="s">
         <v>1252</v>
@@ -12280,12 +12286,12 @@
         <v>1253</v>
       </c>
       <c r="B738" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B739" t="s">
         <v>1255</v>
@@ -12312,12 +12318,12 @@
         <v>1260</v>
       </c>
       <c r="B742" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B743" t="s">
         <v>1262</v>
@@ -12336,12 +12342,12 @@
         <v>1265</v>
       </c>
       <c r="B745" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B746" t="s">
         <v>1267</v>
@@ -12368,20 +12374,20 @@
         <v>1272</v>
       </c>
       <c r="B749" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B750" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B751" t="s">
         <v>1275</v>
@@ -12400,20 +12406,20 @@
         <v>1278</v>
       </c>
       <c r="B753" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B754" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B755" t="s">
         <v>1281</v>
@@ -12512,12 +12518,12 @@
         <v>1304</v>
       </c>
       <c r="B767" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B768" t="s">
         <v>1306</v>
@@ -12528,20 +12534,20 @@
         <v>1307</v>
       </c>
       <c r="B769" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B770" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B771" t="s">
         <v>1310</v>
@@ -12584,12 +12590,12 @@
         <v>1319</v>
       </c>
       <c r="B776" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B777" t="s">
         <v>1321</v>
@@ -12688,36 +12694,36 @@
         <v>1344</v>
       </c>
       <c r="B789" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B790" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B791" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B792" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B793" t="s">
         <v>1349</v>
@@ -12736,12 +12742,12 @@
         <v>1352</v>
       </c>
       <c r="B795" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B796" t="s">
         <v>1354</v>
@@ -12752,20 +12758,20 @@
         <v>1355</v>
       </c>
       <c r="B797" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B798" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B799" t="s">
         <v>1358</v>
@@ -12776,36 +12782,36 @@
         <v>1359</v>
       </c>
       <c r="B800" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B801" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B802" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B803" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B804" t="s">
         <v>1364</v>
@@ -12816,20 +12822,20 @@
         <v>1365</v>
       </c>
       <c r="B805" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B806" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B807" t="s">
         <v>1368</v>
@@ -12888,28 +12894,28 @@
         <v>1381</v>
       </c>
       <c r="B814" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B815" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B816" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B817" t="s">
         <v>1385</v>
@@ -12968,12 +12974,12 @@
         <v>1398</v>
       </c>
       <c r="B824" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B825" t="s">
         <v>1400</v>
@@ -12992,12 +12998,12 @@
         <v>1403</v>
       </c>
       <c r="B827" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B828" t="s">
         <v>1405</v>
@@ -13024,12 +13030,12 @@
         <v>1410</v>
       </c>
       <c r="B831" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B832" t="s">
         <v>1412</v>
@@ -13040,12 +13046,12 @@
         <v>1413</v>
       </c>
       <c r="B833" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B834" t="s">
         <v>1415</v>
@@ -13056,12 +13062,12 @@
         <v>1416</v>
       </c>
       <c r="B835" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B836" t="s">
         <v>1418</v>
@@ -13072,12 +13078,12 @@
         <v>1419</v>
       </c>
       <c r="B837" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B838" t="s">
         <v>1421</v>
@@ -13088,36 +13094,36 @@
         <v>1422</v>
       </c>
       <c r="B839" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B840" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B841" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B842" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B843" t="s">
         <v>1427</v>
@@ -13136,12 +13142,12 @@
         <v>1430</v>
       </c>
       <c r="B845" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B846" t="s">
         <v>1432</v>
@@ -13160,12 +13166,12 @@
         <v>1435</v>
       </c>
       <c r="B848" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B849" t="s">
         <v>1437</v>
@@ -13176,36 +13182,36 @@
         <v>1438</v>
       </c>
       <c r="B850" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B851" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B852" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B853" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B854" t="s">
         <v>1443</v>
@@ -13312,28 +13318,28 @@
         <v>1468</v>
       </c>
       <c r="B867" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B868" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B869" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B870" t="s">
         <v>1472</v>
@@ -13344,36 +13350,36 @@
         <v>1473</v>
       </c>
       <c r="B871" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B872" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B873" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B874" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B875" t="s">
         <v>1478</v>
@@ -13384,28 +13390,28 @@
         <v>1479</v>
       </c>
       <c r="B876" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B877" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B878" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B879" t="s">
         <v>1483</v>
@@ -13424,12 +13430,12 @@
         <v>1486</v>
       </c>
       <c r="B881" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B882" t="s">
         <v>1488</v>
@@ -13488,20 +13494,20 @@
         <v>1501</v>
       </c>
       <c r="B889" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B890" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B891" t="s">
         <v>1504</v>
@@ -13528,20 +13534,20 @@
         <v>1509</v>
       </c>
       <c r="B894" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B895" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B896" t="s">
         <v>1512</v>
@@ -13552,12 +13558,12 @@
         <v>1513</v>
       </c>
       <c r="B897" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B898" t="s">
         <v>1515</v>
@@ -13568,12 +13574,12 @@
         <v>1516</v>
       </c>
       <c r="B899" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B900" t="s">
         <v>1518</v>
@@ -13584,12 +13590,12 @@
         <v>1519</v>
       </c>
       <c r="B901" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B902" t="s">
         <v>1521</v>
@@ -13600,12 +13606,12 @@
         <v>1522</v>
       </c>
       <c r="B903" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B904" t="s">
         <v>1524</v>
@@ -13640,12 +13646,12 @@
         <v>1531</v>
       </c>
       <c r="B908" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B909" t="s">
         <v>1533</v>
@@ -13696,60 +13702,60 @@
         <v>1544</v>
       </c>
       <c r="B915" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B916" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B917" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B918" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B919" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B920" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B921" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B922" t="s">
         <v>1552</v>
@@ -13776,28 +13782,28 @@
         <v>1557</v>
       </c>
       <c r="B925" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B926" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B927" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B928" t="s">
         <v>1561</v>
@@ -13840,20 +13846,20 @@
         <v>1570</v>
       </c>
       <c r="B933" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B934" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B935" t="s">
         <v>1573</v>
@@ -13888,12 +13894,12 @@
         <v>1580</v>
       </c>
       <c r="B939" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B940" t="s">
         <v>1582</v>
@@ -13912,12 +13918,12 @@
         <v>1585</v>
       </c>
       <c r="B942" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B943" t="s">
         <v>1587</v>
@@ -13928,12 +13934,12 @@
         <v>1588</v>
       </c>
       <c r="B944" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B945" t="s">
         <v>1590</v>
@@ -14000,28 +14006,28 @@
         <v>1605</v>
       </c>
       <c r="B953" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B954" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B955" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B956" t="s">
         <v>1609</v>
@@ -14040,44 +14046,44 @@
         <v>1612</v>
       </c>
       <c r="B958" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B959" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B960" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B961" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B962" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B963" t="s">
         <v>1618</v>
@@ -14120,20 +14126,20 @@
         <v>1627</v>
       </c>
       <c r="B968" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B969" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B970" t="s">
         <v>1630</v>
@@ -14168,12 +14174,12 @@
         <v>1637</v>
       </c>
       <c r="B974" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B975" t="s">
         <v>1639</v>
@@ -14192,20 +14198,20 @@
         <v>1642</v>
       </c>
       <c r="B977" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B978" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B979" t="s">
         <v>1645</v>
@@ -14304,28 +14310,28 @@
         <v>1668</v>
       </c>
       <c r="B991" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B992" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B993" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B994" t="s">
         <v>1672</v>
@@ -14336,36 +14342,36 @@
         <v>1673</v>
       </c>
       <c r="B995" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B996" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B997" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B998" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B999" t="s">
         <v>1678</v>
@@ -14376,12 +14382,12 @@
         <v>1679</v>
       </c>
       <c r="B1000" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1001" t="s">
         <v>1681</v>
@@ -14416,12 +14422,12 @@
         <v>1688</v>
       </c>
       <c r="B1005" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1006" t="s">
         <v>1690</v>
@@ -14440,12 +14446,12 @@
         <v>1693</v>
       </c>
       <c r="B1008" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1009" t="s">
         <v>1695</v>
@@ -14496,20 +14502,20 @@
         <v>1706</v>
       </c>
       <c r="B1015" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1016" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1017" t="s">
         <v>1709</v>
@@ -14536,36 +14542,36 @@
         <v>1714</v>
       </c>
       <c r="B1020" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1021" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1022" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1023" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1024" t="s">
         <v>1719</v>
@@ -14584,12 +14590,12 @@
         <v>1722</v>
       </c>
       <c r="B1026" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1027" t="s">
         <v>1724</v>
@@ -14600,20 +14606,20 @@
         <v>1725</v>
       </c>
       <c r="B1028" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1029" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1030" t="s">
         <v>1728</v>
@@ -14632,12 +14638,12 @@
         <v>1731</v>
       </c>
       <c r="B1032" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1033" t="s">
         <v>1733</v>
@@ -14664,12 +14670,12 @@
         <v>1738</v>
       </c>
       <c r="B1036" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1037" t="s">
         <v>1740</v>
@@ -14680,20 +14686,20 @@
         <v>1741</v>
       </c>
       <c r="B1038" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1039" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1040" t="s">
         <v>1744</v>
@@ -14704,52 +14710,52 @@
         <v>1745</v>
       </c>
       <c r="B1041" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1042" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1043" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B1044" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1045" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1046" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1047" t="s">
         <v>1752</v>
@@ -14768,12 +14774,12 @@
         <v>1755</v>
       </c>
       <c r="B1049" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B1050" t="s">
         <v>1757</v>
@@ -14800,12 +14806,12 @@
         <v>1762</v>
       </c>
       <c r="B1053" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B1054" t="s">
         <v>1764</v>
@@ -14824,12 +14830,12 @@
         <v>1767</v>
       </c>
       <c r="B1056" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B1057" t="s">
         <v>1769</v>
@@ -14952,12 +14958,12 @@
         <v>1798</v>
       </c>
       <c r="B1072" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1073" t="s">
         <v>1800</v>
@@ -15056,12 +15062,12 @@
         <v>1823</v>
       </c>
       <c r="B1085" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1086" t="s">
         <v>1825</v>
@@ -15088,20 +15094,20 @@
         <v>1830</v>
       </c>
       <c r="B1089" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1090" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="B1091" t="s">
         <v>1833</v>
@@ -15112,12 +15118,12 @@
         <v>1834</v>
       </c>
       <c r="B1092" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1093" t="s">
         <v>1836</v>
@@ -15136,12 +15142,12 @@
         <v>1839</v>
       </c>
       <c r="B1095" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1096" t="s">
         <v>1841</v>
@@ -15216,12 +15222,12 @@
         <v>1858</v>
       </c>
       <c r="B1105" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1106" t="s">
         <v>1860</v>
@@ -15264,12 +15270,12 @@
         <v>1869</v>
       </c>
       <c r="B1111" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1112" t="s">
         <v>1871</v>
@@ -15288,20 +15294,20 @@
         <v>1874</v>
       </c>
       <c r="B1114" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1115" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B1116" t="s">
         <v>1877</v>
@@ -15312,20 +15318,20 @@
         <v>1878</v>
       </c>
       <c r="B1117" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B1118" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1119" t="s">
         <v>1881</v>
@@ -15376,12 +15382,12 @@
         <v>1892</v>
       </c>
       <c r="B1125" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1126" t="s">
         <v>1894</v>
@@ -15424,12 +15430,12 @@
         <v>1903</v>
       </c>
       <c r="B1131" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1132" t="s">
         <v>1905</v>
@@ -15536,28 +15542,28 @@
         <v>1930</v>
       </c>
       <c r="B1145" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1146" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1147" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1148" t="s">
         <v>1934</v>
@@ -15568,12 +15574,12 @@
         <v>1935</v>
       </c>
       <c r="B1149" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B1150" t="s">
         <v>1937</v>
@@ -15592,28 +15598,28 @@
         <v>1940</v>
       </c>
       <c r="B1152" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="B1153" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="B1154" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B1155" t="s">
         <v>1944</v>
@@ -15696,12 +15702,12 @@
         <v>1963</v>
       </c>
       <c r="B1165" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="B1166" t="s">
         <v>1965</v>
@@ -15744,20 +15750,20 @@
         <v>1974</v>
       </c>
       <c r="B1171" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="B1172" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="B1173" t="s">
         <v>1977</v>
@@ -15768,12 +15774,12 @@
         <v>1978</v>
       </c>
       <c r="B1174" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1175" t="s">
         <v>1980</v>
@@ -15792,20 +15798,20 @@
         <v>1983</v>
       </c>
       <c r="B1177" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="B1178" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="B1179" t="s">
         <v>1986</v>
@@ -15816,36 +15822,36 @@
         <v>1987</v>
       </c>
       <c r="B1180" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1181" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1182" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1183" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B1184" t="s">
         <v>1992</v>
@@ -15864,12 +15870,12 @@
         <v>1995</v>
       </c>
       <c r="B1186" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="B1187" t="s">
         <v>1997</v>
@@ -15888,19 +15894,27 @@
         <v>2000</v>
       </c>
       <c r="B1189" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B1190" t="s">
         <v>2002</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>2004</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2007">
   <si>
     <t>en</t>
   </si>
@@ -1292,6 +1292,12 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>Matrica smrti</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -6378,7 +6384,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8430,12 +8436,12 @@
         <v>425</v>
       </c>
       <c r="B256" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B257" t="s">
         <v>427</v>
@@ -8446,12 +8452,12 @@
         <v>428</v>
       </c>
       <c r="B258" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B259" t="s">
         <v>430</v>
@@ -8518,20 +8524,20 @@
         <v>445</v>
       </c>
       <c r="B267" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B268" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B269" t="s">
         <v>448</v>
@@ -8550,44 +8556,44 @@
         <v>451</v>
       </c>
       <c r="B271" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B272" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B273" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B274" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B275" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B276" t="s">
         <v>457</v>
@@ -8598,20 +8604,20 @@
         <v>458</v>
       </c>
       <c r="B277" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B278" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B279" t="s">
         <v>461</v>
@@ -8654,20 +8660,20 @@
         <v>470</v>
       </c>
       <c r="B284" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B285" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B286" t="s">
         <v>473</v>
@@ -8678,20 +8684,20 @@
         <v>474</v>
       </c>
       <c r="B287" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B288" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B289" t="s">
         <v>477</v>
@@ -8718,12 +8724,12 @@
         <v>482</v>
       </c>
       <c r="B292" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B293" t="s">
         <v>484</v>
@@ -8758,20 +8764,20 @@
         <v>491</v>
       </c>
       <c r="B297" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B298" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B299" t="s">
         <v>494</v>
@@ -8798,20 +8804,20 @@
         <v>499</v>
       </c>
       <c r="B302" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B303" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B304" t="s">
         <v>502</v>
@@ -8822,12 +8828,12 @@
         <v>503</v>
       </c>
       <c r="B305" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B306" t="s">
         <v>505</v>
@@ -8870,20 +8876,20 @@
         <v>514</v>
       </c>
       <c r="B311" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B312" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B313" t="s">
         <v>517</v>
@@ -8902,20 +8908,20 @@
         <v>520</v>
       </c>
       <c r="B315" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B316" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B317" t="s">
         <v>523</v>
@@ -8926,20 +8932,20 @@
         <v>524</v>
       </c>
       <c r="B318" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B319" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B320" t="s">
         <v>527</v>
@@ -8950,36 +8956,36 @@
         <v>528</v>
       </c>
       <c r="B321" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B322" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B323" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B324" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B325" t="s">
         <v>533</v>
@@ -9006,20 +9012,20 @@
         <v>538</v>
       </c>
       <c r="B328" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B329" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B330" t="s">
         <v>541</v>
@@ -9054,12 +9060,12 @@
         <v>548</v>
       </c>
       <c r="B334" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B335" t="s">
         <v>550</v>
@@ -9126,12 +9132,12 @@
         <v>565</v>
       </c>
       <c r="B343" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B344" t="s">
         <v>567</v>
@@ -9150,12 +9156,12 @@
         <v>570</v>
       </c>
       <c r="B346" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B347" t="s">
         <v>572</v>
@@ -9318,12 +9324,12 @@
         <v>611</v>
       </c>
       <c r="B367" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B368" t="s">
         <v>613</v>
@@ -9854,20 +9860,20 @@
         <v>744</v>
       </c>
       <c r="B434" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B435" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B436" t="s">
         <v>747</v>
@@ -9878,20 +9884,20 @@
         <v>748</v>
       </c>
       <c r="B437" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B438" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B439" t="s">
         <v>751</v>
@@ -9966,12 +9972,12 @@
         <v>768</v>
       </c>
       <c r="B448" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B449" t="s">
         <v>770</v>
@@ -9982,12 +9988,12 @@
         <v>771</v>
       </c>
       <c r="B450" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B451" t="s">
         <v>773</v>
@@ -9998,12 +10004,12 @@
         <v>774</v>
       </c>
       <c r="B452" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B453" t="s">
         <v>776</v>
@@ -10038,20 +10044,20 @@
         <v>783</v>
       </c>
       <c r="B457" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B458" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B459" t="s">
         <v>786</v>
@@ -10078,12 +10084,12 @@
         <v>791</v>
       </c>
       <c r="B462" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B463" t="s">
         <v>793</v>
@@ -10118,36 +10124,36 @@
         <v>800</v>
       </c>
       <c r="B467" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B468" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B469" t="s">
-        <v>527</v>
+        <v>803</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B470" t="s">
-        <v>803</v>
+        <v>529</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B471" t="s">
         <v>805</v>
@@ -10158,12 +10164,12 @@
         <v>806</v>
       </c>
       <c r="B472" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B473" t="s">
         <v>808</v>
@@ -10182,36 +10188,36 @@
         <v>811</v>
       </c>
       <c r="B475" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B476" t="s">
-        <v>527</v>
+        <v>813</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B477" t="s">
-        <v>813</v>
+        <v>529</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B478" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B479" t="s">
         <v>816</v>
@@ -10222,12 +10228,12 @@
         <v>817</v>
       </c>
       <c r="B480" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B481" t="s">
         <v>819</v>
@@ -10262,20 +10268,20 @@
         <v>826</v>
       </c>
       <c r="B485" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B486" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B487" t="s">
         <v>829</v>
@@ -10286,12 +10292,12 @@
         <v>830</v>
       </c>
       <c r="B488" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B489" t="s">
         <v>832</v>
@@ -10302,36 +10308,36 @@
         <v>833</v>
       </c>
       <c r="B490" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B491" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B492" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B493" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B494" t="s">
         <v>838</v>
@@ -10486,12 +10492,12 @@
         <v>875</v>
       </c>
       <c r="B513" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B514" t="s">
         <v>877</v>
@@ -10510,12 +10516,12 @@
         <v>880</v>
       </c>
       <c r="B516" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B517" t="s">
         <v>882</v>
@@ -10566,20 +10572,20 @@
         <v>893</v>
       </c>
       <c r="B523" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B524" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B525" t="s">
         <v>896</v>
@@ -10662,12 +10668,12 @@
         <v>915</v>
       </c>
       <c r="B535" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B536" t="s">
         <v>917</v>
@@ -10686,20 +10692,20 @@
         <v>920</v>
       </c>
       <c r="B538" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B539" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B540" t="s">
         <v>923</v>
@@ -10718,28 +10724,28 @@
         <v>926</v>
       </c>
       <c r="B542" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B543" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B544" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B545" t="s">
         <v>930</v>
@@ -10774,20 +10780,20 @@
         <v>937</v>
       </c>
       <c r="B549" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B550" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B551" t="s">
         <v>940</v>
@@ -10806,20 +10812,20 @@
         <v>943</v>
       </c>
       <c r="B553" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B554" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B555" t="s">
         <v>946</v>
@@ -10846,12 +10852,12 @@
         <v>951</v>
       </c>
       <c r="B558" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B559" t="s">
         <v>953</v>
@@ -10910,28 +10916,28 @@
         <v>966</v>
       </c>
       <c r="B566" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B567" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B568" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B569" t="s">
         <v>970</v>
@@ -10950,12 +10956,12 @@
         <v>973</v>
       </c>
       <c r="B571" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B572" t="s">
         <v>975</v>
@@ -11006,12 +11012,12 @@
         <v>986</v>
       </c>
       <c r="B578" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B579" t="s">
         <v>988</v>
@@ -11022,36 +11028,36 @@
         <v>989</v>
       </c>
       <c r="B580" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B581" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B582" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B583" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B584" t="s">
         <v>994</v>
@@ -11070,12 +11076,12 @@
         <v>997</v>
       </c>
       <c r="B586" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B587" t="s">
         <v>999</v>
@@ -11174,12 +11180,12 @@
         <v>1022</v>
       </c>
       <c r="B599" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B600" t="s">
         <v>1024</v>
@@ -11190,12 +11196,12 @@
         <v>1025</v>
       </c>
       <c r="B601" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B602" t="s">
         <v>1027</v>
@@ -11262,20 +11268,20 @@
         <v>1042</v>
       </c>
       <c r="B610" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B611" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B612" t="s">
         <v>1045</v>
@@ -11286,12 +11292,12 @@
         <v>1046</v>
       </c>
       <c r="B613" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B614" t="s">
         <v>1048</v>
@@ -11342,12 +11348,12 @@
         <v>1059</v>
       </c>
       <c r="B620" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B621" t="s">
         <v>1061</v>
@@ -11366,12 +11372,12 @@
         <v>1064</v>
       </c>
       <c r="B623" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B624" t="s">
         <v>1066</v>
@@ -11398,12 +11404,12 @@
         <v>1071</v>
       </c>
       <c r="B627" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B628" t="s">
         <v>1073</v>
@@ -11414,12 +11420,12 @@
         <v>1074</v>
       </c>
       <c r="B629" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B630" t="s">
         <v>1076</v>
@@ -11438,12 +11444,12 @@
         <v>1079</v>
       </c>
       <c r="B632" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B633" t="s">
         <v>1081</v>
@@ -11470,44 +11476,44 @@
         <v>1086</v>
       </c>
       <c r="B636" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B637" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B638" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B639" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B640" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B641" t="s">
         <v>1092</v>
@@ -11526,28 +11532,28 @@
         <v>1095</v>
       </c>
       <c r="B643" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B644" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B645" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B646" t="s">
         <v>1099</v>
@@ -11558,12 +11564,12 @@
         <v>1100</v>
       </c>
       <c r="B647" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B648" t="s">
         <v>1102</v>
@@ -11574,12 +11580,12 @@
         <v>1103</v>
       </c>
       <c r="B649" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B650" t="s">
         <v>1105</v>
@@ -11590,20 +11596,20 @@
         <v>1106</v>
       </c>
       <c r="B651" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B652" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B653" t="s">
         <v>1109</v>
@@ -11638,28 +11644,28 @@
         <v>1116</v>
       </c>
       <c r="B657" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B658" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B659" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B660" t="s">
         <v>1120</v>
@@ -11670,12 +11676,12 @@
         <v>1121</v>
       </c>
       <c r="B661" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B662" t="s">
         <v>1123</v>
@@ -11702,12 +11708,12 @@
         <v>1128</v>
       </c>
       <c r="B665" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B666" t="s">
         <v>1130</v>
@@ -11782,12 +11788,12 @@
         <v>1147</v>
       </c>
       <c r="B675" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B676" t="s">
         <v>1149</v>
@@ -11870,12 +11876,12 @@
         <v>1168</v>
       </c>
       <c r="B686" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B687" t="s">
         <v>1170</v>
@@ -11902,20 +11908,20 @@
         <v>1175</v>
       </c>
       <c r="B690" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B691" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B692" t="s">
         <v>1178</v>
@@ -11998,12 +12004,12 @@
         <v>1197</v>
       </c>
       <c r="B702" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B703" t="s">
         <v>1199</v>
@@ -12046,12 +12052,12 @@
         <v>1208</v>
       </c>
       <c r="B708" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B709" t="s">
         <v>1210</v>
@@ -12062,20 +12068,20 @@
         <v>1211</v>
       </c>
       <c r="B710" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B711" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B712" t="s">
         <v>1214</v>
@@ -12086,28 +12092,28 @@
         <v>1215</v>
       </c>
       <c r="B713" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B714" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B715" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B716" t="s">
         <v>1219</v>
@@ -12126,20 +12132,20 @@
         <v>1222</v>
       </c>
       <c r="B718" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B719" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B720" t="s">
         <v>1225</v>
@@ -12166,20 +12172,20 @@
         <v>1230</v>
       </c>
       <c r="B723" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B724" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B725" t="s">
         <v>1233</v>
@@ -12198,12 +12204,12 @@
         <v>1236</v>
       </c>
       <c r="B727" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B728" t="s">
         <v>1238</v>
@@ -12238,20 +12244,20 @@
         <v>1245</v>
       </c>
       <c r="B732" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B733" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B734" t="s">
         <v>1248</v>
@@ -12270,20 +12276,20 @@
         <v>1251</v>
       </c>
       <c r="B736" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B737" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B738" t="s">
         <v>1254</v>
@@ -12294,12 +12300,12 @@
         <v>1255</v>
       </c>
       <c r="B739" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B740" t="s">
         <v>1257</v>
@@ -12326,12 +12332,12 @@
         <v>1262</v>
       </c>
       <c r="B743" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B744" t="s">
         <v>1264</v>
@@ -12350,12 +12356,12 @@
         <v>1267</v>
       </c>
       <c r="B746" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B747" t="s">
         <v>1269</v>
@@ -12382,20 +12388,20 @@
         <v>1274</v>
       </c>
       <c r="B750" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B751" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B752" t="s">
         <v>1277</v>
@@ -12414,20 +12420,20 @@
         <v>1280</v>
       </c>
       <c r="B754" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B755" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B756" t="s">
         <v>1283</v>
@@ -12526,12 +12532,12 @@
         <v>1306</v>
       </c>
       <c r="B768" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B769" t="s">
         <v>1308</v>
@@ -12542,20 +12548,20 @@
         <v>1309</v>
       </c>
       <c r="B770" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B771" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B772" t="s">
         <v>1312</v>
@@ -12598,12 +12604,12 @@
         <v>1321</v>
       </c>
       <c r="B777" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B778" t="s">
         <v>1323</v>
@@ -12702,36 +12708,36 @@
         <v>1346</v>
       </c>
       <c r="B790" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B791" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B792" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B793" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B794" t="s">
         <v>1351</v>
@@ -12750,12 +12756,12 @@
         <v>1354</v>
       </c>
       <c r="B796" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B797" t="s">
         <v>1356</v>
@@ -12766,20 +12772,20 @@
         <v>1357</v>
       </c>
       <c r="B798" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B799" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B800" t="s">
         <v>1360</v>
@@ -12790,36 +12796,36 @@
         <v>1361</v>
       </c>
       <c r="B801" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B802" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B803" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B804" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B805" t="s">
         <v>1366</v>
@@ -12830,20 +12836,20 @@
         <v>1367</v>
       </c>
       <c r="B806" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B807" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B808" t="s">
         <v>1370</v>
@@ -12902,28 +12908,28 @@
         <v>1383</v>
       </c>
       <c r="B815" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B816" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B817" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B818" t="s">
         <v>1387</v>
@@ -12982,12 +12988,12 @@
         <v>1400</v>
       </c>
       <c r="B825" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B826" t="s">
         <v>1402</v>
@@ -13006,12 +13012,12 @@
         <v>1405</v>
       </c>
       <c r="B828" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B829" t="s">
         <v>1407</v>
@@ -13038,12 +13044,12 @@
         <v>1412</v>
       </c>
       <c r="B832" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B833" t="s">
         <v>1414</v>
@@ -13054,12 +13060,12 @@
         <v>1415</v>
       </c>
       <c r="B834" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B835" t="s">
         <v>1417</v>
@@ -13070,12 +13076,12 @@
         <v>1418</v>
       </c>
       <c r="B836" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B837" t="s">
         <v>1420</v>
@@ -13086,12 +13092,12 @@
         <v>1421</v>
       </c>
       <c r="B838" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B839" t="s">
         <v>1423</v>
@@ -13102,36 +13108,36 @@
         <v>1424</v>
       </c>
       <c r="B840" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B841" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B842" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B843" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B844" t="s">
         <v>1429</v>
@@ -13150,12 +13156,12 @@
         <v>1432</v>
       </c>
       <c r="B846" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B847" t="s">
         <v>1434</v>
@@ -13174,12 +13180,12 @@
         <v>1437</v>
       </c>
       <c r="B849" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B850" t="s">
         <v>1439</v>
@@ -13190,36 +13196,36 @@
         <v>1440</v>
       </c>
       <c r="B851" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B852" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B853" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B854" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B855" t="s">
         <v>1445</v>
@@ -13326,28 +13332,28 @@
         <v>1470</v>
       </c>
       <c r="B868" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B869" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B870" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B871" t="s">
         <v>1474</v>
@@ -13358,36 +13364,36 @@
         <v>1475</v>
       </c>
       <c r="B872" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B873" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B874" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B875" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B876" t="s">
         <v>1480</v>
@@ -13398,28 +13404,28 @@
         <v>1481</v>
       </c>
       <c r="B877" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B878" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B879" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B880" t="s">
         <v>1485</v>
@@ -13438,12 +13444,12 @@
         <v>1488</v>
       </c>
       <c r="B882" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B883" t="s">
         <v>1490</v>
@@ -13502,20 +13508,20 @@
         <v>1503</v>
       </c>
       <c r="B890" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B891" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B892" t="s">
         <v>1506</v>
@@ -13542,20 +13548,20 @@
         <v>1511</v>
       </c>
       <c r="B895" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B896" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B897" t="s">
         <v>1514</v>
@@ -13566,12 +13572,12 @@
         <v>1515</v>
       </c>
       <c r="B898" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B899" t="s">
         <v>1517</v>
@@ -13582,12 +13588,12 @@
         <v>1518</v>
       </c>
       <c r="B900" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B901" t="s">
         <v>1520</v>
@@ -13598,12 +13604,12 @@
         <v>1521</v>
       </c>
       <c r="B902" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B903" t="s">
         <v>1523</v>
@@ -13614,12 +13620,12 @@
         <v>1524</v>
       </c>
       <c r="B904" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B905" t="s">
         <v>1526</v>
@@ -13654,12 +13660,12 @@
         <v>1533</v>
       </c>
       <c r="B909" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B910" t="s">
         <v>1535</v>
@@ -13710,60 +13716,60 @@
         <v>1546</v>
       </c>
       <c r="B916" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B917" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B918" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B919" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B920" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B921" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B922" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B923" t="s">
         <v>1554</v>
@@ -13790,28 +13796,28 @@
         <v>1559</v>
       </c>
       <c r="B926" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B927" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B928" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B929" t="s">
         <v>1563</v>
@@ -13854,20 +13860,20 @@
         <v>1572</v>
       </c>
       <c r="B934" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B935" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B936" t="s">
         <v>1575</v>
@@ -13902,12 +13908,12 @@
         <v>1582</v>
       </c>
       <c r="B940" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B941" t="s">
         <v>1584</v>
@@ -13926,12 +13932,12 @@
         <v>1587</v>
       </c>
       <c r="B943" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B944" t="s">
         <v>1589</v>
@@ -13942,12 +13948,12 @@
         <v>1590</v>
       </c>
       <c r="B945" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B946" t="s">
         <v>1592</v>
@@ -14014,28 +14020,28 @@
         <v>1607</v>
       </c>
       <c r="B954" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B955" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B956" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B957" t="s">
         <v>1611</v>
@@ -14054,44 +14060,44 @@
         <v>1614</v>
       </c>
       <c r="B959" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B960" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B961" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B962" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B963" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B964" t="s">
         <v>1620</v>
@@ -14134,20 +14140,20 @@
         <v>1629</v>
       </c>
       <c r="B969" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B970" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B971" t="s">
         <v>1632</v>
@@ -14182,12 +14188,12 @@
         <v>1639</v>
       </c>
       <c r="B975" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B976" t="s">
         <v>1641</v>
@@ -14206,20 +14212,20 @@
         <v>1644</v>
       </c>
       <c r="B978" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B979" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B980" t="s">
         <v>1647</v>
@@ -14318,28 +14324,28 @@
         <v>1670</v>
       </c>
       <c r="B992" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B993" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B994" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B995" t="s">
         <v>1674</v>
@@ -14350,36 +14356,36 @@
         <v>1675</v>
       </c>
       <c r="B996" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B997" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B998" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B999" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1000" t="s">
         <v>1680</v>
@@ -14390,12 +14396,12 @@
         <v>1681</v>
       </c>
       <c r="B1001" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1002" t="s">
         <v>1683</v>
@@ -14430,12 +14436,12 @@
         <v>1690</v>
       </c>
       <c r="B1006" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1007" t="s">
         <v>1692</v>
@@ -14454,12 +14460,12 @@
         <v>1695</v>
       </c>
       <c r="B1009" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1010" t="s">
         <v>1697</v>
@@ -14510,20 +14516,20 @@
         <v>1708</v>
       </c>
       <c r="B1016" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1017" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1018" t="s">
         <v>1711</v>
@@ -14550,36 +14556,36 @@
         <v>1716</v>
       </c>
       <c r="B1021" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1022" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1023" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1024" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1025" t="s">
         <v>1721</v>
@@ -14598,12 +14604,12 @@
         <v>1724</v>
       </c>
       <c r="B1027" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1028" t="s">
         <v>1726</v>
@@ -14614,20 +14620,20 @@
         <v>1727</v>
       </c>
       <c r="B1029" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1030" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1031" t="s">
         <v>1730</v>
@@ -14646,12 +14652,12 @@
         <v>1733</v>
       </c>
       <c r="B1033" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1034" t="s">
         <v>1735</v>
@@ -14678,12 +14684,12 @@
         <v>1740</v>
       </c>
       <c r="B1037" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="B1038" t="s">
         <v>1742</v>
@@ -14694,20 +14700,20 @@
         <v>1743</v>
       </c>
       <c r="B1039" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="B1040" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1041" t="s">
         <v>1746</v>
@@ -14718,52 +14724,52 @@
         <v>1747</v>
       </c>
       <c r="B1042" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B1043" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1044" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1045" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1046" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1047" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B1048" t="s">
         <v>1754</v>
@@ -14782,12 +14788,12 @@
         <v>1757</v>
       </c>
       <c r="B1050" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1051" t="s">
         <v>1759</v>
@@ -14814,12 +14820,12 @@
         <v>1764</v>
       </c>
       <c r="B1054" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B1055" t="s">
         <v>1766</v>
@@ -14838,12 +14844,12 @@
         <v>1769</v>
       </c>
       <c r="B1057" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B1058" t="s">
         <v>1771</v>
@@ -14966,12 +14972,12 @@
         <v>1800</v>
       </c>
       <c r="B1073" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1074" t="s">
         <v>1802</v>
@@ -15070,12 +15076,12 @@
         <v>1825</v>
       </c>
       <c r="B1086" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1087" t="s">
         <v>1827</v>
@@ -15102,20 +15108,20 @@
         <v>1832</v>
       </c>
       <c r="B1090" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1091" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1092" t="s">
         <v>1835</v>
@@ -15126,12 +15132,12 @@
         <v>1836</v>
       </c>
       <c r="B1093" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1094" t="s">
         <v>1838</v>
@@ -15150,12 +15156,12 @@
         <v>1841</v>
       </c>
       <c r="B1096" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1097" t="s">
         <v>1843</v>
@@ -15230,12 +15236,12 @@
         <v>1860</v>
       </c>
       <c r="B1106" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1107" t="s">
         <v>1862</v>
@@ -15278,12 +15284,12 @@
         <v>1871</v>
       </c>
       <c r="B1112" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1113" t="s">
         <v>1873</v>
@@ -15302,20 +15308,20 @@
         <v>1876</v>
       </c>
       <c r="B1115" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1116" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1117" t="s">
         <v>1879</v>
@@ -15326,20 +15332,20 @@
         <v>1880</v>
       </c>
       <c r="B1118" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1119" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1120" t="s">
         <v>1883</v>
@@ -15390,12 +15396,12 @@
         <v>1894</v>
       </c>
       <c r="B1126" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1127" t="s">
         <v>1896</v>
@@ -15438,12 +15444,12 @@
         <v>1905</v>
       </c>
       <c r="B1132" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1133" t="s">
         <v>1907</v>
@@ -15550,28 +15556,28 @@
         <v>1932</v>
       </c>
       <c r="B1146" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1147" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1148" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1149" t="s">
         <v>1936</v>
@@ -15582,12 +15588,12 @@
         <v>1937</v>
       </c>
       <c r="B1150" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="B1151" t="s">
         <v>1939</v>
@@ -15606,28 +15612,28 @@
         <v>1942</v>
       </c>
       <c r="B1153" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="B1154" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="B1155" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B1156" t="s">
         <v>1946</v>
@@ -15710,12 +15716,12 @@
         <v>1965</v>
       </c>
       <c r="B1166" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="B1167" t="s">
         <v>1967</v>
@@ -15758,20 +15764,20 @@
         <v>1976</v>
       </c>
       <c r="B1172" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="B1173" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="B1174" t="s">
         <v>1979</v>
@@ -15782,12 +15788,12 @@
         <v>1980</v>
       </c>
       <c r="B1175" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="B1176" t="s">
         <v>1982</v>
@@ -15806,20 +15812,20 @@
         <v>1985</v>
       </c>
       <c r="B1178" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="B1179" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="B1180" t="s">
         <v>1988</v>
@@ -15830,36 +15836,36 @@
         <v>1989</v>
       </c>
       <c r="B1181" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="B1182" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="B1183" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1184" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B1185" t="s">
         <v>1994</v>
@@ -15878,12 +15884,12 @@
         <v>1997</v>
       </c>
       <c r="B1187" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="B1188" t="s">
         <v>1999</v>
@@ -15902,19 +15908,27 @@
         <v>2002</v>
       </c>
       <c r="B1190" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B1191" t="s">
         <v>2004</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>2006</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/sl/headTags.xlsx
+++ b/lang/sl/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2009">
   <si>
     <t>en</t>
   </si>
@@ -2135,6 +2135,12 @@
   </si>
   <si>
     <t>Pisava (Orange)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>Črkovna vrsta (Pale Oak)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -6384,7 +6390,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9868,20 +9874,20 @@
         <v>746</v>
       </c>
       <c r="B435" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B436" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B437" t="s">
         <v>749</v>
@@ -9892,20 +9898,20 @@
         <v>750</v>
       </c>
       <c r="B438" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B439" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B440" t="s">
         <v>753</v>
@@ -9980,12 +9986,12 @@
         <v>770</v>
       </c>
       <c r="B449" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B450" t="s">
         <v>772</v>
@@ -9996,12 +10002,12 @@
         <v>773</v>
       </c>
       <c r="B451" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B452" t="s">
         <v>775</v>
@@ -10012,12 +10018,12 @@
         <v>776</v>
       </c>
       <c r="B453" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B454" t="s">
         <v>778</v>
@@ -10052,20 +10058,20 @@
         <v>785</v>
       </c>
       <c r="B458" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B459" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B460" t="s">
         <v>788</v>
@@ -10092,12 +10098,12 @@
         <v>793</v>
       </c>
       <c r="B463" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B464" t="s">
         <v>795</v>
@@ -10132,36 +10138,36 @@
         <v>802</v>
       </c>
       <c r="B468" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B469" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B470" t="s">
-        <v>529</v>
+        <v>805</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B471" t="s">
-        <v>805</v>
+        <v>529</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B472" t="s">
         <v>807</v>
@@ -10172,12 +10178,12 @@
         <v>808</v>
       </c>
       <c r="B473" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B474" t="s">
         <v>810</v>
@@ -10196,36 +10202,36 @@
         <v>813</v>
       </c>
       <c r="B476" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B477" t="s">
-        <v>529</v>
+        <v>815</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B478" t="s">
-        <v>815</v>
+        <v>529</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B479" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B480" t="s">
         <v>818</v>
@@ -10236,12 +10242,12 @@
         <v>819</v>
       </c>
       <c r="B481" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B482" t="s">
         <v>821</v>
@@ -10276,20 +10282,20 @@
         <v>828</v>
       </c>
       <c r="B486" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B487" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B488" t="s">
         <v>831</v>
@@ -10300,12 +10306,12 @@
         <v>832</v>
       </c>
       <c r="B489" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B490" t="s">
         <v>834</v>
@@ -10316,36 +10322,36 @@
         <v>835</v>
       </c>
       <c r="B491" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B492" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B493" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B494" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B495" t="s">
         <v>840</v>
@@ -10500,12 +10506,12 @@
         <v>877</v>
       </c>
       <c r="B514" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B515" t="s">
         <v>879</v>
@@ -10524,12 +10530,12 @@
         <v>882</v>
       </c>
       <c r="B517" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B518" t="s">
         <v>884</v>
@@ -10580,20 +10586,20 @@
         <v>895</v>
       </c>
       <c r="B524" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B525" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B526" t="s">
         <v>898</v>
@@ -10676,12 +10682,12 @@
         <v>917</v>
       </c>
       <c r="B536" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B537" t="s">
         <v>919</v>
@@ -10700,20 +10706,20 @@
         <v>922</v>
       </c>
       <c r="B539" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B540" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B541" t="s">
         <v>925</v>
@@ -10732,28 +10738,28 @@
         <v>928</v>
       </c>
       <c r="B543" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B544" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B545" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B546" t="s">
         <v>932</v>
@@ -10788,20 +10794,20 @@
         <v>939</v>
       </c>
       <c r="B550" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B551" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B552" t="s">
         <v>942</v>
@@ -10820,20 +10826,20 @@
         <v>945</v>
       </c>
       <c r="B554" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B555" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B556" t="s">
         <v>948</v>
@@ -10860,12 +10866,12 @@
         <v>953</v>
       </c>
       <c r="B559" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B560" t="s">
         <v>955</v>
@@ -10924,28 +10930,28 @@
         <v>968</v>
       </c>
       <c r="B567" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B568" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B569" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B570" t="s">
         <v>972</v>
@@ -10964,12 +10970,12 @@
         <v>975</v>
       </c>
       <c r="B572" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B573" t="s">
         <v>977</v>
@@ -11020,12 +11026,12 @@
         <v>988</v>
       </c>
       <c r="B579" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B580" t="s">
         <v>990</v>
@@ -11036,36 +11042,36 @@
         <v>991</v>
       </c>
       <c r="B581" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B582" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B583" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B584" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B585" t="s">
         <v>996</v>
@@ -11084,12 +11090,12 @@
         <v>999</v>
       </c>
       <c r="B587" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B588" t="s">
         <v>1001</v>
@@ -11188,12 +11194,12 @@
         <v>1024</v>
       </c>
       <c r="B600" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B601" t="s">
         <v>1026</v>
@@ -11204,12 +11210,12 @@
         <v>1027</v>
       </c>
       <c r="B602" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B603" t="s">
         <v>1029</v>
@@ -11276,20 +11282,20 @@
         <v>1044</v>
       </c>
       <c r="B611" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B612" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B613" t="s">
         <v>1047</v>
@@ -11300,12 +11306,12 @@
         <v>1048</v>
       </c>
       <c r="B614" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B615" t="s">
         <v>1050</v>
@@ -11356,12 +11362,12 @@
         <v>1061</v>
       </c>
       <c r="B621" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B622" t="s">
         <v>1063</v>
@@ -11380,12 +11386,12 @@
         <v>1066</v>
       </c>
       <c r="B624" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B625" t="s">
         <v>1068</v>
@@ -11412,12 +11418,12 @@
         <v>1073</v>
       </c>
       <c r="B628" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B629" t="s">
         <v>1075</v>
@@ -11428,12 +11434,12 @@
         <v>1076</v>
       </c>
       <c r="B630" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B631" t="s">
         <v>1078</v>
@@ -11452,12 +11458,12 @@
         <v>1081</v>
       </c>
       <c r="B633" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B634" t="s">
         <v>1083</v>
@@ -11484,44 +11490,44 @@
         <v>1088</v>
       </c>
       <c r="B637" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B638" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B639" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B640" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B641" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B642" t="s">
         <v>1094</v>
@@ -11540,28 +11546,28 @@
         <v>1097</v>
       </c>
       <c r="B644" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B645" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B646" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B647" t="s">
         <v>1101</v>
@@ -11572,12 +11578,12 @@
         <v>1102</v>
       </c>
       <c r="B648" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B649" t="s">
         <v>1104</v>
@@ -11588,12 +11594,12 @@
         <v>1105</v>
       </c>
       <c r="B650" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B651" t="s">
         <v>1107</v>
@@ -11604,20 +11610,20 @@
         <v>1108</v>
       </c>
       <c r="B652" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B653" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B654" t="s">
         <v>1111</v>
@@ -11652,28 +11658,28 @@
         <v>1118</v>
       </c>
       <c r="B658" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B659" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B660" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B661" t="s">
         <v>1122</v>
@@ -11684,12 +11690,12 @@
         <v>1123</v>
       </c>
       <c r="B662" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B663" t="s">
         <v>1125</v>
@@ -11716,12 +11722,12 @@
         <v>1130</v>
       </c>
       <c r="B666" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B667" t="s">
         <v>1132</v>
@@ -11796,12 +11802,12 @@
         <v>1149</v>
       </c>
       <c r="B676" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B677" t="s">
         <v>1151</v>
@@ -11884,12 +11890,12 @@
         <v>1170</v>
       </c>
       <c r="B687" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B688" t="s">
         <v>1172</v>
@@ -11916,20 +11922,20 @@
         <v>1177</v>
       </c>
       <c r="B691" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B692" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B693" t="s">
         <v>1180</v>
@@ -12012,12 +12018,12 @@
         <v>1199</v>
       </c>
       <c r="B703" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B704" t="s">
         <v>1201</v>
@@ -12060,12 +12066,12 @@
         <v>1210</v>
       </c>
       <c r="B709" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B710" t="s">
         <v>1212</v>
@@ -12076,20 +12082,20 @@
         <v>1213</v>
       </c>
       <c r="B711" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B712" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B713" t="s">
         <v>1216</v>
@@ -12100,28 +12106,28 @@
         <v>1217</v>
       </c>
       <c r="B714" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B715" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B716" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B717" t="s">
         <v>1221</v>
@@ -12140,20 +12146,20 @@
         <v>1224</v>
       </c>
       <c r="B719" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B720" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B721" t="s">
         <v>1227</v>
@@ -12180,20 +12186,20 @@
         <v>1232</v>
       </c>
       <c r="B724" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B725" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B726" t="s">
         <v>1235</v>
@@ -12212,12 +12218,12 @@
         <v>1238</v>
       </c>
       <c r="B728" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B729" t="s">
         <v>1240</v>
@@ -12252,20 +12258,20 @@
         <v>1247</v>
       </c>
       <c r="B733" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B734" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B735" t="s">
         <v>1250</v>
@@ -12284,20 +12290,20 @@
         <v>1253</v>
       </c>
       <c r="B737" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B738" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B739" t="s">
         <v>1256</v>
@@ -12308,12 +12314,12 @@
         <v>1257</v>
       </c>
       <c r="B740" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B741" t="s">
         <v>1259</v>
@@ -12340,12 +12346,12 @@
         <v>1264</v>
       </c>
       <c r="B744" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B745" t="s">
         <v>1266</v>
@@ -12364,12 +12370,12 @@
         <v>1269</v>
       </c>
       <c r="B747" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B748" t="s">
         <v>1271</v>
@@ -12396,20 +12402,20 @@
         <v>1276</v>
       </c>
       <c r="B751" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B752" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B753" t="s">
         <v>1279</v>
@@ -12428,20 +12434,20 @@
         <v>1282</v>
       </c>
       <c r="B755" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B756" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B757" t="s">
         <v>1285</v>
@@ -12540,12 +12546,12 @@
         <v>1308</v>
       </c>
       <c r="B769" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B770" t="s">
         <v>1310</v>
@@ -12556,20 +12562,20 @@
         <v>1311</v>
       </c>
       <c r="B771" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B772" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B773" t="s">
         <v>1314</v>
@@ -12612,12 +12618,12 @@
         <v>1323</v>
       </c>
       <c r="B778" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B779" t="s">
         <v>1325</v>
@@ -12716,36 +12722,36 @@
         <v>1348</v>
       </c>
       <c r="B791" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B792" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B793" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B794" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B795" t="s">
         <v>1353</v>
@@ -12764,12 +12770,12 @@
         <v>1356</v>
       </c>
       <c r="B797" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B798" t="s">
         <v>1358</v>
@@ -12780,20 +12786,20 @@
         <v>1359</v>
       </c>
       <c r="B799" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B800" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B801" t="s">
         <v>1362</v>
@@ -12804,36 +12810,36 @@
         <v>1363</v>
       </c>
       <c r="B802" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B803" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B804" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B805" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B806" t="s">
         <v>1368</v>
@@ -12844,20 +12850,20 @@
         <v>1369</v>
       </c>
       <c r="B807" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B808" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B809" t="s">
         <v>1372</v>
@@ -12916,28 +12922,28 @@
         <v>1385</v>
       </c>
       <c r="B816" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B817" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B818" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B819" t="s">
         <v>1389</v>
@@ -12996,12 +13002,12 @@
         <v>1402</v>
       </c>
       <c r="B826" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B827" t="s">
         <v>1404</v>
@@ -13020,12 +13026,12 @@
         <v>1407</v>
       </c>
       <c r="B829" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B830" t="s">
         <v>1409</v>
@@ -13052,12 +13058,12 @@
         <v>1414</v>
       </c>
       <c r="B833" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B834" t="s">
         <v>1416</v>
@@ -13068,12 +13074,12 @@
         <v>1417</v>
       </c>
       <c r="B835" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B836" t="s">
         <v>1419</v>
@@ -13084,12 +13090,12 @@
         <v>1420</v>
       </c>
       <c r="B837" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B838" t="s">
         <v>1422</v>
@@ -13100,12 +13106,12 @@
         <v>1423</v>
       </c>
       <c r="B839" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B840" t="s">
         <v>1425</v>
@@ -13116,36 +13122,36 @@
         <v>1426</v>
       </c>
       <c r="B841" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B842" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B843" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B844" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B845" t="s">
         <v>1431</v>
@@ -13164,12 +13170,12 @@
         <v>1434</v>
       </c>
       <c r="B847" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B848" t="s">
         <v>1436</v>
@@ -13188,12 +13194,12 @@
         <v>1439</v>
       </c>
       <c r="B850" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B851" t="s">
         <v>1441</v>
@@ -13204,36 +13210,36 @@
         <v>1442</v>
       </c>
       <c r="B852" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B853" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B854" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B855" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B856" t="s">
         <v>1447</v>
@@ -13340,28 +13346,28 @@
         <v>1472</v>
       </c>
       <c r="B869" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B870" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B871" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B872" t="s">
         <v>1476</v>
@@ -13372,36 +13378,36 @@
         <v>1477</v>
       </c>
       <c r="B873" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B874" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B875" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B876" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B877" t="s">
         <v>1482</v>
@@ -13412,28 +13418,28 @@
         <v>1483</v>
       </c>
       <c r="B878" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B879" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B880" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B881" t="s">
         <v>1487</v>
@@ -13452,12 +13458,12 @@
         <v>1490</v>
       </c>
       <c r="B883" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B884" t="s">
         <v>1492</v>
@@ -13516,20 +13522,20 @@
         <v>1505</v>
       </c>
       <c r="B891" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B892" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B893" t="s">
         <v>1508</v>
@@ -13556,20 +13562,20 @@
         <v>1513</v>
       </c>
       <c r="B896" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B897" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B898" t="s">
         <v>1516</v>
@@ -13580,12 +13586,12 @@
         <v>1517</v>
       </c>
       <c r="B899" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B900" t="s">
         <v>1519</v>
@@ -13596,12 +13602,12 @@
         <v>1520</v>
       </c>
       <c r="B901" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B902" t="s">
         <v>1522</v>
@@ -13612,12 +13618,12 @@
         <v>1523</v>
       </c>
       <c r="B903" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B904" t="s">
         <v>1525</v>
@@ -13628,12 +13634,12 @@
         <v>1526</v>
       </c>
       <c r="B905" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B906" t="s">
         <v>1528</v>
@@ -13668,12 +13674,12 @@
         <v>1535</v>
       </c>
       <c r="B910" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B911" t="s">
         <v>1537</v>
@@ -13724,60 +13730,60 @@
         <v>1548</v>
       </c>
       <c r="B917" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B918" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B919" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B920" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B921" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B922" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B923" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B924" t="s">
         <v>1556</v>
@@ -13804,28 +13810,28 @@
         <v>1561</v>
       </c>
       <c r="B927" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B928" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B929" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B930" t="s">
         <v>1565</v>
@@ -13868,20 +13874,20 @@
         <v>1574</v>
       </c>
       <c r="B935" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B936" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B937" t="s">
         <v>1577</v>
@@ -13916,12 +13922,12 @@
         <v>1584</v>
       </c>
       <c r="B941" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B942" t="s">
         <v>1586</v>
@@ -13940,12 +13946,12 @@
         <v>1589</v>
       </c>
       <c r="B944" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B945" t="s">
         <v>1591</v>
@@ -13956,12 +13962,12 @@
         <v>1592</v>
       </c>
       <c r="B946" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B947" t="s">
         <v>1594</v>
@@ -14028,28 +14034,28 @@
         <v>1609</v>
       </c>
       <c r="B955" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B956" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B957" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B958" t="s">
         <v>1613</v>
@@ -14068,44 +14074,44 @@
         <v>1616</v>
       </c>
       <c r="B960" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B961" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B962" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B963" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B964" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B965" t="s">
         <v>1622</v>
@@ -14148,20 +14154,20 @@
         <v>1631</v>
       </c>
       <c r="B970" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B971" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B972" t="s">
         <v>1634</v>
@@ -14196,12 +14202,12 @@
         <v>1641</v>
       </c>
       <c r="B976" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B977" t="s">
         <v>1643</v>
@@ -14220,20 +14226,20 @@
         <v>1646</v>
       </c>
       <c r="B979" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B980" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B981" t="s">
         <v>1649</v>
@@ -14332,28 +14338,28 @@
         <v>1672</v>
       </c>
       <c r="B993" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B994" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B995" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B996" t="s">
         <v>1676</v>
@@ -14364,36 +14370,36 @@
         <v>1677</v>
       </c>
       <c r="B997" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B998" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B999" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1000" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1001" t="s">
         <v>1682</v>
@@ -14404,12 +14410,12 @@
         <v>1683</v>
       </c>
       <c r="B1002" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1003" t="s">
         <v>1685</v>
@@ -14444,12 +14450,12 @@
         <v>1692</v>
       </c>
       <c r="B1007" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1008" t="s">
         <v>1694</v>
@@ -14468,12 +14474,12 @@
         <v>1697</v>
       </c>
       <c r="B1010" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1011" t="s">
         <v>1699</v>
@@ -14524,20 +14530,20 @@
         <v>1710</v>
       </c>
       <c r="B1017" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1018" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1019" t="s">
         <v>1713</v>
@@ -14564,36 +14570,36 @@
         <v>1718</v>
       </c>
       <c r="B1022" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1023" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1024" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1025" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1026" t="s">
         <v>1723</v>
@@ -14612,12 +14618,12 @@
         <v>1726</v>
       </c>
       <c r="B1028" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1029" t="s">
         <v>1728</v>
@@ -14628,20 +14634,20 @@
         <v>1729</v>
       </c>
       <c r="B1030" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1031" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1032" t="s">
         <v>1732</v>
@@ -14660,12 +14666,12 @@
         <v>1735</v>
       </c>
       <c r="B1034" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1035" t="s">
         <v>1737</v>
@@ -14692,12 +14698,12 @@
         <v>1742</v>
       </c>
       <c r="B1038" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1039" t="s">
         <v>1744</v>
@@ -14708,20 +14714,20 @@
         <v>1745</v>
       </c>
       <c r="B1040" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1041" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1042" t="s">
         <v>1748</v>
@@ -14732,52 +14738,52 @@
         <v>1749</v>
       </c>
       <c r="B1043" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1044" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1045" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1046" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B1047" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1048" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1049" t="s">
         <v>1756</v>
@@ -14796,12 +14802,12 @@
         <v>1759</v>
       </c>
       <c r="B1051" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B1052" t="s">
         <v>1761</v>
@@ -14828,12 +14834,12 @@
         <v>1766</v>
       </c>
       <c r="B1055" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B1056" t="s">
         <v>1768</v>
@@ -14852,12 +14858,12 @@
         <v>1771</v>
       </c>
       <c r="B1058" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1059" t="s">
         <v>1773</v>
@@ -14980,12 +14986,12 @@
         <v>1802</v>
       </c>
       <c r="B1074" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="B1075" t="s">
         <v>1804</v>
@@ -15084,12 +15090,12 @@
         <v>1827</v>
       </c>
       <c r="B1087" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1088" t="s">
         <v>1829</v>
@@ -15116,20 +15122,20 @@
         <v>1834</v>
       </c>
       <c r="B1091" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1092" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="B1093" t="s">
         <v>1837</v>
@@ -15140,12 +15146,12 @@
         <v>1838</v>
       </c>
       <c r="B1094" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="B1095" t="s">
         <v>1840</v>
@@ -15164,12 +15170,12 @@
         <v>1843</v>
       </c>
       <c r="B1097" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1098" t="s">
         <v>1845</v>
@@ -15244,12 +15250,12 @@
         <v>1862</v>
       </c>
       <c r="B1107" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1108" t="s">
         <v>1864</v>
@@ -15292,12 +15298,12 @@
         <v>1873</v>
       </c>
       <c r="B1113" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1114" t="s">
         <v>1875</v>
@@ -15316,20 +15322,20 @@
         <v>1878</v>
       </c>
       <c r="B1116" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B1117" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1118" t="s">
         <v>1881</v>
@@ -15340,20 +15346,20 @@
         <v>1882</v>
       </c>
       <c r="B1119" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B1120" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B1121" t="s">
         <v>1885</v>
@@ -15404,12 +15410,12 @@
         <v>1896</v>
       </c>
       <c r="B1127" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B1128" t="s">
         <v>1898</v>
@@ -15452,12 +15458,12 @@
         <v>1907</v>
       </c>
       <c r="B1133" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1134" t="s">
         <v>1909</v>
@@ -15564,28 +15570,28 @@
         <v>1934</v>
       </c>
       <c r="B1147" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1148" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B1149" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="B1150" t="s">
         <v>1938</v>
@@ -15596,12 +15602,12 @@
         <v>1939</v>
       </c>
       <c r="B1151" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="B1152" t="s">
         <v>1941</v>
@@ -15620,28 +15626,28 @@
         <v>1944</v>
       </c>
       <c r="B1154" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="B1155" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="B1156" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="B1157" t="s">
         <v>1948</v>
@@ -15724,12 +15730,12 @@
         <v>1967</v>
       </c>
       <c r="B1167" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="B1168" t="s">
         <v>1969</v>
@@ -15772,20 +15778,20 @@
         <v>1978</v>
       </c>
       <c r="B1173" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="B1174" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="B1175" t="s">
         <v>1981</v>
@@ -15796,12 +15802,12 @@
         <v>1982</v>
       </c>
       <c r="B1176" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="B1177" t="s">
         <v>1984</v>
@@ -15820,20 +15826,20 @@
         <v>1987</v>
       </c>
       <c r="B1179" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="B1180" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="B1181" t="s">
         <v>1990</v>
@@ -15844,36 +15850,36 @@
         <v>1991</v>
       </c>
       <c r="B1182" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="B1183" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="B1184" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="B1185" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="B1186" t="s">
         <v>1996</v>
@@ -15892,12 +15898,12 @@
         <v>1999</v>
       </c>
       <c r="B1188" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B1189" t="s">
         <v>2001</v>
@@ -15916,19 +15922,27 @@
         <v>2004</v>
       </c>
       <c r="B1191" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B1192" t="s">
         <v>2006</v>
       </c>
     </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>2008</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
